--- a/data.xlsx
+++ b/data.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R81e8c0b303da4dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Rfdf294bd60b94460"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R36188a97010e4876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R1842c2faa4944806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="Rfb33a9898c574a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="Ra36d01f7e3024107"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Raab706a60a7b424a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R56aef494ce9d4715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="Raf6b9546dae241f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R7a192d00b87545ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -299,7 +299,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.0.0</x:v>
+        <x:v>v3.1.0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R3cfe8ca754424e07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Rc70f931c09b44f2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Rfa720460f724475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R56fea1aad0644c43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="Rc8719890d2514c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Rb708caff7bfb4aae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R2f81c6373eed4298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R86dc3b31573b4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Ra185e35d55704e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R12f8ecd0a45647d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R41f02ea5e09a43cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R3b81ce047176405c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -317,7 +317,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.1.1</x:v>
+        <x:v>v3.1.2</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R2f81c6373eed4298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R86dc3b31573b4cee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Ra185e35d55704e6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R12f8ecd0a45647d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R41f02ea5e09a43cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R3b81ce047176405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="Rd93319efadb2448d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Re75e5985a20e455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R2a9905ce337344c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="Ree42beae42dd49ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="Re3d20c7d1abb4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R713f5c29847c4530"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -317,7 +317,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.1.2</x:v>
+        <x:v>v3.1.3</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="Rd93319efadb2448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Re75e5985a20e455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R2a9905ce337344c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="Ree42beae42dd49ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="Re3d20c7d1abb4cee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R713f5c29847c4530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="Rc17f017f621f431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Reabd52bc72464877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Rf188f40a0ec74cb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R28706b2d06d94c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R3d489657e75047be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Rf44b08a1df564fa7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -317,7 +317,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.1.3</x:v>
+        <x:v>v3.1.4</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1613,7 +1613,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而D.Va的打法核心是——擅长吃飞行弹道与切后排。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给D.Va真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给D.Va真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -1642,7 +1642,7 @@
         <x:v>D.Mon</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而D.Mon的打法核心是——机甲坦克，兼具正面屏障、机动和近战压迫。D.Va应把自己的坦克资源用于占住D.Mon最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵D.Mon时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -1671,7 +1671,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而破坏球的打法核心是——靠骚扰和位移制造空间。D.Va应把自己的坦克资源用于占住破坏球最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵破坏球时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -1700,7 +1700,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而温斯顿的打法核心是——主要针对脆皮后排和高台。D.Va应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵温斯顿时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -1932,7 +1932,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而末日铁拳的打法核心是——核心是机动性与进出场节奏。奥丽莎应把自己的坦克资源用于占住末日铁拳最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住末日铁拳最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2019,7 +2019,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而末日铁拳的打法核心是——核心是机动性与进出场节奏。黑影需要利用自身伤害窗口持续逼末日铁拳交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼末日铁拳交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2106,7 +2106,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而末日铁拳的打法核心是——核心是机动性与进出场节奏。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给末日铁拳真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给末日铁拳真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2135,7 +2135,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而末日铁拳的打法核心是——核心是机动性与进出场节奏。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给末日铁拳真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给末日铁拳真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2164,7 +2164,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。末日铁拳应把自己的坦克资源用于占住西格玛最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵西格玛时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2193,7 +2193,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。末日铁拳应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵查莉娅时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2222,7 +2222,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而D.Va的打法核心是——擅长吃飞行弹道与切后排。末日铁拳应把自己的坦克资源用于占住D.Va最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵D.Va时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2251,7 +2251,7 @@
         <x:v>士兵：76</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而士兵：76的打法核心是——泛用性高，对空稳定。末日铁拳应把自己的坦克资源用于占住士兵：76最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵士兵：76时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2338,7 +2338,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。末日铁拳应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵禅雅塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2367,7 +2367,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。末日铁拳应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵安娜时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2396,7 +2396,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。末日铁拳应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵天使时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2425,7 +2425,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。奥丽莎应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2454,7 +2454,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。D.Va应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2483,7 +2483,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。查莉娅应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>查莉娅应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F42" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。法老之鹰需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2628,7 +2628,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F45" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2657,7 +2657,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F46" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2686,7 +2686,7 @@
         <x:v>拉玛刹</x:v>
       </x:c>
       <x:c r="F47" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而拉玛刹的打法核心是——变身阶段近战压制力高。渣客女王应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵拉玛刹时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2715,7 +2715,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F48" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而路霸的打法核心是——钩中关键目标能快速形成击杀。渣客女王应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵路霸时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F49" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而莱因哈特的打法核心是——强依赖近距离与地图拐角。渣客女王应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莱因哈特时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2773,7 +2773,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F50" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而美的打法核心是——擅长分割阵型和减速近战目标。渣客女王应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵美时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2802,7 +2802,7 @@
         <x:v>卡西迪</x:v>
       </x:c>
       <x:c r="F51" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。渣客女王应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卡西迪时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2831,7 +2831,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F52" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。渣客女王应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵托比昂时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G52" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2860,7 +2860,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F53" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。渣客女王应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵禅雅塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G53" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2889,7 +2889,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F54" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。渣客女王应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵生命之梭时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G54" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2918,7 +2918,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F55" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。渣客女王应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卢西奥时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G55" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2947,7 +2947,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F56" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而奥丽莎的打法核心是——强在正面抗压和打断。查莉娅应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>查莉娅应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G56" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -2976,7 +2976,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F57" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而奥丽莎的打法核心是——强在正面抗压和打断。西格玛应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G57" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3005,7 +3005,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F58" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而奥丽莎的打法核心是——强在正面抗压和打断。D.Va应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G58" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3034,7 +3034,7 @@
         <x:v>秩序之光</x:v>
       </x:c>
       <x:c r="F59" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而奥丽莎的打法核心是——强在正面抗压和打断。秩序之光需要利用自身伤害窗口持续逼奥丽莎交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>秩序之光需要利用自身伤害窗口持续逼奥丽莎交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G59" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3179,7 +3179,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F64" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而奥丽莎的打法核心是——强在正面抗压和打断。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给奥丽莎真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给奥丽莎真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G64" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3208,7 +3208,7 @@
         <x:v>末日铁拳</x:v>
       </x:c>
       <x:c r="F65" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而末日铁拳的打法核心是——核心是机动性与进出场节奏。奥丽莎应把自己的坦克资源用于占住末日铁拳最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵末日铁拳时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G65" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3237,7 +3237,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F66" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而路霸的打法核心是——钩中关键目标能快速形成击杀。奥丽莎应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵路霸时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G66" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3266,7 +3266,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F67" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而莱因哈特的打法核心是——强依赖近距离与地图拐角。奥丽莎应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莱因哈特时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G67" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3295,7 +3295,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F68" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而源氏的打法核心是——适合切脆皮和收割残血。奥丽莎应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵源氏时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G68" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3324,7 +3324,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F69" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。奥丽莎应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵死神时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G69" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3353,7 +3353,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F70" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而美的打法核心是——擅长分割阵型和减速近战目标。奥丽莎应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵美时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G70" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3382,7 +3382,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F71" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而布丽吉塔的打法核心是——专长是保护后排、反突进。奥丽莎应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵布丽吉塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G71" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3411,7 +3411,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F72" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。奥丽莎应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卢西奥时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G72" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3440,7 +3440,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F73" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。奥丽莎应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莫伊拉时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G73" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3469,7 +3469,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F74" s="11" t="str">
-        <x:v>路霸的对位优势来自其核心特点——钩中关键目标能快速形成击杀；而拉玛刹的打法核心是——变身阶段近战压制力高。路霸应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>路霸应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G74" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3498,7 +3498,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F75" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而拉玛刹的打法核心是——变身阶段近战压制力高。渣客女王应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>渣客女王应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G75" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3527,7 +3527,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F76" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而拉玛刹的打法核心是——变身阶段近战压制力高。奥丽莎应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G76" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3556,7 +3556,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F77" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而拉玛刹的打法核心是——变身阶段近战压制力高。堡垒需要利用自身伤害窗口持续逼拉玛刹交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>堡垒需要利用自身伤害窗口持续逼拉玛刹交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G77" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3585,7 +3585,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F78" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而拉玛刹的打法核心是——变身阶段近战压制力高。法老之鹰需要利用自身伤害窗口持续逼拉玛刹交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼拉玛刹交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G78" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3701,7 +3701,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F82" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而拉玛刹的打法核心是——变身阶段近战压制力高。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给拉玛刹真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给拉玛刹真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G82" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3730,7 +3730,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F83" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而莱因哈特的打法核心是——强依赖近距离与地图拐角。拉玛刹应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莱因哈特时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G83" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3759,7 +3759,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F84" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而温斯顿的打法核心是——主要针对脆皮后排和高台。拉玛刹应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵温斯顿时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G84" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3817,7 +3817,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F86" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而美的打法核心是——擅长分割阵型和减速近战目标。拉玛刹应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵美时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G86" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3846,7 +3846,7 @@
         <x:v>卡西迪</x:v>
       </x:c>
       <x:c r="F87" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。拉玛刹应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卡西迪时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G87" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3875,7 +3875,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F88" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。拉玛刹应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵托比昂时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G88" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3904,7 +3904,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F89" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而布丽吉塔的打法核心是——专长是保护后排、反突进。拉玛刹应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵布丽吉塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G89" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3933,7 +3933,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F90" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。拉玛刹应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卢西奥时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G90" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3962,7 +3962,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F91" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。拉玛刹应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵生命之梭时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G91" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -3991,7 +3991,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F92" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而莱因哈特的打法核心是——强依赖近距离与地图拐角。奥丽莎应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G92" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4020,7 +4020,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F93" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而莱因哈特的打法核心是——强依赖近距离与地图拐角。温斯顿应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G93" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4049,7 +4049,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F94" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而莱因哈特的打法核心是——强依赖近距离与地图拐角。D.Va应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住莱因哈特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G94" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4078,7 +4078,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F95" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而莱因哈特的打法核心是——强依赖近距离与地图拐角。法老之鹰需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G95" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4107,7 +4107,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F96" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而莱因哈特的打法核心是——强依赖近距离与地图拐角。堡垒需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>堡垒需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G96" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4165,7 +4165,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F98" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而莱因哈特的打法核心是——强依赖近距离与地图拐角。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G98" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4223,7 +4223,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F100" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而莱因哈特的打法核心是——强依赖近距离与地图拐角。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G100" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4252,7 +4252,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F101" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。莱因哈特应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵查莉娅时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G101" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4281,7 +4281,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F102" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。莱因哈特应把自己的坦克资源用于占住西格玛最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵西格玛时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G102" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4310,7 +4310,7 @@
         <x:v>拉玛刹</x:v>
       </x:c>
       <x:c r="F103" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而拉玛刹的打法核心是——变身阶段近战压制力高。莱因哈特应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵拉玛刹时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G103" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4339,7 +4339,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F104" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而美的打法核心是——擅长分割阵型和减速近战目标。莱因哈特应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵美时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G104" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4368,7 +4368,7 @@
         <x:v>卡西迪</x:v>
       </x:c>
       <x:c r="F105" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。莱因哈特应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卡西迪时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G105" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4397,7 +4397,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F106" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。莱因哈特应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵托比昂时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G106" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4426,7 +4426,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F107" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。莱因哈特应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卢西奥时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G107" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4455,7 +4455,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F108" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而布丽吉塔的打法核心是——专长是保护后排、反突进。莱因哈特应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵布丽吉塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G108" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4484,7 +4484,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F109" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。莱因哈特应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莫伊拉时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G109" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4513,7 +4513,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F110" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而路霸的打法核心是——钩中关键目标能快速形成击杀。奥丽莎应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G110" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4542,7 +4542,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F111" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而路霸的打法核心是——钩中关键目标能快速形成击杀。渣客女王应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>渣客女王应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G111" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4571,7 +4571,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F112" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而路霸的打法核心是——钩中关键目标能快速形成击杀。D.Va应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G112" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4600,7 +4600,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F113" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而路霸的打法核心是——钩中关键目标能快速形成击杀。死神需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>死神需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G113" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4629,7 +4629,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F114" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而路霸的打法核心是——钩中关键目标能快速形成击杀。堡垒需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>堡垒需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G114" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4687,7 +4687,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F116" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而路霸的打法核心是——钩中关键目标能快速形成击杀。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G116" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4832,7 +4832,7 @@
         <x:v>拉玛刹</x:v>
       </x:c>
       <x:c r="F121" s="11" t="str">
-        <x:v>路霸的对位优势来自其核心特点——钩中关键目标能快速形成击杀；而拉玛刹的打法核心是——变身阶段近战压制力高。路霸应把自己的坦克资源用于占住拉玛刹最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵拉玛刹时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G121" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4919,7 +4919,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F124" s="11" t="str">
-        <x:v>路霸的对位优势来自其核心特点——钩中关键目标能快速形成击杀；而美的打法核心是——擅长分割阵型和减速近战目标。路霸应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵美时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G124" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -4977,7 +4977,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F126" s="11" t="str">
-        <x:v>路霸的对位优势来自其核心特点——钩中关键目标能快速形成击杀；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。路霸应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵禅雅塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G126" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F127" s="11" t="str">
-        <x:v>路霸的对位优势来自其核心特点——钩中关键目标能快速形成击杀；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。路霸应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵安娜时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G127" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5064,7 +5064,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F129" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。莱因哈特应把自己的坦克资源用于占住西格玛最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>莱因哈特应把自己的坦克资源用于占住西格玛最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G129" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5151,7 +5151,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F132" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。源氏需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G132" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5180,7 +5180,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F133" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。猎空需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G133" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5209,7 +5209,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F134" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西格玛真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西格玛真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G134" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5267,7 +5267,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F136" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西格玛真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西格玛真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G136" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5296,7 +5296,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F137" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而路霸的打法核心是——钩中关键目标能快速形成击杀。西格玛应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵路霸时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G137" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5325,7 +5325,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F138" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而奥丽莎的打法核心是——强在正面抗压和打断。西格玛应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵奥丽莎时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G138" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5354,7 +5354,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F139" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。西格玛应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵渣客女王时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G139" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5383,7 +5383,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F140" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。西格玛应把自己的坦克资源用于占住堡垒最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵堡垒时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G140" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5412,7 +5412,7 @@
         <x:v>艾什</x:v>
       </x:c>
       <x:c r="F141" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而艾什的打法核心是——中远距离压制优秀，怕强突脸。西格玛应把自己的坦克资源用于占住艾什最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵艾什时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G141" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5441,7 +5441,7 @@
         <x:v>黑百合</x:v>
       </x:c>
       <x:c r="F142" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而黑百合的打法核心是——远距离威慑强，最怕高机动强突。西格玛应把自己的坦克资源用于占住黑百合最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵黑百合时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G142" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5470,7 +5470,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F143" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。西格玛应把自己的坦克资源用于占住巴蒂斯特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵巴蒂斯特时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G143" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5499,7 +5499,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F144" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。西格玛应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵禅雅塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G144" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5528,7 +5528,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F145" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。西格玛应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵安娜时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G145" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5586,7 +5586,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F147" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而温斯顿的打法核心是——主要针对脆皮后排和高台。D.Va应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G147" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5615,7 +5615,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F148" s="11" t="str">
-        <x:v>渣客女王的对位优势来自其核心特点——近距离持续压迫强，怕被拉扯与减疗；而温斯顿的打法核心是——主要针对脆皮后排和高台。渣客女王应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>渣客女王应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G148" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5644,7 +5644,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F149" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而温斯顿的打法核心是——主要针对脆皮后排和高台。死神需要利用自身伤害窗口持续逼温斯顿交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>死神需要利用自身伤害窗口持续逼温斯顿交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G149" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5673,7 +5673,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F150" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而温斯顿的打法核心是——主要针对脆皮后排和高台。堡垒需要利用自身伤害窗口持续逼温斯顿交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>堡垒需要利用自身伤害窗口持续逼温斯顿交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G150" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5760,7 +5760,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F153" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而温斯顿的打法核心是——主要针对脆皮后排和高台。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给温斯顿真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给温斯顿真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G153" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5789,7 +5789,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F154" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而温斯顿的打法核心是——主要针对脆皮后排和高台。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给温斯顿真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给温斯顿真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G154" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5847,7 +5847,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F156" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。温斯顿应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵查莉娅时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G156" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5934,7 +5934,7 @@
         <x:v>安燃</x:v>
       </x:c>
       <x:c r="F159" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而安燃的打法核心是——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力。温斯顿应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵安燃时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G159" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5963,7 +5963,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F160" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而源氏的打法核心是——适合切脆皮和收割残血。温斯顿应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵源氏时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G160" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -5992,7 +5992,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F161" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。温斯顿应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵禅雅塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G161" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6021,7 +6021,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F162" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。温斯顿应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵安娜时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G162" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6050,7 +6050,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F163" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。温斯顿应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵天使时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G163" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6137,7 +6137,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F166" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而破坏球的打法核心是——靠骚扰和位移制造空间。奥丽莎应把自己的坦克资源用于占住破坏球最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住破坏球最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G166" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6166,7 +6166,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F167" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而破坏球的打法核心是——靠骚扰和位移制造空间。黑影需要利用自身伤害窗口持续逼破坏球交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼破坏球交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G167" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6282,7 +6282,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F171" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而破坏球的打法核心是——靠骚扰和位移制造空间。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给破坏球真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给破坏球真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G171" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6311,7 +6311,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F172" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而破坏球的打法核心是——靠骚扰和位移制造空间。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给破坏球真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给破坏球真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G172" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6340,7 +6340,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F173" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。破坏球应把自己的坦克资源用于占住西格玛最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵西格玛时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G173" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6369,7 +6369,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F174" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。破坏球应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵查莉娅时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G174" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6398,7 +6398,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F175" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而D.Va的打法核心是——擅长吃飞行弹道与切后排。破坏球应把自己的坦克资源用于占住D.Va最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵D.Va时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G175" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6427,7 +6427,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F176" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而源氏的打法核心是——适合切脆皮和收割残血。破坏球应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵源氏时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G176" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6514,7 +6514,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F179" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。破坏球应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵天使时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G179" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6543,7 +6543,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F180" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。破坏球应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵生命之梭时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G180" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6572,7 +6572,7 @@
         <x:v>无漾</x:v>
       </x:c>
       <x:c r="F181" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。破坏球应把自己的坦克资源用于占住无漾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵无漾时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G181" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6601,7 +6601,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F182" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。温斯顿应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G182" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6630,7 +6630,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F183" s="11" t="str">
-        <x:v>莱因哈特的对位优势来自其核心特点——强依赖近距离与地图拐角；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。莱因哈特应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>莱因哈特应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G183" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6659,7 +6659,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F184" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。破坏球应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住查莉娅最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G184" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6688,7 +6688,7 @@
         <x:v>秩序之光</x:v>
       </x:c>
       <x:c r="F185" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。秩序之光需要利用自身伤害窗口持续逼查莉娅交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>秩序之光需要利用自身伤害窗口持续逼查莉娅交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G185" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6717,7 +6717,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F186" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。法老之鹰需要利用自身伤害窗口持续逼查莉娅交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼查莉娅交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G186" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6775,7 +6775,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F188" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给查莉娅真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给查莉娅真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G188" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6804,7 +6804,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F189" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给查莉娅真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给查莉娅真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G189" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6833,7 +6833,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F190" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给查莉娅真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给查莉娅真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G190" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6891,7 +6891,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F192" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而奥丽莎的打法核心是——强在正面抗压和打断。查莉娅应把自己的坦克资源用于占住奥丽莎最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵奥丽莎时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G192" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6949,7 +6949,7 @@
         <x:v>半藏</x:v>
       </x:c>
       <x:c r="F194" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而半藏的打法核心是——有高爆发和探测能力，但被贴脸后容错下降。查莉娅应把自己的坦克资源用于占住半藏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵半藏时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G194" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -6978,7 +6978,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F195" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而源氏的打法核心是——适合切脆皮和收割残血。查莉娅应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵源氏时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G195" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7007,7 +7007,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F196" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而美的打法核心是——擅长分割阵型和减速近战目标。查莉娅应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵美时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G196" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7036,7 +7036,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F197" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而布丽吉塔的打法核心是——专长是保护后排、反突进。查莉娅应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵布丽吉塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G197" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7065,7 +7065,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F198" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。查莉娅应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莫伊拉时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G198" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7094,7 +7094,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F199" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。查莉娅应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卢西奥时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G199" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7152,7 +7152,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F201" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而D.Mon的打法核心是——机甲坦克，兼具正面屏障、机动和近战压迫。D.Va应把自己的坦克资源用于占住D.Mon最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住D.Mon最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G201" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7181,7 +7181,7 @@
         <x:v>拉玛刹</x:v>
       </x:c>
       <x:c r="F202" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而D.Mon的打法核心是——机甲坦克，兼具正面屏障、机动和近战压迫。拉玛刹应把自己的坦克资源用于占住D.Mon最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>拉玛刹应把自己的坦克资源用于占住D.Mon最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G202" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7239,7 +7239,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F204" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而D.Mon的打法核心是——机甲坦克，兼具正面屏障、机动和近战压迫。堡垒需要利用自身伤害窗口持续逼D.Mon交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>堡垒需要利用自身伤害窗口持续逼D.Mon交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G204" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7326,7 +7326,7 @@
         <x:v>飞天猫</x:v>
       </x:c>
       <x:c r="F207" s="11" t="str">
-        <x:v>飞天猫的对位优势来自其核心特点——空中机动辅助，可以快速转移并帮助队友调整位置；而D.Mon的打法核心是——机甲坦克，兼具正面屏障、机动和近战压迫。飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给D.Mon真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给D.Mon真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G207" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7384,7 +7384,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F209" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而温斯顿的打法核心是——主要针对脆皮后排和高台。D.Mon应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵温斯顿时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G209" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7413,7 +7413,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F210" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而破坏球的打法核心是——靠骚扰和位移制造空间。D.Mon应把自己的坦克资源用于占住破坏球最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵破坏球时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G210" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7442,7 +7442,7 @@
         <x:v>骇灾</x:v>
       </x:c>
       <x:c r="F211" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而骇灾的打法核心是——强突进坦克，依靠跳跃、尖刺和墙体压缩空间。D.Mon应把自己的坦克资源用于占住骇灾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵骇灾时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G211" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7471,7 +7471,7 @@
         <x:v>安燃</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而安燃的打法核心是——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力。D.Mon应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵安燃时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G212" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7500,7 +7500,7 @@
         <x:v>黑百合</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而黑百合的打法核心是——远距离威慑强，最怕高机动强突。D.Mon应把自己的坦克资源用于占住黑百合最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵黑百合时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G213" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7529,7 +7529,7 @@
         <x:v>探奇</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而探奇的打法核心是——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。D.Mon应把自己的坦克资源用于占住探奇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵探奇时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G214" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7558,7 +7558,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。D.Mon应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵天使时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G215" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7587,7 +7587,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。D.Mon应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵生命之梭时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G216" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7616,7 +7616,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。D.Mon应把自己的坦克资源用于占住雾子最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵雾子时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G217" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7703,7 +7703,7 @@
         <x:v>D.Mon</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>D.Mon的对位优势来自其核心特点——机甲坦克，兼具正面屏障、机动和近战压迫；而金驭的打法核心是——硬光坦克，依靠屏障、推击和中距离压制控制正面空间。D.Mon应把自己的坦克资源用于占住金驭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Mon应把自己的坦克资源用于占住金驭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G220" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters ; https://overwatch.blizzard.com/en-us/news/patch-notes/pc/</x:v>
@@ -7790,7 +7790,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而金驭的打法核心是——硬光坦克，依靠屏障、推击和中距离压制控制正面空间。死神需要利用自身伤害窗口持续逼金驭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>死神需要利用自身伤害窗口持续逼金驭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G223" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7848,7 +7848,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而金驭的打法核心是——硬光坦克，依靠屏障、推击和中距离压制控制正面空间。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给金驭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给金驭真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G225" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7877,7 +7877,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而金驭的打法核心是——硬光坦克，依靠屏障、推击和中距离压制控制正面空间。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给金驭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给金驭真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G226" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7906,7 +7906,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而破坏球的打法核心是——靠骚扰和位移制造空间。金驭应把自己的坦克资源用于占住破坏球最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵破坏球时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G227" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7935,7 +7935,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而温斯顿的打法核心是——主要针对脆皮后排和高台。金驭应把自己的坦克资源用于占住温斯顿最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵温斯顿时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G228" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7964,7 +7964,7 @@
         <x:v>末日铁拳</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而末日铁拳的打法核心是——核心是机动性与进出场节奏。金驭应把自己的坦克资源用于占住末日铁拳最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵末日铁拳时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G229" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -7993,7 +7993,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而源氏的打法核心是——适合切脆皮和收割残血。金驭应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵源氏时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G230" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8022,7 +8022,7 @@
         <x:v>黑百合</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而黑百合的打法核心是——远距离威慑强，最怕高机动强突。金驭应把自己的坦克资源用于占住黑百合最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵黑百合时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G231" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8051,7 +8051,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。金驭应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵托比昂时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G232" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8080,7 +8080,7 @@
         <x:v>伊拉锐</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。金驭应把自己的坦克资源用于占住伊拉锐最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵伊拉锐时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G233" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8109,7 +8109,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。金驭应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卢西奥时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G234" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8138,7 +8138,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>金驭的对位优势来自其核心特点——硬光坦克，依靠屏障、推击和中距离压制控制正面空间；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。金驭应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莫伊拉时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G235" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8196,7 +8196,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而骇灾的打法核心是——强突进坦克，依靠跳跃、尖刺和墙体压缩空间。奥丽莎应把自己的坦克资源用于占住骇灾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住骇灾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G237" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8225,7 +8225,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而骇灾的打法核心是——强突进坦克，依靠跳跃、尖刺和墙体压缩空间。查莉娅应把自己的坦克资源用于占住骇灾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>查莉娅应把自己的坦克资源用于占住骇灾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G238" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8312,7 +8312,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F241" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而骇灾的打法核心是——强突进坦克，依靠跳跃、尖刺和墙体压缩空间。法老之鹰需要利用自身伤害窗口持续逼骇灾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼骇灾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G241" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8370,7 +8370,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F243" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而骇灾的打法核心是——强突进坦克，依靠跳跃、尖刺和墙体压缩空间。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给骇灾真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给骇灾真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G243" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8428,7 +8428,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F245" s="11" t="str">
-        <x:v>骇灾的对位优势来自其核心特点——强突进坦克，依靠跳跃、尖刺和墙体压缩空间；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。骇灾应把自己的坦克资源用于占住西格玛最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵西格玛时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G245" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8457,7 +8457,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F246" s="11" t="str">
-        <x:v>骇灾的对位优势来自其核心特点——强突进坦克，依靠跳跃、尖刺和墙体压缩空间；而路霸的打法核心是——钩中关键目标能快速形成击杀。骇灾应把自己的坦克资源用于占住路霸最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵路霸时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G246" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8486,7 +8486,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F247" s="11" t="str">
-        <x:v>骇灾的对位优势来自其核心特点——强突进坦克，依靠跳跃、尖刺和墙体压缩空间；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。骇灾应把自己的坦克资源用于占住渣客女王最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵渣客女王时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G247" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8602,7 +8602,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F251" s="11" t="str">
-        <x:v>骇灾的对位优势来自其核心特点——强突进坦克，依靠跳跃、尖刺和墙体压缩空间；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。骇灾应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵禅雅塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G251" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8631,7 +8631,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F252" s="11" t="str">
-        <x:v>骇灾的对位优势来自其核心特点——强突进坦克，依靠跳跃、尖刺和墙体压缩空间；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。骇灾应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵安娜时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G252" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8660,7 +8660,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F253" s="11" t="str">
-        <x:v>骇灾的对位优势来自其核心特点——强突进坦克，依靠跳跃、尖刺和墙体压缩空间；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。骇灾应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵生命之梭时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G253" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8689,7 +8689,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F254" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而毛加的打法核心是——持续火力和近中距离压迫很强，适合正面对拼大体型目标。D.Va应把自己的坦克资源用于占住毛加最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住毛加最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G254" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8718,7 +8718,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F255" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而毛加的打法核心是——持续火力和近中距离压迫很强，适合正面对拼大体型目标。西格玛应把自己的坦克资源用于占住毛加最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住毛加最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G255" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8747,7 +8747,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F256" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而毛加的打法核心是——持续火力和近中距离压迫很强，适合正面对拼大体型目标。奥丽莎应把自己的坦克资源用于占住毛加最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住毛加最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G256" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8776,7 +8776,7 @@
         <x:v>秩序之光</x:v>
       </x:c>
       <x:c r="F257" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而毛加的打法核心是——持续火力和近中距离压迫很强，适合正面对拼大体型目标。秩序之光需要利用自身伤害窗口持续逼毛加交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>秩序之光需要利用自身伤害窗口持续逼毛加交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G257" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -8921,7 +8921,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F262" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而毛加的打法核心是——持续火力和近中距离压迫很强，适合正面对拼大体型目标。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给毛加真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给毛加真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G262" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9037,7 +9037,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F266" s="11" t="str">
-        <x:v>毛加的对位优势来自其核心特点——持续火力和近中距离压迫很强，适合正面对拼大体型目标；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。毛加应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵死神时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G266" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9066,7 +9066,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F267" s="11" t="str">
-        <x:v>毛加的对位优势来自其核心特点——持续火力和近中距离压迫很强，适合正面对拼大体型目标；而美的打法核心是——擅长分割阵型和减速近战目标。毛加应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵美时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G267" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9095,7 +9095,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F268" s="11" t="str">
-        <x:v>毛加的对位优势来自其核心特点——持续火力和近中距离压迫很强，适合正面对拼大体型目标；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。毛加应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵托比昂时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G268" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9124,7 +9124,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F269" s="11" t="str">
-        <x:v>毛加的对位优势来自其核心特点——持续火力和近中距离压迫很强，适合正面对拼大体型目标；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。毛加应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵莫伊拉时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G269" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9153,7 +9153,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F270" s="11" t="str">
-        <x:v>毛加的对位优势来自其核心特点——持续火力和近中距离压迫很强，适合正面对拼大体型目标；而布丽吉塔的打法核心是——专长是保护后排、反突进。毛加应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵布丽吉塔时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G270" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9182,7 +9182,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F271" s="11" t="str">
-        <x:v>毛加的对位优势来自其核心特点——持续火力和近中距离压迫很强，适合正面对拼大体型目标；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。毛加应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>对阵卢西奥时，应优先卡住其进场或输出角度；等关键防御、控制或位移进入冷却后再向前压，避免把资源全部耗在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G271" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9385,7 +9385,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F278" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而艾什的打法核心是——中远距离压制优秀，怕强突脸。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给艾什真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给艾什真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G278" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9414,7 +9414,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F279" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而艾什的打法核心是——中远距离压制优秀，怕强突脸。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给艾什真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给艾什真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G279" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9443,7 +9443,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F280" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而艾什的打法核心是——中远距离压制优秀，怕强突脸。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给艾什真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给艾什真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G280" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9733,7 +9733,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F290" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。西格玛应把自己的坦克资源用于占住堡垒最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住堡垒最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G290" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9762,7 +9762,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F291" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。D.Va应把自己的坦克资源用于占住堡垒最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住堡垒最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G291" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9791,7 +9791,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F292" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。奥丽莎应把自己的坦克资源用于占住堡垒最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住堡垒最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G292" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9820,7 +9820,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F293" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。源氏需要利用自身伤害窗口持续逼堡垒交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼堡垒交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G293" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9907,7 +9907,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F296" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G296" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9936,7 +9936,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F297" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G297" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9965,7 +9965,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F298" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G298" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -9994,7 +9994,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F299" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而温斯顿的打法核心是——主要针对脆皮后排和高台。堡垒需要利用自身伤害窗口持续逼温斯顿交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵温斯顿时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G299" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10023,7 +10023,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F300" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而莱因哈特的打法核心是——强依赖近距离与地图拐角。堡垒需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G300" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10052,7 +10052,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F301" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而路霸的打法核心是——钩中关键目标能快速形成击杀。堡垒需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G301" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10081,7 +10081,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F302" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而美的打法核心是——擅长分割阵型和减速近战目标。堡垒需要利用自身伤害窗口持续逼美交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵美时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G302" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10110,7 +10110,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F303" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。堡垒需要利用自身伤害窗口持续逼死神交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵死神时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G303" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10139,7 +10139,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F304" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。堡垒需要利用自身伤害窗口持续逼托比昂交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵托比昂时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G304" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10168,7 +10168,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F305" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。堡垒需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G305" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10197,7 +10197,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F306" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。堡垒需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G306" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10226,7 +10226,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F307" s="11" t="str">
-        <x:v>堡垒的对位优势来自其核心特点——爆发火力高，但体型大、技能窗口明显；而布丽吉塔的打法核心是——专长是保护后排、反突进。堡垒需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G307" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10255,7 +10255,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F308" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。西格玛应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G308" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10284,7 +10284,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F309" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。D.Va应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G309" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10313,7 +10313,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F310" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。奥丽莎应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住卡西迪最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G310" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10429,7 +10429,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F314" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G314" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10458,7 +10458,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F315" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G315" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10487,7 +10487,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F316" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G316" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10690,7 +10690,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F323" s="11" t="str">
-        <x:v>卡西迪的对位优势来自其核心特点——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。卡西迪需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵卢西奥时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G323" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10719,7 +10719,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F324" s="11" t="str">
-        <x:v>卡西迪的对位优势来自其核心特点——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。卡西迪需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G324" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10748,7 +10748,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F325" s="11" t="str">
-        <x:v>卡西迪的对位优势来自其核心特点——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。卡西迪需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵天使时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G325" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10777,7 +10777,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F326" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而源氏的打法核心是——适合切脆皮和收割残血。破坏球应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G326" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10806,7 +10806,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F327" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而源氏的打法核心是——适合切脆皮和收割残血。温斯顿应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G327" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10835,7 +10835,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F328" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而源氏的打法核心是——适合切脆皮和收割残血。查莉娅应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>查莉娅应把自己的坦克资源用于占住源氏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G328" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10864,7 +10864,7 @@
         <x:v>秩序之光</x:v>
       </x:c>
       <x:c r="F329" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而源氏的打法核心是——适合切脆皮和收割残血。秩序之光需要利用自身伤害窗口持续逼源氏交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>秩序之光需要利用自身伤害窗口持续逼源氏交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G329" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -10951,7 +10951,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F332" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而源氏的打法核心是——适合切脆皮和收割残血。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给源氏真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给源氏真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G332" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11009,7 +11009,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F334" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而源氏的打法核心是——适合切脆皮和收割残血。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给源氏真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给源氏真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G334" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11038,7 +11038,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F335" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。源氏需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵西格玛时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G335" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11067,7 +11067,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F336" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而路霸的打法核心是——钩中关键目标能快速形成击杀。源氏需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G336" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11096,7 +11096,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F337" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。源氏需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G337" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11125,7 +11125,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F338" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。源氏需要利用自身伤害窗口持续逼堡垒交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵堡垒时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G338" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11212,7 +11212,7 @@
         <x:v>瑞稀</x:v>
       </x:c>
       <x:c r="F341" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。源氏需要利用自身伤害窗口持续逼瑞稀交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵瑞稀时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G341" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11241,7 +11241,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F342" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。源氏需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G342" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11270,7 +11270,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F343" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。源氏需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G343" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11299,7 +11299,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F344" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而半藏的打法核心是——有高爆发和探测能力，但被贴脸后容错下降。查莉娅应把自己的坦克资源用于占住半藏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>查莉娅应把自己的坦克资源用于占住半藏最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G344" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11473,7 +11473,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F350" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而半藏的打法核心是——有高爆发和探测能力，但被贴脸后容错下降。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给半藏真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给半藏真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G350" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11502,7 +11502,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F351" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而半藏的打法核心是——有高爆发和探测能力，但被贴脸后容错下降。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给半藏真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给半藏真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G351" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11531,7 +11531,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F352" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而半藏的打法核心是——有高爆发和探测能力，但被贴脸后容错下降。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给半藏真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给半藏真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G352" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11821,7 +11821,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F362" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。D.Va应把自己的坦克资源用于占住狂鼠最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住狂鼠最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G362" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11850,7 +11850,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F363" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。温斯顿应把自己的坦克资源用于占住狂鼠最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住狂鼠最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G363" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11879,7 +11879,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F364" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。西格玛应把自己的坦克资源用于占住狂鼠最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住狂鼠最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G364" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -11995,7 +11995,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F368" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给狂鼠真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给狂鼠真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G368" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12024,7 +12024,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F369" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给狂鼠真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给狂鼠真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G369" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12053,7 +12053,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F370" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给狂鼠真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给狂鼠真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G370" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12082,7 +12082,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F371" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而莱因哈特的打法核心是——强依赖近距离与地图拐角。狂鼠需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G371" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12111,7 +12111,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F372" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而奥丽莎的打法核心是——强在正面抗压和打断。狂鼠需要利用自身伤害窗口持续逼奥丽莎交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵奥丽莎时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G372" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12140,7 +12140,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F373" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而路霸的打法核心是——钩中关键目标能快速形成击杀。狂鼠需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G373" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12169,7 +12169,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F374" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而猎空的打法核心是——靠持续骚扰和资源差取胜。狂鼠需要利用自身伤害窗口持续逼猎空交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵猎空时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G374" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12198,7 +12198,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F375" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而美的打法核心是——擅长分割阵型和减速近战目标。狂鼠需要利用自身伤害窗口持续逼美交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵美时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G375" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12227,7 +12227,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F376" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。狂鼠需要利用自身伤害窗口持续逼托比昂交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵托比昂时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G376" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12256,7 +12256,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F377" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而布丽吉塔的打法核心是——专长是保护后排、反突进。狂鼠需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G377" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12285,7 +12285,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F378" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。狂鼠需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G378" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12314,7 +12314,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F379" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。狂鼠需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G379" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12343,7 +12343,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F380" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而美的打法核心是——擅长分割阵型和减速近战目标。D.Va应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G380" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12372,7 +12372,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F381" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而美的打法核心是——擅长分割阵型和减速近战目标。西格玛应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G381" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12401,7 +12401,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F382" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而美的打法核心是——擅长分割阵型和减速近战目标。奥丽莎应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住美最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G382" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12546,7 +12546,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F387" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而美的打法核心是——擅长分割阵型和减速近战目标。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G387" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12575,7 +12575,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F388" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而美的打法核心是——擅长分割阵型和减速近战目标。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G388" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12633,7 +12633,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F390" s="11" t="str">
-        <x:v>美的对位优势来自其核心特点——擅长分割阵型和减速近战目标；而莱因哈特的打法核心是——强依赖近距离与地图拐角。美需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G390" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12720,7 +12720,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F393" s="11" t="str">
-        <x:v>美的对位优势来自其核心特点——擅长分割阵型和减速近战目标；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。美需要利用自身伤害窗口持续逼死神交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵死神时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G393" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12778,7 +12778,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F395" s="11" t="str">
-        <x:v>美的对位优势来自其核心特点——擅长分割阵型和减速近战目标；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。美需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵卢西奥时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G395" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12807,7 +12807,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F396" s="11" t="str">
-        <x:v>美的对位优势来自其核心特点——擅长分割阵型和减速近战目标；而布丽吉塔的打法核心是——专长是保护后排、反突进。美需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G396" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12836,7 +12836,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F397" s="11" t="str">
-        <x:v>美的对位优势来自其核心特点——擅长分割阵型和减速近战目标；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。美需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G397" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12865,7 +12865,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F398" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而法老之鹰的打法核心是——利用高空角度绕盾输出。D.Va应把自己的坦克资源用于占住法老之鹰最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住法老之鹰最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G398" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12894,7 +12894,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F399" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而法老之鹰的打法核心是——利用高空角度绕盾输出。温斯顿应把自己的坦克资源用于占住法老之鹰最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住法老之鹰最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G399" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -12923,7 +12923,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F400" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而法老之鹰的打法核心是——利用高空角度绕盾输出。西格玛应把自己的坦克资源用于占住法老之鹰最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住法老之鹰最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G400" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13039,7 +13039,7 @@
         <x:v>朱诺</x:v>
       </x:c>
       <x:c r="F404" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而法老之鹰的打法核心是——利用高空角度绕盾输出。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给法老之鹰真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给法老之鹰真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G404" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13097,7 +13097,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F406" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而法老之鹰的打法核心是——利用高空角度绕盾输出。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给法老之鹰真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给法老之鹰真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G406" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13126,7 +13126,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F407" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而莱因哈特的打法核心是——强依赖近距离与地图拐角。法老之鹰需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G407" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13155,7 +13155,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F408" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。法老之鹰需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G408" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13184,7 +13184,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F409" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而路霸的打法核心是——钩中关键目标能快速形成击杀。法老之鹰需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G409" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13300,7 +13300,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F413" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。法老之鹰需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵卢西奥时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G413" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13329,7 +13329,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F414" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而布丽吉塔的打法核心是——专长是保护后排、反突进。法老之鹰需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G414" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13358,7 +13358,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F415" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。法老之鹰需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G415" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13387,7 +13387,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F416" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。D.Va应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G416" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13416,7 +13416,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F417" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。西格玛应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G417" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13445,7 +13445,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F418" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。奥丽莎应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住死神最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G418" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13561,7 +13561,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F422" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G422" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13590,7 +13590,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F423" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G423" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13619,7 +13619,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F424" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G424" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13648,7 +13648,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F425" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而温斯顿的打法核心是——主要针对脆皮后排和高台。死神需要利用自身伤害窗口持续逼温斯顿交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵温斯顿时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G425" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13677,7 +13677,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F426" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而路霸的打法核心是——钩中关键目标能快速形成击杀。死神需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G426" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13706,7 +13706,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F427" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而莱因哈特的打法核心是——强依赖近距离与地图拐角。死神需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G427" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13735,7 +13735,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F428" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而美的打法核心是——擅长分割阵型和减速近战目标。死神需要利用自身伤害窗口持续逼美交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵美时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G428" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13764,7 +13764,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F429" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。死神需要利用自身伤害窗口持续逼托比昂交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵托比昂时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G429" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13793,7 +13793,7 @@
         <x:v>狂鼠</x:v>
       </x:c>
       <x:c r="F430" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。死神需要利用自身伤害窗口持续逼狂鼠交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵狂鼠时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G430" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13822,7 +13822,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F431" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。死神需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G431" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13851,7 +13851,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F432" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而布丽吉塔的打法核心是——专长是保护后排、反突进。死神需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G432" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13880,7 +13880,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F433" s="11" t="str">
-        <x:v>死神的对位优势来自其核心特点——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。死神需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵卢西奥时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G433" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13909,7 +13909,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F434" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而黑影的打法核心是——适合破坏高机动英雄节奏。D.Va应把自己的坦克资源用于占住黑影最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住黑影最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G434" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13938,7 +13938,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F435" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而黑影的打法核心是——适合破坏高机动英雄节奏。奥丽莎应把自己的坦克资源用于占住黑影最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住黑影最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G435" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -13967,7 +13967,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F436" s="11" t="str">
-        <x:v>查莉娅的对位优势来自其核心特点——对依赖吸收弹道的坦克很强；而黑影的打法核心是——适合破坏高机动英雄节奏。查莉娅应把自己的坦克资源用于占住黑影最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>查莉娅应把自己的坦克资源用于占住黑影最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G436" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14141,7 +14141,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F442" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而黑影的打法核心是——适合破坏高机动英雄节奏。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑影真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑影真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G442" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14170,7 +14170,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F443" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而破坏球的打法核心是——靠骚扰和位移制造空间。黑影需要利用自身伤害窗口持续逼破坏球交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵破坏球时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G443" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14199,7 +14199,7 @@
         <x:v>末日铁拳</x:v>
       </x:c>
       <x:c r="F444" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而末日铁拳的打法核心是——核心是机动性与进出场节奏。黑影需要利用自身伤害窗口持续逼末日铁拳交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵末日铁拳时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G444" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14228,7 +14228,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F445" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而温斯顿的打法核心是——主要针对脆皮后排和高台。黑影需要利用自身伤害窗口持续逼温斯顿交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵温斯顿时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G445" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14257,7 +14257,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F446" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而源氏的打法核心是——适合切脆皮和收割残血。黑影需要利用自身伤害窗口持续逼源氏交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵源氏时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G446" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14286,7 +14286,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F447" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而猎空的打法核心是——靠持续骚扰和资源差取胜。黑影需要利用自身伤害窗口持续逼猎空交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵猎空时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G447" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14344,7 +14344,7 @@
         <x:v>朱诺</x:v>
       </x:c>
       <x:c r="F449" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。黑影需要利用自身伤害窗口持续逼朱诺交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵朱诺时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G449" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14373,7 +14373,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F450" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。黑影需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G450" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14402,7 +14402,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F451" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。黑影需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G451" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14431,7 +14431,7 @@
         <x:v>末日铁拳</x:v>
       </x:c>
       <x:c r="F452" s="11" t="str">
-        <x:v>末日铁拳的对位优势来自其核心特点——核心是机动性与进出场节奏；而士兵：76的打法核心是——泛用性高，对空稳定。末日铁拳应把自己的坦克资源用于占住士兵：76最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>末日铁拳应把自己的坦克资源用于占住士兵：76最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G452" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14460,7 +14460,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F453" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而士兵：76的打法核心是——泛用性高，对空稳定。温斯顿应把自己的坦克资源用于占住士兵：76最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住士兵：76最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G453" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14489,7 +14489,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F454" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而士兵：76的打法核心是——泛用性高，对空稳定。D.Va应把自己的坦克资源用于占住士兵：76最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住士兵：76最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G454" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14576,7 +14576,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F457" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而士兵：76的打法核心是——泛用性高，对空稳定。源氏需要利用自身伤害窗口持续逼士兵：76交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼士兵：76交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G457" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14605,7 +14605,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F458" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而士兵：76的打法核心是——泛用性高，对空稳定。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给士兵：76真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给士兵：76真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G458" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14634,7 +14634,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F459" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而士兵：76的打法核心是——泛用性高，对空稳定。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给士兵：76真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给士兵：76真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G459" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14663,7 +14663,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F460" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而士兵：76的打法核心是——泛用性高，对空稳定。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给士兵：76真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给士兵：76真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G460" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14692,7 +14692,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F461" s="11" t="str">
-        <x:v>士兵：76的对位优势来自其核心特点——泛用性高，对空稳定；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。士兵：76需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G461" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14721,7 +14721,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F462" s="11" t="str">
-        <x:v>士兵：76的对位优势来自其核心特点——泛用性高，对空稳定；而路霸的打法核心是——钩中关键目标能快速形成击杀。士兵：76需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G462" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14750,7 +14750,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F463" s="11" t="str">
-        <x:v>士兵：76的对位优势来自其核心特点——泛用性高，对空稳定；而莱因哈特的打法核心是——强依赖近距离与地图拐角。士兵：76需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G463" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14837,7 +14837,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F466" s="11" t="str">
-        <x:v>士兵：76的对位优势来自其核心特点——泛用性高，对空稳定；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。士兵：76需要利用自身伤害窗口持续逼死神交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵死神时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G466" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14866,7 +14866,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F467" s="11" t="str">
-        <x:v>士兵：76的对位优势来自其核心特点——泛用性高，对空稳定；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。士兵：76需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G467" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14895,7 +14895,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F468" s="11" t="str">
-        <x:v>士兵：76的对位优势来自其核心特点——泛用性高，对空稳定；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。士兵：76需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G468" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14924,7 +14924,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F469" s="11" t="str">
-        <x:v>士兵：76的对位优势来自其核心特点——泛用性高，对空稳定；而布丽吉塔的打法核心是——专长是保护后排、反突进。士兵：76需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G469" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14953,7 +14953,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F470" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。温斯顿应把自己的坦克资源用于占住索杰恩最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住索杰恩最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G470" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -14982,7 +14982,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F471" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。D.Va应把自己的坦克资源用于占住索杰恩最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住索杰恩最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G471" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15011,7 +15011,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F472" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。破坏球应把自己的坦克资源用于占住索杰恩最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住索杰恩最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G472" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15069,7 +15069,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F474" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。源氏需要利用自身伤害窗口持续逼索杰恩交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼索杰恩交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G474" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15098,7 +15098,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F475" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。猎空需要利用自身伤害窗口持续逼索杰恩交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼索杰恩交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G475" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15127,7 +15127,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F476" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给索杰恩真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给索杰恩真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G476" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15156,7 +15156,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F477" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给索杰恩真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给索杰恩真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G477" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15185,7 +15185,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F478" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给索杰恩真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给索杰恩真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G478" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15214,7 +15214,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F479" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而路霸的打法核心是——钩中关键目标能快速形成击杀。索杰恩需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G479" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15243,7 +15243,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F480" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而奥丽莎的打法核心是——强在正面抗压和打断。索杰恩需要利用自身伤害窗口持续逼奥丽莎交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵奥丽莎时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G480" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15272,7 +15272,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F481" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而莱因哈特的打法核心是——强依赖近距离与地图拐角。索杰恩需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G481" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15301,7 +15301,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F482" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而法老之鹰的打法核心是——利用高空角度绕盾输出。索杰恩需要利用自身伤害窗口持续逼法老之鹰交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵法老之鹰时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G482" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15330,7 +15330,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F483" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。索杰恩需要利用自身伤害窗口持续逼死神交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵死神时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G483" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15359,7 +15359,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F484" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。索杰恩需要利用自身伤害窗口持续逼托比昂交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵托比昂时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G484" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15388,7 +15388,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F485" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。索杰恩需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G485" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15417,7 +15417,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F486" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。索杰恩需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G486" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15446,7 +15446,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F487" s="11" t="str">
-        <x:v>索杰恩的对位优势来自其核心特点——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。索杰恩需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G487" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15475,7 +15475,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F488" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而秩序之光的打法核心是——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。温斯顿应把自己的坦克资源用于占住秩序之光最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住秩序之光最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G488" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15504,7 +15504,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F489" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而秩序之光的打法核心是——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。D.Va应把自己的坦克资源用于占住秩序之光最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住秩序之光最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G489" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15533,7 +15533,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F490" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而秩序之光的打法核心是——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。破坏球应把自己的坦克资源用于占住秩序之光最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住秩序之光最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G490" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15620,7 +15620,7 @@
         <x:v>狂鼠</x:v>
       </x:c>
       <x:c r="F493" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而秩序之光的打法核心是——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。狂鼠需要利用自身伤害窗口持续逼秩序之光交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>狂鼠需要利用自身伤害窗口持续逼秩序之光交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G493" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15649,7 +15649,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F494" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而秩序之光的打法核心是——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给秩序之光真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给秩序之光真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G494" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15678,7 +15678,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F495" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而秩序之光的打法核心是——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给秩序之光真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给秩序之光真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G495" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15707,7 +15707,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F496" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而秩序之光的打法核心是——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给秩序之光真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给秩序之光真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G496" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15736,7 +15736,7 @@
         <x:v>查莉娅</x:v>
       </x:c>
       <x:c r="F497" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而查莉娅的打法核心是——对依赖吸收弹道的坦克很强。秩序之光需要利用自身伤害窗口持续逼查莉娅交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵查莉娅时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G497" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15794,7 +15794,7 @@
         <x:v>毛加</x:v>
       </x:c>
       <x:c r="F499" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而毛加的打法核心是——持续火力和近中距离压迫很强，适合正面对拼大体型目标。秩序之光需要利用自身伤害窗口持续逼毛加交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵毛加时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G499" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15823,7 +15823,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F500" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而源氏的打法核心是——适合切脆皮和收割残血。秩序之光需要利用自身伤害窗口持续逼源氏交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵源氏时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G500" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15852,7 +15852,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F501" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而美的打法核心是——擅长分割阵型和减速近战目标。秩序之光需要利用自身伤害窗口持续逼美交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵美时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G501" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15881,7 +15881,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F502" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。秩序之光需要利用自身伤害窗口持续逼死神交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵死神时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G502" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15910,7 +15910,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F503" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而布丽吉塔的打法核心是——专长是保护后排、反突进。秩序之光需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G503" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15939,7 +15939,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F504" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。秩序之光需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G504" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15968,7 +15968,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F505" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。秩序之光需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵卢西奥时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G505" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -15997,7 +15997,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F506" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。西格玛应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G506" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16026,7 +16026,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F507" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。D.Va应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G507" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16055,7 +16055,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F508" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。奥丽莎应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住托比昂最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G508" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16084,7 +16084,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F509" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。法老之鹰需要利用自身伤害窗口持续逼托比昂交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼托比昂交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G509" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16171,7 +16171,7 @@
         <x:v>伊拉锐</x:v>
       </x:c>
       <x:c r="F512" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G512" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16200,7 +16200,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F513" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G513" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16229,7 +16229,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F514" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G514" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16432,7 +16432,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F521" s="11" t="str">
-        <x:v>托比昂的对位优势来自其核心特点——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。托比昂需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵卢西奥时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G521" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16461,7 +16461,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F522" s="11" t="str">
-        <x:v>托比昂的对位优势来自其核心特点——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。托比昂需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G522" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16490,7 +16490,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F523" s="11" t="str">
-        <x:v>托比昂的对位优势来自其核心特点——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。托比昂需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵天使时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G523" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16519,7 +16519,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F524" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而猎空的打法核心是——靠持续骚扰和资源差取胜。温斯顿应把自己的坦克资源用于占住猎空最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住猎空最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G524" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16548,7 +16548,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F525" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而猎空的打法核心是——靠持续骚扰和资源差取胜。D.Va应把自己的坦克资源用于占住猎空最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住猎空最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G525" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16577,7 +16577,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F526" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而猎空的打法核心是——靠持续骚扰和资源差取胜。破坏球应把自己的坦克资源用于占住猎空最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住猎空最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G526" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16606,7 +16606,7 @@
         <x:v>狂鼠</x:v>
       </x:c>
       <x:c r="F527" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而猎空的打法核心是——靠持续骚扰和资源差取胜。狂鼠需要利用自身伤害窗口持续逼猎空交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>狂鼠需要利用自身伤害窗口持续逼猎空交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G527" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16722,7 +16722,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F531" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而猎空的打法核心是——靠持续骚扰和资源差取胜。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给猎空真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给猎空真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G531" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16751,7 +16751,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F532" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而猎空的打法核心是——靠持续骚扰和资源差取胜。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给猎空真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给猎空真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G532" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16780,7 +16780,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F533" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。猎空需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵西格玛时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G533" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16809,7 +16809,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F534" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而路霸的打法核心是——钩中关键目标能快速形成击杀。猎空需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G534" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16838,7 +16838,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F535" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。猎空需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G535" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16954,7 +16954,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F539" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。猎空需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G539" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -16983,7 +16983,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F540" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。猎空需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G540" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17012,7 +17012,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F541" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。猎空需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵天使时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G541" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17215,7 +17215,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F548" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而黑百合的打法核心是——远距离威慑强，最怕高机动强突。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑百合真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑百合真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G548" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17244,7 +17244,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F549" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而黑百合的打法核心是——远距离威慑强，最怕高机动强突。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑百合真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑百合真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G549" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17273,7 +17273,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F550" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而黑百合的打法核心是——远距离威慑强，最怕高机动强突。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑百合真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑百合真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G550" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17563,7 +17563,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F560" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而回声的打法核心是——机动性与爆发强，但空中轨迹容易被长枪锁定。D.Va应把自己的坦克资源用于占住回声最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住回声最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G560" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17592,7 +17592,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F561" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而回声的打法核心是——机动性与爆发强，但空中轨迹容易被长枪锁定。温斯顿应把自己的坦克资源用于占住回声最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住回声最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G561" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17621,7 +17621,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F562" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而回声的打法核心是——机动性与爆发强，但空中轨迹容易被长枪锁定。西格玛应把自己的坦克资源用于占住回声最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住回声最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G562" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17650,7 +17650,7 @@
         <x:v>死怨</x:v>
       </x:c>
       <x:c r="F563" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而回声的打法核心是——机动性与爆发强，但空中轨迹容易被长枪锁定。死怨需要利用自身伤害窗口持续逼回声交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>死怨需要利用自身伤害窗口持续逼回声交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G563" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17766,7 +17766,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F567" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而回声的打法核心是——机动性与爆发强，但空中轨迹容易被长枪锁定。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给回声真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给回声真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G567" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17795,7 +17795,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F568" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而回声的打法核心是——机动性与爆发强，但空中轨迹容易被长枪锁定。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给回声真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给回声真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G568" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17824,7 +17824,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F569" s="11" t="str">
-        <x:v>回声的对位优势来自其核心特点——机动性与爆发强，但空中轨迹容易被长枪锁定；而莱因哈特的打法核心是——强依赖近距离与地图拐角。回声需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G569" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17853,7 +17853,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F570" s="11" t="str">
-        <x:v>回声的对位优势来自其核心特点——机动性与爆发强，但空中轨迹容易被长枪锁定；而路霸的打法核心是——钩中关键目标能快速形成击杀。回声需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G570" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17882,7 +17882,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F571" s="11" t="str">
-        <x:v>回声的对位优势来自其核心特点——机动性与爆发强，但空中轨迹容易被长枪锁定；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。回声需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G571" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -17998,7 +17998,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F575" s="11" t="str">
-        <x:v>回声的对位优势来自其核心特点——机动性与爆发强，但空中轨迹容易被长枪锁定；而布丽吉塔的打法核心是——专长是保护后排、反突进。回声需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G575" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18027,7 +18027,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F576" s="11" t="str">
-        <x:v>回声的对位优势来自其核心特点——机动性与爆发强，但空中轨迹容易被长枪锁定；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。回声需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G576" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18056,7 +18056,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F577" s="11" t="str">
-        <x:v>回声的对位优势来自其核心特点——机动性与爆发强，但空中轨迹容易被长枪锁定；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。回声需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G577" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18085,7 +18085,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F578" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而安燃的打法核心是——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力。温斯顿应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G578" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18114,7 +18114,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F579" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而安燃的打法核心是——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力。D.Va应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G579" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18143,7 +18143,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F580" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而安燃的打法核心是——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力。奥丽莎应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住安燃最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G580" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18317,7 +18317,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F586" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而安燃的打法核心是——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安燃真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安燃真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G586" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18346,7 +18346,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F587" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。安燃需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵西格玛时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G587" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18375,7 +18375,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F588" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而路霸的打法核心是——钩中关键目标能快速形成击杀。安燃需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G588" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18404,7 +18404,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F589" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。安燃需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G589" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18520,7 +18520,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F593" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。安燃需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G593" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18549,7 +18549,7 @@
         <x:v>伊拉锐</x:v>
       </x:c>
       <x:c r="F594" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。安燃需要利用自身伤害窗口持续逼伊拉锐交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵伊拉锐时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G594" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18578,7 +18578,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F595" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。安燃需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G595" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18607,7 +18607,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F596" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。温斯顿应把自己的坦克资源用于占住埃姆雷最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住埃姆雷最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G596" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18636,7 +18636,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F597" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。D.Va应把自己的坦克资源用于占住埃姆雷最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住埃姆雷最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G597" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18665,7 +18665,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F598" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。破坏球应把自己的坦克资源用于占住埃姆雷最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住埃姆雷最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G598" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18694,7 +18694,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F599" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。源氏需要利用自身伤害窗口持续逼埃姆雷交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼埃姆雷交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G599" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18723,7 +18723,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F600" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。猎空需要利用自身伤害窗口持续逼埃姆雷交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼埃姆雷交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G600" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18781,7 +18781,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F602" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给埃姆雷真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给埃姆雷真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G602" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18810,7 +18810,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F603" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给埃姆雷真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给埃姆雷真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G603" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18839,7 +18839,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F604" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给埃姆雷真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给埃姆雷真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G604" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18868,7 +18868,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F605" s="11" t="str">
-        <x:v>埃姆雷的对位优势来自其核心特点——中距离爆发型输出，步枪和手雷适合持续压血线；而路霸的打法核心是——钩中关键目标能快速形成击杀。埃姆雷需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G605" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18897,7 +18897,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F606" s="11" t="str">
-        <x:v>埃姆雷的对位优势来自其核心特点——中距离爆发型输出，步枪和手雷适合持续压血线；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。埃姆雷需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G606" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -18926,7 +18926,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F607" s="11" t="str">
-        <x:v>埃姆雷的对位优势来自其核心特点——中距离爆发型输出，步枪和手雷适合持续压血线；而莱因哈特的打法核心是——强依赖近距离与地图拐角。埃姆雷需要利用自身伤害窗口持续逼莱因哈特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莱因哈特时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G607" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19013,7 +19013,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F610" s="11" t="str">
-        <x:v>埃姆雷的对位优势来自其核心特点——中距离爆发型输出，步枪和手雷适合持续压血线；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。埃姆雷需要利用自身伤害窗口持续逼死神交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵死神时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G610" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19042,7 +19042,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F611" s="11" t="str">
-        <x:v>埃姆雷的对位优势来自其核心特点——中距离爆发型输出，步枪和手雷适合持续压血线；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。埃姆雷需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵莫伊拉时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G611" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19071,7 +19071,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F612" s="11" t="str">
-        <x:v>埃姆雷的对位优势来自其核心特点——中距离爆发型输出，步枪和手雷适合持续压血线；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。埃姆雷需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G612" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19100,7 +19100,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F613" s="11" t="str">
-        <x:v>埃姆雷的对位优势来自其核心特点——中距离爆发型输出，步枪和手雷适合持续压血线；而布丽吉塔的打法核心是——专长是保护后排、反突进。埃姆雷需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵布丽吉塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G613" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19303,7 +19303,7 @@
         <x:v>伊拉锐</x:v>
       </x:c>
       <x:c r="F620" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而弗蕾娅的打法核心是——高机动远程输出，擅长借助位移寻找射击角度。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给弗蕾娅真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给弗蕾娅真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G620" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19332,7 +19332,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F621" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而弗蕾娅的打法核心是——高机动远程输出，擅长借助位移寻找射击角度。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给弗蕾娅真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给弗蕾娅真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G621" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19361,7 +19361,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F622" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而弗蕾娅的打法核心是——高机动远程输出，擅长借助位移寻找射击角度。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给弗蕾娅真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给弗蕾娅真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G622" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19680,7 +19680,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F633" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而死怨的打法核心是——高机动侧翼输出，通过位移和持续枪火切入后排。温斯顿应把自己的坦克资源用于占住死怨最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住死怨最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G633" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19709,7 +19709,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F634" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而死怨的打法核心是——高机动侧翼输出，通过位移和持续枪火切入后排。奥丽莎应把自己的坦克资源用于占住死怨最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住死怨最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G634" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19854,7 +19854,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F639" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而死怨的打法核心是——高机动侧翼输出，通过位移和持续枪火切入后排。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死怨真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死怨真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G639" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19883,7 +19883,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F640" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而死怨的打法核心是——高机动侧翼输出，通过位移和持续枪火切入后排。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死怨真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死怨真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G640" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19912,7 +19912,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F641" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。死怨需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵西格玛时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G641" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19941,7 +19941,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F642" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而路霸的打法核心是——钩中关键目标能快速形成击杀。死怨需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G642" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19970,7 +19970,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F643" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。死怨需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G643" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -19999,7 +19999,7 @@
         <x:v>回声</x:v>
       </x:c>
       <x:c r="F644" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而回声的打法核心是——机动性与爆发强，但空中轨迹容易被长枪锁定。死怨需要利用自身伤害窗口持续逼回声交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵回声时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G644" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20086,7 +20086,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F647" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。死怨需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G647" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20115,7 +20115,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F648" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。死怨需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G648" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20144,7 +20144,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F649" s="11" t="str">
-        <x:v>死怨的对位优势来自其核心特点——高机动侧翼输出，通过位移和持续枪火切入后排；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。死怨需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G649" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20347,7 +20347,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F656" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而西拉的打法核心是——偏精准追踪和中距离持续输出，能够稳定惩罚暴露目标。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西拉真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G656" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20376,7 +20376,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F657" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而西拉的打法核心是——偏精准追踪和中距离持续输出，能够稳定惩罚暴露目标。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西拉真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G657" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20405,7 +20405,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F658" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而西拉的打法核心是——偏精准追踪和中距离持续输出，能够稳定惩罚暴露目标。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西拉真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G658" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20695,7 +20695,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F668" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而斩仇的打法核心是——近战侧翼输出，依靠冲刺和格挡接近目标。D.Va应把自己的坦克资源用于占住斩仇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住斩仇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G668" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20724,7 +20724,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F669" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而斩仇的打法核心是——近战侧翼输出，依靠冲刺和格挡接近目标。温斯顿应把自己的坦克资源用于占住斩仇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住斩仇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G669" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20753,7 +20753,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F670" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而斩仇的打法核心是——近战侧翼输出，依靠冲刺和格挡接近目标。奥丽莎应把自己的坦克资源用于占住斩仇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住斩仇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G670" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20840,7 +20840,7 @@
         <x:v>艾什</x:v>
       </x:c>
       <x:c r="F673" s="11" t="str">
-        <x:v>艾什的对位优势来自其核心特点——中远距离压制优秀，怕强突脸；而斩仇的打法核心是——近战侧翼输出，依靠冲刺和格挡接近目标。艾什需要利用自身伤害窗口持续逼斩仇交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>艾什需要利用自身伤害窗口持续逼斩仇交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G673" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20898,7 +20898,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F675" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而斩仇的打法核心是——近战侧翼输出，依靠冲刺和格挡接近目标。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给斩仇真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给斩仇真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G675" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20927,7 +20927,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F676" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而斩仇的打法核心是——近战侧翼输出，依靠冲刺和格挡接近目标。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给斩仇真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给斩仇真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G676" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20956,7 +20956,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F677" s="11" t="str">
-        <x:v>斩仇的对位优势来自其核心特点——近战侧翼输出，依靠冲刺和格挡接近目标；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。斩仇需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵西格玛时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G677" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -20985,7 +20985,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F678" s="11" t="str">
-        <x:v>斩仇的对位优势来自其核心特点——近战侧翼输出，依靠冲刺和格挡接近目标；而路霸的打法核心是——钩中关键目标能快速形成击杀。斩仇需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G678" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21014,7 +21014,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F679" s="11" t="str">
-        <x:v>斩仇的对位优势来自其核心特点——近战侧翼输出，依靠冲刺和格挡接近目标；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。斩仇需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G679" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21130,7 +21130,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F683" s="11" t="str">
-        <x:v>斩仇的对位优势来自其核心特点——近战侧翼输出，依靠冲刺和格挡接近目标；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。斩仇需要利用自身伤害窗口持续逼雾子交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵雾子时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G683" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21159,7 +21159,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F684" s="11" t="str">
-        <x:v>斩仇的对位优势来自其核心特点——近战侧翼输出，依靠冲刺和格挡接近目标；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。斩仇需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G684" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21188,7 +21188,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F685" s="11" t="str">
-        <x:v>斩仇的对位优势来自其核心特点——近战侧翼输出，依靠冲刺和格挡接近目标；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。斩仇需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G685" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21217,7 +21217,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F686" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而探奇的打法核心是——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。D.Va应把自己的坦克资源用于占住探奇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住探奇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G686" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21246,7 +21246,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F687" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而探奇的打法核心是——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。温斯顿应把自己的坦克资源用于占住探奇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住探奇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G687" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21275,7 +21275,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F688" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而探奇的打法核心是——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。奥丽莎应把自己的坦克资源用于占住探奇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住探奇最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G688" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21333,7 +21333,7 @@
         <x:v>艾什</x:v>
       </x:c>
       <x:c r="F690" s="11" t="str">
-        <x:v>艾什的对位优势来自其核心特点——中远距离压制优秀，怕强突脸；而探奇的打法核心是——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。艾什需要利用自身伤害窗口持续逼探奇交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>艾什需要利用自身伤害窗口持续逼探奇交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G690" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21420,7 +21420,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F693" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而探奇的打法核心是——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给探奇真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给探奇真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G693" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21449,7 +21449,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F694" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而探奇的打法核心是——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给探奇真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给探奇真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G694" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21478,7 +21478,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F695" s="11" t="str">
-        <x:v>探奇的对位优势来自其核心特点——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。探奇需要利用自身伤害窗口持续逼西格玛交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵西格玛时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G695" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21507,7 +21507,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F696" s="11" t="str">
-        <x:v>探奇的对位优势来自其核心特点——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排；而路霸的打法核心是——钩中关键目标能快速形成击杀。探奇需要利用自身伤害窗口持续逼路霸交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵路霸时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G696" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21536,7 +21536,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F697" s="11" t="str">
-        <x:v>探奇的对位优势来自其核心特点——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。探奇需要利用自身伤害窗口持续逼渣客女王交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵渣客女王时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G697" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21652,7 +21652,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F701" s="11" t="str">
-        <x:v>探奇的对位优势来自其核心特点——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。探奇需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵禅雅塔时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G701" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21681,7 +21681,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F702" s="11" t="str">
-        <x:v>探奇的对位优势来自其核心特点——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。探奇需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵安娜时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G702" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21710,7 +21710,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F703" s="11" t="str">
-        <x:v>探奇的对位优势来自其核心特点——钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。探奇需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>对阵生命之梭时，先用持续压力逼出防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G703" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21739,7 +21739,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F704" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。温斯顿应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G704" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21768,7 +21768,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F705" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。D.Va应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G705" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21797,7 +21797,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F706" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。破坏球应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住安娜最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G706" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21826,7 +21826,7 @@
         <x:v>安燃</x:v>
       </x:c>
       <x:c r="F707" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。安燃需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>安燃需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G707" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21855,7 +21855,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F708" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。源氏需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G708" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21884,7 +21884,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F709" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。猎空需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼安娜交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G709" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21942,7 +21942,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F711" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安娜真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安娜真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G711" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -21971,7 +21971,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F712" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安娜真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安娜真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G712" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22087,7 +22087,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F716" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G716" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22116,7 +22116,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F717" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵堡垒时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G717" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22145,7 +22145,7 @@
         <x:v>卡西迪</x:v>
       </x:c>
       <x:c r="F718" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卡西迪时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G718" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22174,7 +22174,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F719" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G719" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22203,7 +22203,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F720" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G720" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22232,7 +22232,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F721" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵巴蒂斯特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G721" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22261,7 +22261,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F722" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。温斯顿应把自己的坦克资源用于占住巴蒂斯特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住巴蒂斯特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G722" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22290,7 +22290,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F723" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。D.Va应把自己的坦克资源用于占住巴蒂斯特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住巴蒂斯特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G723" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22319,7 +22319,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F724" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。破坏球应把自己的坦克资源用于占住巴蒂斯特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住巴蒂斯特最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G724" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22348,7 +22348,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F725" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。源氏需要利用自身伤害窗口持续逼巴蒂斯特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼巴蒂斯特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G725" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22377,7 +22377,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F726" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。猎空需要利用自身伤害窗口持续逼巴蒂斯特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼巴蒂斯特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G726" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22406,7 +22406,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F727" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。黑影需要利用自身伤害窗口持续逼巴蒂斯特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼巴蒂斯特交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G727" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22435,7 +22435,7 @@
         <x:v>伊拉锐</x:v>
       </x:c>
       <x:c r="F728" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G728" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22464,7 +22464,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F729" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G729" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22493,7 +22493,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F730" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G730" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22522,7 +22522,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F731" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而路霸的打法核心是——钩中关键目标能快速形成击杀。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G731" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22551,7 +22551,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F732" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而奥丽莎的打法核心是——强在正面抗压和打断。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给奥丽莎真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵奥丽莎时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G732" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22580,7 +22580,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F733" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而莱因哈特的打法核心是——强依赖近距离与地图拐角。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G733" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22638,7 +22638,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F735" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G735" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22667,7 +22667,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F736" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵堡垒时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G736" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22696,7 +22696,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F737" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G737" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22725,7 +22725,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F738" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G738" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22754,7 +22754,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F739" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G739" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22783,7 +22783,7 @@
         <x:v>拉玛刹</x:v>
       </x:c>
       <x:c r="F740" s="11" t="str">
-        <x:v>拉玛刹的对位优势来自其核心特点——变身阶段近战压制力高；而布丽吉塔的打法核心是——专长是保护后排、反突进。拉玛刹应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>拉玛刹应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G740" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22812,7 +22812,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F741" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而布丽吉塔的打法核心是——专长是保护后排、反突进。西格玛应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G741" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22841,7 +22841,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F742" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而布丽吉塔的打法核心是——专长是保护后排、反突进。奥丽莎应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住布丽吉塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G742" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22870,7 +22870,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F743" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而布丽吉塔的打法核心是——专长是保护后排、反突进。法老之鹰需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G743" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22928,7 +22928,7 @@
         <x:v>狂鼠</x:v>
       </x:c>
       <x:c r="F745" s="11" t="str">
-        <x:v>狂鼠的对位优势来自其核心特点——狭窄地形强，空中与远距离目标难处理；而布丽吉塔的打法核心是——专长是保护后排、反突进。狂鼠需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>狂鼠需要利用自身伤害窗口持续逼布丽吉塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G745" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22957,7 +22957,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F746" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而布丽吉塔的打法核心是——专长是保护后排、反突进。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G746" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -22986,7 +22986,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F747" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而布丽吉塔的打法核心是——专长是保护后排、反突进。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G747" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23015,7 +23015,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F748" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而布丽吉塔的打法核心是——专长是保护后排、反突进。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G748" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23160,7 +23160,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F753" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G753" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23218,7 +23218,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F755" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G755" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23247,7 +23247,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F756" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G756" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23276,7 +23276,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F757" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵禅雅塔时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G757" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23305,7 +23305,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F758" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。温斯顿应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G758" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23334,7 +23334,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F759" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。D.Va应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G759" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23363,7 +23363,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F760" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。破坏球应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住卢西奥最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G760" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23392,7 +23392,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F761" s="11" t="str">
-        <x:v>法老之鹰的对位优势来自其核心特点——利用高空角度绕盾输出；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。法老之鹰需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>法老之鹰需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G761" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23421,7 +23421,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F762" s="11" t="str">
-        <x:v>托比昂的对位优势来自其核心特点——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。托比昂需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>托比昂需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G762" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23450,7 +23450,7 @@
         <x:v>秩序之光</x:v>
       </x:c>
       <x:c r="F763" s="11" t="str">
-        <x:v>秩序之光的对位优势来自其核心特点——光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。秩序之光需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>秩序之光需要利用自身伤害窗口持续逼卢西奥交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G763" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23479,7 +23479,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F764" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G764" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23508,7 +23508,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F765" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G765" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23537,7 +23537,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F766" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G766" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23566,7 +23566,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F767" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而莱因哈特的打法核心是——强依赖近距离与地图拐角。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G767" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23595,7 +23595,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F768" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵渣客女王时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G768" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23624,7 +23624,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F769" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而路霸的打法核心是——钩中关键目标能快速形成击杀。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G769" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23653,7 +23653,7 @@
         <x:v>黑百合</x:v>
       </x:c>
       <x:c r="F770" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而黑百合的打法核心是——远距离威慑强，最怕高机动强突。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给黑百合真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵黑百合时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G770" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23682,7 +23682,7 @@
         <x:v>半藏</x:v>
       </x:c>
       <x:c r="F771" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而半藏的打法核心是——有高爆发和探测能力，但被贴脸后容错下降。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给半藏真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵半藏时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G771" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23711,7 +23711,7 @@
         <x:v>艾什</x:v>
       </x:c>
       <x:c r="F772" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而艾什的打法核心是——中远距离压制优秀，怕强突脸。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给艾什真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵艾什时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G772" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23740,7 +23740,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F773" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵禅雅塔时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G773" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23769,7 +23769,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F774" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G774" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23798,7 +23798,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F775" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安娜真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵安娜时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G775" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23827,7 +23827,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F776" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。破坏球应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G776" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23856,7 +23856,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F777" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。温斯顿应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住天使最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G777" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23914,7 +23914,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F779" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。猎空需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G779" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23943,7 +23943,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F780" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。源氏需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G780" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -23972,7 +23972,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F781" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。黑影需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼天使交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G781" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24001,7 +24001,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F782" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给天使真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给天使真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G782" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24030,7 +24030,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F783" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给天使真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给天使真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G783" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24059,7 +24059,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F784" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给天使真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给天使真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G784" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24088,7 +24088,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F785" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而西格玛的打法核心是——中远距离资源交换很强，怕被贴脸和多方向切入。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西格玛真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵西格玛时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G785" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24117,7 +24117,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F786" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而路霸的打法核心是——钩中关键目标能快速形成击杀。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G786" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24146,7 +24146,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F787" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而奥丽莎的打法核心是——强在正面抗压和打断。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给奥丽莎真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵奥丽莎时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G787" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24175,7 +24175,7 @@
         <x:v>埃姆雷</x:v>
       </x:c>
       <x:c r="F788" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而埃姆雷的打法核心是——中距离爆发型输出，步枪和手雷适合持续压血线。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给埃姆雷真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵埃姆雷时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G788" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24204,7 +24204,7 @@
         <x:v>索杰恩</x:v>
       </x:c>
       <x:c r="F789" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而索杰恩的打法核心是——轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给索杰恩真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵索杰恩时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G789" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24233,7 +24233,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F790" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而法老之鹰的打法核心是——利用高空角度绕盾输出。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给法老之鹰真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵法老之鹰时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G790" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24262,7 +24262,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F791" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵禅雅塔时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G791" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24291,7 +24291,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F792" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而安娜的打法核心是——禁疗是对高回复阵容的核心克制。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给安娜真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵安娜时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G792" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24320,7 +24320,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F793" s="11" t="str">
-        <x:v>天使的对位优势来自其核心特点——伤害增幅能显著提高长枪/飞行英雄威胁；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。天使的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G793" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24378,7 +24378,7 @@
         <x:v>西格玛</x:v>
       </x:c>
       <x:c r="F795" s="11" t="str">
-        <x:v>西格玛的对位优势来自其核心特点——中远距离资源交换很强，怕被贴脸和多方向切入；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。西格玛应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>西格玛应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G795" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24407,7 +24407,7 @@
         <x:v>奥丽莎</x:v>
       </x:c>
       <x:c r="F796" s="11" t="str">
-        <x:v>奥丽莎的对位优势来自其核心特点——强在正面抗压和打断；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。奥丽莎应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>奥丽莎应把自己的坦克资源用于占住莫伊拉最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G796" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24494,7 +24494,7 @@
         <x:v>卡西迪</x:v>
       </x:c>
       <x:c r="F799" s="11" t="str">
-        <x:v>卡西迪的对位优势来自其核心特点——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。卡西迪需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>卡西迪需要利用自身伤害窗口持续逼莫伊拉交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G799" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24523,7 +24523,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F800" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G800" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24552,7 +24552,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F801" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G801" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24581,7 +24581,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F802" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G802" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24610,7 +24610,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F803" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而温斯顿的打法核心是——主要针对脆皮后排和高台。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给温斯顿真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵温斯顿时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G803" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24639,7 +24639,7 @@
         <x:v>末日铁拳</x:v>
       </x:c>
       <x:c r="F804" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而末日铁拳的打法核心是——核心是机动性与进出场节奏。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给末日铁拳真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵末日铁拳时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G804" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24668,7 +24668,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F805" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而破坏球的打法核心是——靠骚扰和位移制造空间。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给破坏球真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵破坏球时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G805" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24697,7 +24697,7 @@
         <x:v>西拉</x:v>
       </x:c>
       <x:c r="F806" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而西拉的打法核心是——偏精准追踪和中距离持续输出，能够稳定惩罚暴露目标。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给西拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵西拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G806" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24726,7 +24726,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F807" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而源氏的打法核心是——适合切脆皮和收割残血。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给源氏真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵源氏时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G807" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24755,7 +24755,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F808" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而猎空的打法核心是——靠持续骚扰和资源差取胜。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给猎空真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵猎空时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G808" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24784,7 +24784,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F809" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G809" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24813,7 +24813,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F810" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而布丽吉塔的打法核心是——专长是保护后排、反突进。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵布丽吉塔时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G810" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24842,7 +24842,7 @@
         <x:v>天使</x:v>
       </x:c>
       <x:c r="F811" s="11" t="str">
-        <x:v>莫伊拉的对位优势来自其核心特点——自保和追残血强，但功能性偏少；而天使的打法核心是——伤害增幅能显著提高长枪/飞行英雄威胁。莫伊拉的优势更多体现在资源交换和团队保护上，应把关键功能技能留给天使真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵天使时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G811" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24871,7 +24871,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F812" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。温斯顿应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G812" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24900,7 +24900,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F813" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。D.Va应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G813" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24929,7 +24929,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F814" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。破坏球应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住禅雅塔最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G814" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24958,7 +24958,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F815" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。源氏需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G815" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -24987,7 +24987,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F816" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。猎空需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G816" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25016,7 +25016,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F817" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。黑影需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼禅雅塔交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G817" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25045,7 +25045,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F818" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G818" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25074,7 +25074,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F819" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G819" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25103,7 +25103,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F820" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G820" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25219,7 +25219,7 @@
         <x:v>堡垒</x:v>
       </x:c>
       <x:c r="F824" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而堡垒的打法核心是——爆发火力高，但体型大、技能窗口明显。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给堡垒真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵堡垒时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G824" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25248,7 +25248,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F825" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G825" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25277,7 +25277,7 @@
         <x:v>卡西迪</x:v>
       </x:c>
       <x:c r="F826" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卡西迪时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G826" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25306,7 +25306,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F827" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G827" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25335,7 +25335,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F828" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G828" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25364,7 +25364,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F829" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵巴蒂斯特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G829" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25393,7 +25393,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F830" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。温斯顿应把自己的坦克资源用于占住雾子最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住雾子最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G830" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25422,7 +25422,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F831" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。D.Va应把自己的坦克资源用于占住雾子最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住雾子最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G831" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25451,7 +25451,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F832" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。破坏球应把自己的坦克资源用于占住雾子最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住雾子最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G832" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25480,7 +25480,7 @@
         <x:v>斩仇</x:v>
       </x:c>
       <x:c r="F833" s="11" t="str">
-        <x:v>斩仇的对位优势来自其核心特点——近战侧翼输出，依靠冲刺和格挡接近目标；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。斩仇需要利用自身伤害窗口持续逼雾子交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>斩仇需要利用自身伤害窗口持续逼雾子交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G833" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25567,7 +25567,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F836" s="11" t="str">
-        <x:v>巴蒂斯特的对位优势来自其核心特点——不朽领域能反制爆发，但怕被强突后排；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给雾子真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>巴蒂斯特的优势更多体现在资源交换和团队保护上，应把关键功能技能留给雾子真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G836" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25596,7 +25596,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F837" s="11" t="str">
-        <x:v>卢西奥的对位优势来自其核心特点——价值主要来自加速与节奏控制，而不是单纯治疗量；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给雾子真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>卢西奥的优势更多体现在资源交换和团队保护上，应把关键功能技能留给雾子真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G837" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25625,7 +25625,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F838" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而雾子的打法核心是——铃可以解除多种负面效果，位移让她很难被单切。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给雾子真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给雾子真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G838" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25654,7 +25654,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F839" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而路霸的打法核心是——钩中关键目标能快速形成击杀。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G839" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25683,7 +25683,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F840" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵渣客女王时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G840" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25712,7 +25712,7 @@
         <x:v>拉玛刹</x:v>
       </x:c>
       <x:c r="F841" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而拉玛刹的打法核心是——变身阶段近战压制力高。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给拉玛刹真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵拉玛刹时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G841" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25770,7 +25770,7 @@
         <x:v>卡西迪</x:v>
       </x:c>
       <x:c r="F843" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而卡西迪的打法核心是——中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卡西迪真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卡西迪时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G843" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25857,7 +25857,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F846" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而禅雅塔的打法核心是——乱能显著提高集火效率，但自身缺乏位移，需要队友保护。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给禅雅塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵禅雅塔时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G846" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25886,7 +25886,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F847" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G847" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25915,7 +25915,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F848" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。破坏球应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G848" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -25944,7 +25944,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F849" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。温斯顿应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住生命之梭最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G849" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26002,7 +26002,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F851" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。源氏需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G851" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26031,7 +26031,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F852" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。猎空需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G852" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26060,7 +26060,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F853" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。黑影需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼生命之梭交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G853" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26089,7 +26089,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F854" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G854" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26118,7 +26118,7 @@
         <x:v>禅雅塔</x:v>
       </x:c>
       <x:c r="F855" s="11" t="str">
-        <x:v>禅雅塔的对位优势来自其核心特点——乱能显著提高集火效率，但自身缺乏位移，需要队友保护；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>禅雅塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G855" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26147,7 +26147,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F856" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G856" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26176,7 +26176,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F857" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而路霸的打法核心是——钩中关键目标能快速形成击杀。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G857" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26205,7 +26205,7 @@
         <x:v>末日铁拳</x:v>
       </x:c>
       <x:c r="F858" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而末日铁拳的打法核心是——核心是机动性与进出场节奏。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给末日铁拳真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵末日铁拳时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G858" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26234,7 +26234,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F859" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而莱因哈特的打法核心是——强依赖近距离与地图拐角。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G859" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26263,7 +26263,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F860" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而美的打法核心是——擅长分割阵型和减速近战目标。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵美时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G860" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26292,7 +26292,7 @@
         <x:v>狂鼠</x:v>
       </x:c>
       <x:c r="F861" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而狂鼠的打法核心是——狭窄地形强，空中与远距离目标难处理。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给狂鼠真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵狂鼠时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G861" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26321,7 +26321,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F862" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G862" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26350,7 +26350,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F863" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G863" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26379,7 +26379,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F864" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G864" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26408,7 +26408,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F865" s="11" t="str">
-        <x:v>生命之梭的对位优势来自其核心特点——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置；而布丽吉塔的打法核心是——专长是保护后排、反突进。生命之梭的优势更多体现在资源交换和团队保护上，应把关键功能技能留给布丽吉塔真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵布丽吉塔时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G865" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26437,7 +26437,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F866" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。温斯顿应把自己的坦克资源用于占住伊拉锐最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住伊拉锐最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G866" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26466,7 +26466,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F867" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。D.Va应把自己的坦克资源用于占住伊拉锐最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住伊拉锐最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G867" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26495,7 +26495,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F868" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。破坏球应把自己的坦克资源用于占住伊拉锐最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住伊拉锐最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G868" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26524,7 +26524,7 @@
         <x:v>安燃</x:v>
       </x:c>
       <x:c r="F869" s="11" t="str">
-        <x:v>安燃的对位优势来自其核心特点——高机动火焰侧翼，擅长追击脆皮和制造燃烧压力；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。安燃需要利用自身伤害窗口持续逼伊拉锐交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>安燃需要利用自身伤害窗口持续逼伊拉锐交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G869" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26553,7 +26553,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F870" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。源氏需要利用自身伤害窗口持续逼伊拉锐交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼伊拉锐交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G870" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26582,7 +26582,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F871" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。猎空需要利用自身伤害窗口持续逼伊拉锐交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼伊拉锐交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G871" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26611,7 +26611,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F872" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给伊拉锐真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给伊拉锐真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G872" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26640,7 +26640,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F873" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给伊拉锐真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给伊拉锐真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G873" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26669,7 +26669,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F874" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而伊拉锐的打法核心是——输出能力较高，治疗塔位置决定续航。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给伊拉锐真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给伊拉锐真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G874" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26698,7 +26698,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F875" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而路霸的打法核心是——钩中关键目标能快速形成击杀。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G875" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26727,7 +26727,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F876" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵渣客女王时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G876" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26756,7 +26756,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F877" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而莱因哈特的打法核心是——强依赖近距离与地图拐角。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G877" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26785,7 +26785,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F878" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵托比昂时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G878" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26814,7 +26814,7 @@
         <x:v>弗蕾娅</x:v>
       </x:c>
       <x:c r="F879" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而弗蕾娅的打法核心是——高机动远程输出，擅长借助位移寻找射击角度。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给弗蕾娅真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵弗蕾娅时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G879" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26872,7 +26872,7 @@
         <x:v>巴蒂斯特</x:v>
       </x:c>
       <x:c r="F881" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而巴蒂斯特的打法核心是——不朽领域能反制爆发，但怕被强突后排。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给巴蒂斯特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵巴蒂斯特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G881" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26901,7 +26901,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F882" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G882" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26930,7 +26930,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F883" s="11" t="str">
-        <x:v>伊拉锐的对位优势来自其核心特点——输出能力较高，治疗塔位置决定续航；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。伊拉锐的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G883" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26959,7 +26959,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F884" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。温斯顿应把自己的坦克资源用于占住朱诺最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住朱诺最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G884" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -26988,7 +26988,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F885" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。D.Va应把自己的坦克资源用于占住朱诺最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住朱诺最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G885" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27017,7 +27017,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F886" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。破坏球应把自己的坦克资源用于占住朱诺最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住朱诺最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G886" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27046,7 +27046,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F887" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。黑影需要利用自身伤害窗口持续逼朱诺交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼朱诺交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G887" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27075,7 +27075,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F888" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。源氏需要利用自身伤害窗口持续逼朱诺交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼朱诺交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G888" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27104,7 +27104,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F889" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。猎空需要利用自身伤害窗口持续逼朱诺交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼朱诺交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G889" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27133,7 +27133,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F890" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给朱诺真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给朱诺真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G890" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27162,7 +27162,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F891" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给朱诺真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给朱诺真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G891" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27191,7 +27191,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F892" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而朱诺的打法核心是——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给朱诺真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给朱诺真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G892" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27220,7 +27220,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F893" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而莱因哈特的打法核心是——强依赖近距离与地图拐角。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G893" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27249,7 +27249,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F894" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而路霸的打法核心是——钩中关键目标能快速形成击杀。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G894" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27278,7 +27278,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F895" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵渣客女王时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G895" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27307,7 +27307,7 @@
         <x:v>法老之鹰</x:v>
       </x:c>
       <x:c r="F896" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而法老之鹰的打法核心是——利用高空角度绕盾输出。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给法老之鹰真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵法老之鹰时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G896" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27336,7 +27336,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F897" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G897" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27365,7 +27365,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F898" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而美的打法核心是——擅长分割阵型和减速近战目标。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵美时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G898" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27394,7 +27394,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F899" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G899" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27423,7 +27423,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F900" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G900" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27452,7 +27452,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F901" s="11" t="str">
-        <x:v>朱诺的对位优势来自其核心特点——依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。朱诺的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G901" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27510,7 +27510,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F903" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而飞天猫的打法核心是——空中机动辅助，可以快速转移并帮助队友调整位置。温斯顿应把自己的坦克资源用于占住飞天猫最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住飞天猫最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G903" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27539,7 +27539,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F904" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而飞天猫的打法核心是——空中机动辅助，可以快速转移并帮助队友调整位置。破坏球应把自己的坦克资源用于占住飞天猫最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住飞天猫最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G904" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27655,7 +27655,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F908" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而飞天猫的打法核心是——空中机动辅助，可以快速转移并帮助队友调整位置。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给飞天猫真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给飞天猫真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G908" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27684,7 +27684,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F909" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而飞天猫的打法核心是——空中机动辅助，可以快速转移并帮助队友调整位置。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给飞天猫真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给飞天猫真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G909" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27713,7 +27713,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F910" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而飞天猫的打法核心是——空中机动辅助，可以快速转移并帮助队友调整位置。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给飞天猫真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给飞天猫真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G910" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27742,7 +27742,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F911" s="11" t="str">
-        <x:v>飞天猫的对位优势来自其核心特点——空中机动辅助，可以快速转移并帮助队友调整位置；而莱因哈特的打法核心是——强依赖近距离与地图拐角。飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G911" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27771,7 +27771,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F912" s="11" t="str">
-        <x:v>飞天猫的对位优势来自其核心特点——空中机动辅助，可以快速转移并帮助队友调整位置；而路霸的打法核心是——钩中关键目标能快速形成击杀。飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G912" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27800,7 +27800,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F913" s="11" t="str">
-        <x:v>飞天猫的对位优势来自其核心特点——空中机动辅助，可以快速转移并帮助队友调整位置；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵渣客女王时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G913" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27916,7 +27916,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F917" s="11" t="str">
-        <x:v>飞天猫的对位优势来自其核心特点——空中机动辅助，可以快速转移并帮助队友调整位置；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G917" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27945,7 +27945,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F918" s="11" t="str">
-        <x:v>飞天猫的对位优势来自其核心特点——空中机动辅助，可以快速转移并帮助队友调整位置；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G918" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -27974,7 +27974,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F919" s="11" t="str">
-        <x:v>飞天猫的对位优势来自其核心特点——空中机动辅助，可以快速转移并帮助队友调整位置；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。飞天猫的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G919" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28003,7 +28003,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F920" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。温斯顿应把自己的坦克资源用于占住瑞稀最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住瑞稀最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G920" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28032,7 +28032,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F921" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。D.Va应把自己的坦克资源用于占住瑞稀最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住瑞稀最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G921" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28061,7 +28061,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F922" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。破坏球应把自己的坦克资源用于占住瑞稀最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住瑞稀最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G922" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28090,7 +28090,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F923" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。源氏需要利用自身伤害窗口持续逼瑞稀交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼瑞稀交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G923" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28119,7 +28119,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F924" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。猎空需要利用自身伤害窗口持续逼瑞稀交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼瑞稀交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G924" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28148,7 +28148,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F925" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。黑影需要利用自身伤害窗口持续逼瑞稀交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼瑞稀交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G925" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28177,7 +28177,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F926" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给瑞稀真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给瑞稀真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G926" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28206,7 +28206,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F927" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给瑞稀真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给瑞稀真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G927" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28235,7 +28235,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F928" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而瑞稀的打法核心是——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给瑞稀真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给瑞稀真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G928" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28264,7 +28264,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F929" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而莱因哈特的打法核心是——强依赖近距离与地图拐角。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G929" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28293,7 +28293,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F930" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而路霸的打法核心是——钩中关键目标能快速形成击杀。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G930" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28322,7 +28322,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F931" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵渣客女王时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G931" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28351,7 +28351,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F932" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G932" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28380,7 +28380,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F933" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而美的打法核心是——擅长分割阵型和减速近战目标。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵美时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G933" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28409,7 +28409,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F934" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵托比昂时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G934" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28438,7 +28438,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F935" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G935" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28467,7 +28467,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F936" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G936" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28496,7 +28496,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F937" s="11" t="str">
-        <x:v>瑞稀的对位优势来自其核心特点——兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。瑞稀的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G937" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28525,7 +28525,7 @@
         <x:v>破坏球</x:v>
       </x:c>
       <x:c r="F938" s="11" t="str">
-        <x:v>破坏球的对位优势来自其核心特点——靠骚扰和位移制造空间；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。破坏球应把自己的坦克资源用于占住无漾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>破坏球应把自己的坦克资源用于占住无漾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G938" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28554,7 +28554,7 @@
         <x:v>温斯顿</x:v>
       </x:c>
       <x:c r="F939" s="11" t="str">
-        <x:v>温斯顿的对位优势来自其核心特点——主要针对脆皮后排和高台；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。温斯顿应把自己的坦克资源用于占住无漾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>温斯顿应把自己的坦克资源用于占住无漾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G939" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28583,7 +28583,7 @@
         <x:v>D.Va</x:v>
       </x:c>
       <x:c r="F940" s="11" t="str">
-        <x:v>D.Va的对位优势来自其核心特点——擅长吃飞行弹道与切后排；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。D.Va应把自己的坦克资源用于占住无漾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，而不是只在正面互刷伤害。</x:v>
+        <x:v>D.Va应把自己的坦克资源用于占住无漾最想使用的输出/进场角度，并在对方关键技能进入冷却后再向前压，不要把资源浪费在正面无效换血上。</x:v>
       </x:c>
       <x:c r="G940" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28612,7 +28612,7 @@
         <x:v>源氏</x:v>
       </x:c>
       <x:c r="F941" s="11" t="str">
-        <x:v>源氏的对位优势来自其核心特点——适合切脆皮和收割残血；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。源氏需要利用自身伤害窗口持续逼无漾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>源氏需要利用自身伤害窗口持续逼无漾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G941" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28641,7 +28641,7 @@
         <x:v>猎空</x:v>
       </x:c>
       <x:c r="F942" s="11" t="str">
-        <x:v>猎空的对位优势来自其核心特点——靠持续骚扰和资源差取胜；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。猎空需要利用自身伤害窗口持续逼无漾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>猎空需要利用自身伤害窗口持续逼无漾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G942" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28670,7 +28670,7 @@
         <x:v>黑影</x:v>
       </x:c>
       <x:c r="F943" s="11" t="str">
-        <x:v>黑影的对位优势来自其核心特点——适合破坏高机动英雄节奏；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。黑影需要利用自身伤害窗口持续逼无漾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这个克制关系很难真正体现。</x:v>
+        <x:v>黑影需要利用自身伤害窗口持续逼无漾交防御或位移资源，并在这些资源进入冷却后再完成击杀；如果只打无压力的前排伤害，这组对位优势就很难转化成实际击杀或空间收益。</x:v>
       </x:c>
       <x:c r="G943" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28699,7 +28699,7 @@
         <x:v>安娜</x:v>
       </x:c>
       <x:c r="F944" s="11" t="str">
-        <x:v>安娜的对位优势来自其核心特点——禁疗是对高回复阵容的核心克制；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给无漾真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>安娜的优势更多体现在资源交换和团队保护上，应把关键功能技能留给无漾真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G944" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28728,7 +28728,7 @@
         <x:v>雾子</x:v>
       </x:c>
       <x:c r="F945" s="11" t="str">
-        <x:v>雾子的对位优势来自其核心特点——铃可以解除多种负面效果，位移让她很难被单切；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给无漾真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>雾子的优势更多体现在资源交换和团队保护上，应把关键功能技能留给无漾真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G945" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28757,7 +28757,7 @@
         <x:v>布丽吉塔</x:v>
       </x:c>
       <x:c r="F946" s="11" t="str">
-        <x:v>布丽吉塔的对位优势来自其核心特点——专长是保护后排、反突进；而无漾的打法核心是——高机动治疗辅助，可以持续照顾队友并快速重新站位。布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给无漾真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>布丽吉塔的优势更多体现在资源交换和团队保护上，应把关键功能技能留给无漾真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G946" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28786,7 +28786,7 @@
         <x:v>莱因哈特</x:v>
       </x:c>
       <x:c r="F947" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而莱因哈特的打法核心是——强依赖近距离与地图拐角。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莱因哈特真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莱因哈特时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G947" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28815,7 +28815,7 @@
         <x:v>路霸</x:v>
       </x:c>
       <x:c r="F948" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而路霸的打法核心是——钩中关键目标能快速形成击杀。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给路霸真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵路霸时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G948" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28844,7 +28844,7 @@
         <x:v>渣客女王</x:v>
       </x:c>
       <x:c r="F949" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而渣客女王的打法核心是——近距离持续压迫强，怕被拉扯与减疗。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给渣客女王真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵渣客女王时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G949" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28873,7 +28873,7 @@
         <x:v>死神</x:v>
       </x:c>
       <x:c r="F950" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而死神的打法核心是——近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给死神真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵死神时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G950" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28902,7 +28902,7 @@
         <x:v>美</x:v>
       </x:c>
       <x:c r="F951" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而美的打法核心是——擅长分割阵型和减速近战目标。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给美真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵美时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G951" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28931,7 +28931,7 @@
         <x:v>托比昂</x:v>
       </x:c>
       <x:c r="F952" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而托比昂的打法核心是——炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给托比昂真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵托比昂时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G952" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28960,7 +28960,7 @@
         <x:v>莫伊拉</x:v>
       </x:c>
       <x:c r="F953" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而莫伊拉的打法核心是——自保和追残血强，但功能性偏少。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给莫伊拉真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵莫伊拉时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G953" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -28989,7 +28989,7 @@
         <x:v>生命之梭</x:v>
       </x:c>
       <x:c r="F954" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而生命之梭的打法核心是——拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给生命之梭真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵生命之梭时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G954" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>
@@ -29018,7 +29018,7 @@
         <x:v>卢西奥</x:v>
       </x:c>
       <x:c r="F955" s="11" t="str">
-        <x:v>无漾的对位优势来自其核心特点——高机动治疗辅助，可以持续照顾队友并快速重新站位；而卢西奥的打法核心是——价值主要来自加速与节奏控制，而不是单纯治疗量。无漾的优势更多体现在资源交换和团队保护上，应把关键功能技能留给卢西奥真正发起进攻的时间点，并立即呼叫队友集火，而不是为了面板数据提前交技能。</x:v>
+        <x:v>对阵卢西奥时，应把关键功能技能留到其真正发起进攻的时间点，并立即呼叫队友集火，不要为了面板数据提前交掉关键资源。</x:v>
       </x:c>
       <x:c r="G955" s="11" t="str">
         <x:v>https://www.counterwatch.gg/stats/overwatch/counters</x:v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,12 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R8682bd5fadf14ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R7955a460c79e4156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R7c3dd66eecf341a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R202e4379840c4b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R04cab864a31e4095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R11f43750df1642da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R9e7f795c3f094279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R82b86f40873a4c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Rd16353446cc940d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R78d6bc48f5894bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R03884f3e8333474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R9633441699e24555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R2ecde5d78be149bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="Rd10d2d8537aa4348"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,12 +32,22 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -55,7 +67,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -98,11 +110,67 @@
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -317,7 +385,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.2.0</x:v>
+        <x:v>v3.3.1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -20458,6 +20526,7 @@
     <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="50" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="64" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -20506,6 +20575,9 @@
       <x:c r="O1" s="10" t="str">
         <x:v>reason</x:v>
       </x:c>
+      <x:c r="P1" s="24" t="str">
+        <x:v>image_path</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
@@ -20553,6 +20625,9 @@
       <x:c r="O2" s="11" t="str">
         <x:v>街道狭窄、拐角密集，正面推进和速度增益价值高。大锤体系容易形成稳定的资源交换，美可以封路分割。</x:v>
       </x:c>
+      <x:c r="P2" s="11" t="str">
+        <x:v>assets/maps/kings-row.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
@@ -20600,6 +20675,9 @@
       <x:c r="O3" s="11" t="str">
         <x:v>大量高台和垂直空间让机动坦克价值很高。进攻要抢高台，防守长枪位也非常强势。</x:v>
       </x:c>
+      <x:c r="P3" s="11" t="str">
+        <x:v>assets/maps/gibraltar.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
@@ -20645,6 +20723,9 @@
       <x:c r="O4" s="11" t="str">
         <x:v>视野长且天然射击位多，西格玛可以维持远程资源交换，同时为双长枪创造输出空间。</x:v>
       </x:c>
+      <x:c r="P4" s="11" t="str">
+        <x:v>assets/maps/circuit-royal.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
@@ -20690,6 +20771,9 @@
       <x:c r="O5" s="11" t="str">
         <x:v>多个阶段都存在很长的射线，远程击杀能力通常比纯近战阵容更容易发挥。</x:v>
       </x:c>
+      <x:c r="P5" s="11" t="str">
+        <x:v>assets/maps/havana.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
@@ -20737,6 +20821,9 @@
       <x:c r="O6" s="11" t="str">
         <x:v>既有长视野也有高地与侧翼路线，机动性和远程输出都重要，阵容不宜过度偏科。</x:v>
       </x:c>
+      <x:c r="P6" s="11" t="str">
+        <x:v>assets/maps/route-66.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
@@ -20784,6 +20871,9 @@
       <x:c r="O7" s="11" t="str">
         <x:v>第一段尤其开放，长枪和伤害增幅很强；后续区域则需要更注意近距离遭遇和高台争夺。</x:v>
       </x:c>
+      <x:c r="P7" s="11" t="str">
+        <x:v>assets/maps/junkertown.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
@@ -20829,6 +20919,9 @@
       <x:c r="O8" s="11" t="str">
         <x:v>高台连贯且路线复杂，能快速上下高台的英雄更容易持续保持优势角度。</x:v>
       </x:c>
+      <x:c r="P8" s="11" t="str">
+        <x:v>assets/maps/dorado.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
@@ -20874,6 +20967,9 @@
       <x:c r="O9" s="11" t="str">
         <x:v>桥口与狭窄入口很多，中远程消耗很强，但也需要防止侧翼从多个角度切入。</x:v>
       </x:c>
+      <x:c r="P9" s="11" t="str">
+        <x:v>assets/maps/rialto.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
@@ -20921,6 +21017,9 @@
       <x:c r="O10" s="11" t="str">
         <x:v>地图同时存在高地、窄口和中距离枪线，灵活的混合阵容通常比单一纯冲阵更舒服。</x:v>
       </x:c>
+      <x:c r="P10" s="11" t="str">
+        <x:v>assets/maps/midtown.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
@@ -20968,6 +21067,9 @@
       <x:c r="O11" s="11" t="str">
         <x:v>第一阶段桥口适合正面推进；进入城堡后空间更紧，近战和控场价值进一步提高。</x:v>
       </x:c>
+      <x:c r="P11" s="11" t="str">
+        <x:v>assets/maps/eichenwalde.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
@@ -21013,6 +21115,9 @@
       <x:c r="O12" s="11" t="str">
         <x:v>第一点高台非常关键，机动坦克能更快争夺射击位并帮助队友清理高地。</x:v>
       </x:c>
+      <x:c r="P12" s="11" t="str">
+        <x:v>assets/maps/numbani.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
@@ -21060,6 +21165,9 @@
       <x:c r="O13" s="11" t="str">
         <x:v>从窄口到开放高台都有，阵容最好同时保留高地处理能力和稳定中距离火力。</x:v>
       </x:c>
+      <x:c r="P13" s="11" t="str">
+        <x:v>assets/maps/hollywood.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
@@ -21107,6 +21215,9 @@
       <x:c r="O14" s="11" t="str">
         <x:v>不同子图差异较大，但整体很重视机动、抢点速度与地形利用。深井等区域尤其要防地形杀。</x:v>
       </x:c>
+      <x:c r="P14" s="11" t="str">
+        <x:v>assets/maps/ilios.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
@@ -21154,6 +21265,9 @@
       <x:c r="O15" s="11" t="str">
         <x:v>控制点周围窄口明显，速度和近距离控场往往能直接决定第一波站位。</x:v>
       </x:c>
+      <x:c r="P15" s="11" t="str">
+        <x:v>assets/maps/lijiang-tower.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
@@ -21201,6 +21315,9 @@
       <x:c r="O16" s="11" t="str">
         <x:v>三张子图差异明显，推荐保留一定机动性，方便高低差和外围路线的争夺。</x:v>
       </x:c>
+      <x:c r="P16" s="11" t="str">
+        <x:v>assets/maps/nepal.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
@@ -21248,6 +21365,9 @@
       <x:c r="O17" s="11" t="str">
         <x:v>多个子图有明显高地与开阔角度，D.Va和长枪都很容易找到发挥空间。</x:v>
       </x:c>
+      <x:c r="P17" s="11" t="str">
+        <x:v>assets/maps/busan.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
@@ -21295,6 +21415,9 @@
       <x:c r="O18" s="11" t="str">
         <x:v>转点和侧翼路线丰富，快速切入后排、再迅速撤离的机动体系比较舒服。</x:v>
       </x:c>
+      <x:c r="P18" s="11" t="str">
+        <x:v>assets/maps/oasis.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
@@ -21342,6 +21465,9 @@
       <x:c r="O19" s="11" t="str">
         <x:v>机器人路线长，战线经常变化。高机动英雄能更快重新集结、抢高地和追击残血。</x:v>
       </x:c>
+      <x:c r="P19" s="11" t="str">
+        <x:v>assets/maps/new-queen-street.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
@@ -21389,6 +21515,9 @@
       <x:c r="O20" s="11" t="str">
         <x:v>中心区域与弯道多，阵容既需要正面持续作战，也需要快速回到机器人附近。</x:v>
       </x:c>
+      <x:c r="P20" s="11" t="str">
+        <x:v>assets/maps/colosseo.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
@@ -21436,6 +21565,9 @@
       <x:c r="O21" s="11" t="str">
         <x:v>视野和高低差都比较丰富，灵活阵容更容易兼顾抢高台、侧翼和机器人转点。</x:v>
       </x:c>
+      <x:c r="P21" s="11" t="str">
+        <x:v>assets/maps/esperanca.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
@@ -21483,6 +21615,9 @@
       <x:c r="O22" s="11" t="str">
         <x:v>点位之间距离远，移动效率非常重要。过慢的阵容经常会输在转点和重新集结。</x:v>
       </x:c>
+      <x:c r="P22" s="11" t="str">
+        <x:v>assets/maps/suravasa.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
@@ -21530,6 +21665,9 @@
       <x:c r="O23" s="11" t="str">
         <x:v>多入口和频繁转点让机动性成为核心价值，侧翼英雄很容易制造交叉火力。</x:v>
       </x:c>
+      <x:c r="P23" s="11" t="str">
+        <x:v>assets/maps/new-junk-city.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
@@ -21577,6 +21715,9 @@
       <x:c r="O24" s="11" t="str">
         <x:v>地图强调紧凑战斗和快速轮转，因此高机动、快速接战和脱战的英雄更容易发挥。</x:v>
       </x:c>
+      <x:c r="P24" s="11" t="str">
+        <x:v>assets/maps/aatlis.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
@@ -21623,6 +21764,9 @@
       </x:c>
       <x:c r="O25" s="11" t="str">
         <x:v>作为混合地图，推荐用兼顾机动与中距离火力的阵容作为默认起点，再根据具体卡点调整。</x:v>
+      </x:c>
+      <x:c r="P25" s="11" t="str">
+        <x:v>assets/maps/neon-junction.svg</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22001,4 +22145,3785 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="64" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="68" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="64" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="27" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="B1" s="27" t="str">
+        <x:v>route_type</x:v>
+      </x:c>
+      <x:c r="C1" s="27" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="D1" s="27" t="str">
+        <x:v>color</x:v>
+      </x:c>
+      <x:c r="E1" s="27" t="str">
+        <x:v>points</x:v>
+      </x:c>
+      <x:c r="F1" s="27" t="str">
+        <x:v>line_width</x:v>
+      </x:c>
+      <x:c r="G1" s="27" t="str">
+        <x:v>dashed</x:v>
+      </x:c>
+      <x:c r="H1" s="27" t="str">
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="I1" s="27" t="str">
+        <x:v>source</x:v>
+      </x:c>
+      <x:c r="J1" s="27" t="str">
+        <x:v>basis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>国王大道</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>8,82;20,75;34,66;46,58;58,54;72,46;92,34</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G2" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str">
+        <x:v>第一段先通过正门压到雕像附近，再进入A点；不要长时间卡死在出生点正门。</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391314</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>国王大道</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>10,80;18,64;30,52;45,50;56,54</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G3" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="str">
+        <x:v>酒店/侧路可以避开正门直线火力，适合机动英雄先制造侧面压力。</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>https://www.pcgamesn.com/overwatch/overwatch-map-guide</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>国王大道</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>57,54;67,44;77,38;87,44;93,58</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G4" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str">
+        <x:v>进入运载阶段后优先清理街道和高台角度，再让车安全通过狭窄街区。</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>直布罗陀</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>7,78;20,72;36,70;50,60;65,56;82,48;94,38</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G5" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>主路推进必须围绕货车，但不要五个人全叠车；先处理桥上和机库高台。</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391265</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>直布罗陀</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>9,82;22,86;35,76;46,64;58,58</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G6" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>第一段右侧隧道可避开主门枪线，适合侧翼/机动位绕到防守阵型侧面。</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391265</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>直布罗陀</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>10,69;24,54;39,45;55,40;70,34;84,37</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G7" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>直布罗陀高台价值很高，进攻方应主动夺取而不是一直从车后向上仰射。</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391265</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>皇家赛道</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G8" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
+        <x:v>第一段视野很长，主路应借车辆和拐角逐段推进，避免整队裸露在长枪线。</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>皇家赛道</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G9" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str">
+        <x:v>侧翼的目的不是单人绕很远，而是逼防守长枪转头，让正面能跨过开阔区。</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>皇家赛道</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G10" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str">
+        <x:v>第一段尤其依赖高地与长视野控制，先抢输出角再推车。</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>哈瓦那</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G11" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str">
+        <x:v>三个阶段都存在长枪视野，应按掩体分段推进而不是一路跟车直走。</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>哈瓦那</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G12" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str">
+        <x:v>利用室内和侧路缩短与长枪的距离，迫使防守方离开最舒服的远端角度。</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
+        <x:v>哈瓦那</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G13" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>高地清不掉时货车很难安全通过；机动位优先清高台，再回到车线。</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="str">
+        <x:v>66号公路</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G14" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str">
+        <x:v>货车路线较直，但每段都有高地和拐角；推进前先处理加油站、洞口等优势位。</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="str">
+        <x:v>66号公路</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G15" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="str">
+        <x:v>侧洞和建筑能帮助队伍避开长线正面火力，适合侧翼位制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11" t="str">
+        <x:v>66号公路</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G16" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str">
+        <x:v>第一段和中段都要重视高地，单纯站车后会让上方输出持续白打。</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11" t="str">
+        <x:v>渣客镇</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G17" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="str">
+        <x:v>第一段非常开放，主路推进应利用货车和掩体逐段压进，不宜长期暴露在远程视野。</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="11" t="str">
+        <x:v>渣客镇</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G18" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="str">
+        <x:v>建筑与侧路适合侧翼英雄切入后排，目的在于打散防守长枪的站位。</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J18" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="11" t="str">
+        <x:v>渣客镇</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G19" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="str">
+        <x:v>进入城区后高台价值上升，应先抢建筑上方再推进货车。</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J19" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="11" t="str">
+        <x:v>多拉多</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G20" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="str">
+        <x:v>市场前拱门是经典窄口，正面推进要配合资源跨过，而不是在门口持续消耗。</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391182</x:v>
+      </x:c>
+      <x:c r="J20" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="11" t="str">
+        <x:v>多拉多</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G21" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="str">
+        <x:v>利用互通建筑和侧路绕过拱门枪线，机动英雄可先切入市场内部。</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391182</x:v>
+      </x:c>
+      <x:c r="J21" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="11" t="str">
+        <x:v>多拉多</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G22" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="11" t="str">
+        <x:v>第二、三段大量高台和屋顶可形成长视野，进攻方必须主动清高。</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391182</x:v>
+      </x:c>
+      <x:c r="J22" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="11" t="str">
+        <x:v>里阿尔托</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G23" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="str">
+        <x:v>主路会多次经过桥口和狭窄街道，推进时要提前占下一段掩体而不是只跟着车。</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J23" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="11" t="str">
+        <x:v>里阿尔托</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G24" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="11" t="str">
+        <x:v>利用建筑和水道附近侧路制造交叉火力，避免在桥口被单一方向压制。</x:v>
+      </x:c>
+      <x:c r="I24" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J24" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="11" t="str">
+        <x:v>里阿尔托</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G25" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="str">
+        <x:v>二层窗口和桥上视角能覆盖主路，机动位优先清掉这些位置再让车前进。</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J25" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="11" t="str">
+        <x:v>中城</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G26" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="str">
+        <x:v>第一点主路开阔，拿点后进入车站/街道阶段，需持续按拐角分段推进。</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J26" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="11" t="str">
+        <x:v>中城</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G27" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="str">
+        <x:v>第一点侧路可绕开正门枪线，适合机动位先逼退侧翼和后排。</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J27" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="11" t="str">
+        <x:v>中城</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G28" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="str">
+        <x:v>中城高台能覆盖大量主路，尤其第一点与二段要优先争夺。</x:v>
+      </x:c>
+      <x:c r="I28" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J28" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="11" t="str">
+        <x:v>艾兴瓦尔德</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G29" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="str">
+        <x:v>第一点桥口很窄，主路要靠速度/资源一次跨过；拿点后再围绕货车推进。</x:v>
+      </x:c>
+      <x:c r="I29" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391311</x:v>
+      </x:c>
+      <x:c r="J29" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="11" t="str">
+        <x:v>艾兴瓦尔德</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G30" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="str">
+        <x:v>机动英雄可利用侧路跳过桥口正面火力，直接给高台和后排压力。</x:v>
+      </x:c>
+      <x:c r="I30" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391311</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="str">
+        <x:v>艾兴瓦尔德</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G31" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="str">
+        <x:v>二段高地非常重要，进攻方不清高地会很难持续推车。</x:v>
+      </x:c>
+      <x:c r="I31" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/391311</x:v>
+      </x:c>
+      <x:c r="J31" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="11" t="str">
+        <x:v>努巴尼</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G32" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="11" t="str">
+        <x:v>第一点不要只从中路直冲，主路线应配合多入口一起压缩防守空间。</x:v>
+      </x:c>
+      <x:c r="I32" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J32" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="11" t="str">
+        <x:v>努巴尼</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G33" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="11" t="str">
+        <x:v>第一点有多种进入方式，侧楼路线能直接威胁后排和高台。</x:v>
+      </x:c>
+      <x:c r="I33" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J33" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="11" t="str">
+        <x:v>努巴尼</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G34" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="11" t="str">
+        <x:v>垂直机动英雄在努巴尼价值很高，优先处理第一点和中段的高台。</x:v>
+      </x:c>
+      <x:c r="I34" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J34" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="11" t="str">
+        <x:v>好莱坞</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G35" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="11" t="str">
+        <x:v>第一点进入后要迅速接管点周围空间，二段则围绕建筑和车线分段推进。</x:v>
+      </x:c>
+      <x:c r="I35" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J35" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="11" t="str">
+        <x:v>好莱坞</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D36" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G36" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" s="11" t="str">
+        <x:v>侧门与小房能避开门口集火，适合侧翼位制造第二进攻角。</x:v>
+      </x:c>
+      <x:c r="I36" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J36" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="11" t="str">
+        <x:v>好莱坞</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G37" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="11" t="str">
+        <x:v>二段建筑顶部是关键位置，谁控制高台谁更容易控制货车路线。</x:v>
+      </x:c>
+      <x:c r="I37" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J37" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="11" t="str">
+        <x:v>伊利奥斯</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C38" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="str">
+        <x:v>10,78;27,67;43,58;50,50;58,42;74,34;90,24</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G38" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="11" t="str">
+        <x:v>第一波重点是尽快拿到点周边空间，不要让全队在入口处停滞。</x:v>
+      </x:c>
+      <x:c r="I38" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J38" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="11" t="str">
+        <x:v>伊利奥斯</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str">
+        <x:v>10,82;24,88;40,75;50,62;61,52</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G39" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" s="11" t="str">
+        <x:v>井、灯塔和废墟都存在侧路/外圈角度，侧翼用于逼迫对方转身。</x:v>
+      </x:c>
+      <x:c r="I39" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J39" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="11" t="str">
+        <x:v>伊利奥斯</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="str">
+        <x:v>14,64;30,48;48,38;66,34;84,27</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G40" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="11" t="str">
+        <x:v>废墟更偏长枪，高位和远端角度价值高；灯塔则更偏近战控制。</x:v>
+      </x:c>
+      <x:c r="I40" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J40" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="11" t="str">
+        <x:v>漓江塔</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>10,79;27,68;43,59;50,50;59,42;74,33;90,24</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G41" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="11" t="str">
+        <x:v>控制中心和夜市常见快速正面争点，抢先占住入口和点边掩体很重要。</x:v>
+      </x:c>
+      <x:c r="I41" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J41" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="str">
+        <x:v>漓江塔</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="str">
+        <x:v>10,84;25,88;40,75;51,62;63,52</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G42" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" s="11" t="str">
+        <x:v>花园和夜市侧路多，适合利用房间/桥侧做包夹，不要所有人挤一条路。</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J42" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="str">
+        <x:v>漓江塔</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str">
+        <x:v>13,65;30,49;47,39;64,34;82,28</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G43" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="11" t="str">
+        <x:v>花园高地价值突出，控制高台能同时影响点和对方转点路线。</x:v>
+      </x:c>
+      <x:c r="I43" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J43" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="str">
+        <x:v>尼泊尔</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C44" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G44" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="11" t="str">
+        <x:v>三个子图都应尽快拿点边空间；村庄更偏近战，圣所/神殿更重视角度控制。</x:v>
+      </x:c>
+      <x:c r="I44" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J44" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="str">
+        <x:v>尼泊尔</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G45" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" s="11" t="str">
+        <x:v>侧廊能让侧翼英雄绕开正面坦克，直接压辅助或迫使对方分人防守。</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J45" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="str">
+        <x:v>尼泊尔</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G46" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" s="11" t="str">
+        <x:v>神殿/圣所的高低差能决定枪线，优先站住可覆盖点位的高处。</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J46" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="11" t="str">
+        <x:v>釜山</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G47" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" s="11" t="str">
+        <x:v>三张子图节奏差异大，但第一波都应优先抢点周边关键空间，而不是只追人。</x:v>
+      </x:c>
+      <x:c r="I47" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J47" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="11" t="str">
+        <x:v>釜山</x:v>
+      </x:c>
+      <x:c r="B48" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C48" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G48" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H48" s="11" t="str">
+        <x:v>市区和机甲基地都有侧房/外圈路线，可用于切断对方后排视野。</x:v>
+      </x:c>
+      <x:c r="I48" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J48" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="str">
+        <x:v>釜山</x:v>
+      </x:c>
+      <x:c r="B49" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G49" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" s="11" t="str">
+        <x:v>高台对中远距离英雄价值高，先控高再落点会比一直站点内更安全。</x:v>
+      </x:c>
+      <x:c r="I49" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J49" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="11" t="str">
+        <x:v>绿洲</x:v>
+      </x:c>
+      <x:c r="B50" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G50" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H50" s="11" t="str">
+        <x:v>大学更偏狭窄近战，花园和市中心则更强调机动和角度切换。</x:v>
+      </x:c>
+      <x:c r="I50" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J50" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="11" t="str">
+        <x:v>绿洲</x:v>
+      </x:c>
+      <x:c r="B51" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G51" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H51" s="11" t="str">
+        <x:v>利用外圈和跳台路线绕开正面，对辅助和远端输出制造侧压。</x:v>
+      </x:c>
+      <x:c r="I51" s="11" t="str">
+        <x:v>https://pwm-pro.com/blog/post/overwatch-2-control-maps-secrets-key-locations-and-best-routes</x:v>
+      </x:c>
+      <x:c r="J51" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="11" t="str">
+        <x:v>绿洲</x:v>
+      </x:c>
+      <x:c r="B52" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C52" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G52" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H52" s="11" t="str">
+        <x:v>市中心跳台和二层能形成快速高低差转换，控制高位能扩大视野。</x:v>
+      </x:c>
+      <x:c r="I52" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J52" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="11" t="str">
+        <x:v>新皇后街</x:v>
+      </x:c>
+      <x:c r="B53" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="str">
+        <x:v>8,72;23,62;40,55;50,50;62,46;77,38;92,28</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G53" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H53" s="11" t="str">
+        <x:v>机器人主路呈弯曲路线，推进时应提前占下一个拐角而不是所有人贴机器人。</x:v>
+      </x:c>
+      <x:c r="I53" s="11" t="str">
+        <x:v>https://theglobalgaming.com/overwatch/all-maps</x:v>
+      </x:c>
+      <x:c r="J53" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="11" t="str">
+        <x:v>新皇后街</x:v>
+      </x:c>
+      <x:c r="B54" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C54" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D54" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E54" s="11" t="str">
+        <x:v>10,80;26,84;40,70;54,58;68,50</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G54" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H54" s="11" t="str">
+        <x:v>商店和小巷能直接穿过主路弯道，适合侧翼制造前后夹击。</x:v>
+      </x:c>
+      <x:c r="I54" s="11" t="str">
+        <x:v>https://game8.co/games/Overwatch2/archives/393849</x:v>
+      </x:c>
+      <x:c r="J54" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="11" t="str">
+        <x:v>新皇后街</x:v>
+      </x:c>
+      <x:c r="B55" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="str">
+        <x:v>15,61;31,48;48,40;65,35;82,29</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G55" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="11" t="str">
+        <x:v>中央和终段高台能覆盖长枪线，主力应抢空间而不是全员站机器人旁边。</x:v>
+      </x:c>
+      <x:c r="I55" s="11" t="str">
+        <x:v>https://overwatch.blizzard.com/en-gb/news/23785339/uniting-gameplay-and-style-behind-overwatch-2-s-complex-map-design/</x:v>
+      </x:c>
+      <x:c r="J55" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="11" t="str">
+        <x:v>斗兽场</x:v>
+      </x:c>
+      <x:c r="B56" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D56" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F56" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G56" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="11" t="str">
+        <x:v>机器人路线会绕桥和环形区域，推进队应提前抢桥口后的空间。</x:v>
+      </x:c>
+      <x:c r="I56" s="11" t="str">
+        <x:v>https://theglobalgaming.com/overwatch/all-maps</x:v>
+      </x:c>
+      <x:c r="J56" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="11" t="str">
+        <x:v>斗兽场</x:v>
+      </x:c>
+      <x:c r="B57" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C57" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D57" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E57" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F57" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G57" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H57" s="11" t="str">
+        <x:v>侧廊能绕开机器人主路并快速切后排，尤其适合高机动英雄。</x:v>
+      </x:c>
+      <x:c r="I57" s="11" t="str">
+        <x:v>https://www.reddit.com/r/OverwatchUniversity/comments/znyn2r</x:v>
+      </x:c>
+      <x:c r="J57" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="11" t="str">
+        <x:v>斗兽场</x:v>
+      </x:c>
+      <x:c r="B58" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C58" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D58" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E58" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F58" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G58" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="11" t="str">
+        <x:v>桥上和高位通道能覆盖中央庭院，控制后更容易安全推进机器人。</x:v>
+      </x:c>
+      <x:c r="I58" s="11" t="str">
+        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+      </x:c>
+      <x:c r="J58" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="11" t="str">
+        <x:v>埃斯佩兰萨</x:v>
+      </x:c>
+      <x:c r="B59" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C59" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D59" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E59" s="11" t="str">
+        <x:v>8,80;22,72;38,64;52,56;68,49;84,41;94,32</x:v>
+      </x:c>
+      <x:c r="F59" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G59" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H59" s="11" t="str">
+        <x:v>中段较开阔，机器人推进前要先占前方建筑/拱门空间，避免被远程点名。</x:v>
+      </x:c>
+      <x:c r="I59" s="11" t="str">
+        <x:v>https://theglobalgaming.com/overwatch/all-maps</x:v>
+      </x:c>
+      <x:c r="J59" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="11" t="str">
+        <x:v>埃斯佩兰萨</x:v>
+      </x:c>
+      <x:c r="B60" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C60" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D60" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E60" s="11" t="str">
+        <x:v>10,85;25,88;40,75;54,64;68,56</x:v>
+      </x:c>
+      <x:c r="F60" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G60" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H60" s="11" t="str">
+        <x:v>地图有大量捷径和建筑通道，合理使用能缩短回场和绕侧时间。</x:v>
+      </x:c>
+      <x:c r="I60" s="11" t="str">
+        <x:v>https://theglobalgaming.com/overwatch/all-maps</x:v>
+      </x:c>
+      <x:c r="J60" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="11" t="str">
+        <x:v>埃斯佩兰萨</x:v>
+      </x:c>
+      <x:c r="B61" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="str">
+        <x:v>13,66;29,51;46,42;63,37;80,31</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G61" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="11" t="str">
+        <x:v>中段高地非常关键，控制后能同时看机器人和两侧通路。</x:v>
+      </x:c>
+      <x:c r="I61" s="11" t="str">
+        <x:v>https://theglobalgaming.com/overwatch/all-maps</x:v>
+      </x:c>
+      <x:c r="J61" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="11" t="str">
+        <x:v>苏拉瓦萨</x:v>
+      </x:c>
+      <x:c r="B62" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E62" s="11" t="str">
+        <x:v>50,50;44,38;34,27;24,20;16,14</x:v>
+      </x:c>
+      <x:c r="F62" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G62" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="11" t="str">
+        <x:v>新点出现后快速判断最短安全路线，提前到点周边占空间。</x:v>
+      </x:c>
+      <x:c r="I62" s="11" t="str">
+        <x:v>https://overwatch.blizzard.com/en-gb/news/24215719/weekly-recall-flashpoint-map-reworks</x:v>
+      </x:c>
+      <x:c r="J62" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="11" t="str">
+        <x:v>苏拉瓦萨</x:v>
+      </x:c>
+      <x:c r="B63" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C63" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E63" s="11" t="str">
+        <x:v>50,50;61,44;72,36;82,28;90,21</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G63" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H63" s="11" t="str">
+        <x:v>2025重做增加/简化多条侧路与连接线，转点时可绕开主 choke。</x:v>
+      </x:c>
+      <x:c r="I63" s="11" t="str">
+        <x:v>https://overwatch.blizzard.com/en-gb/news/24215719/weekly-recall-flashpoint-map-reworks</x:v>
+      </x:c>
+      <x:c r="J63" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="11" t="str">
+        <x:v>苏拉瓦萨</x:v>
+      </x:c>
+      <x:c r="B64" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C64" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E64" s="11" t="str">
+        <x:v>50,50;50,40;52,31;58,23;66,16</x:v>
+      </x:c>
+      <x:c r="F64" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G64" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64" s="11" t="str">
+        <x:v>中心点新增更容易上高台的路径，高台能帮助队伍观察下一波转点和入口。</x:v>
+      </x:c>
+      <x:c r="I64" s="11" t="str">
+        <x:v>https://overwatch.blizzard.com/en-gb/news/24215719/weekly-recall-flashpoint-map-reworks</x:v>
+      </x:c>
+      <x:c r="J64" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="11" t="str">
+        <x:v>新渣客城</x:v>
+      </x:c>
+      <x:c r="B65" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C65" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="str">
+        <x:v>50,50;42,39;32,30;23,21;15,14</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G65" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="11" t="str">
+        <x:v>五个闪点之间距离较大，抢先转点比在旧点追残血更重要。</x:v>
+      </x:c>
+      <x:c r="I65" s="11" t="str">
+        <x:v>https://www.youtube.com/watch?v=gVYzUzgFDvU</x:v>
+      </x:c>
+      <x:c r="J65" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="11" t="str">
+        <x:v>新渣客城</x:v>
+      </x:c>
+      <x:c r="B66" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C66" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D66" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E66" s="11" t="str">
+        <x:v>50,50;61,44;72,36;82,28;90,21</x:v>
+      </x:c>
+      <x:c r="F66" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G66" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H66" s="11" t="str">
+        <x:v>重做后加入更顺畅的上层路线与连接通道，用于避开主 choke 或快速回场。</x:v>
+      </x:c>
+      <x:c r="I66" s="11" t="str">
+        <x:v>https://overwatch.blizzard.com/en-gb/news/24215719/weekly-recall-flashpoint-map-reworks</x:v>
+      </x:c>
+      <x:c r="J66" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="11" t="str">
+        <x:v>新渣客城</x:v>
+      </x:c>
+      <x:c r="B67" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="str">
+        <x:v>50,50;50,40;52,31;58,23;66,16</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G67" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H67" s="11" t="str">
+        <x:v>上层路径既能缩短回场，也能在进入点位前先取得视野和角度。</x:v>
+      </x:c>
+      <x:c r="I67" s="11" t="str">
+        <x:v>https://overwatch.blizzard.com/en-gb/news/24215719/weekly-recall-flashpoint-map-reworks</x:v>
+      </x:c>
+      <x:c r="J67" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="11" t="str">
+        <x:v>阿特利斯</x:v>
+      </x:c>
+      <x:c r="B68" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C68" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D68" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E68" s="11" t="str">
+        <x:v>50,50;39,40;30,31;22,23;14,16</x:v>
+      </x:c>
+      <x:c r="F68" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G68" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H68" s="11" t="str">
+        <x:v>Aatlis整体更紧凑，Station、Garden、Town Center、Bazaar、Resort之间应快速转点。</x:v>
+      </x:c>
+      <x:c r="I68" s="11" t="str">
+        <x:v>https://overwatch.fandom.com/wiki/Aatlis</x:v>
+      </x:c>
+      <x:c r="J68" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="11" t="str">
+        <x:v>阿特利斯</x:v>
+      </x:c>
+      <x:c r="B69" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="str">
+        <x:v>50,50;61,44;73,36;83,28;91,20</x:v>
+      </x:c>
+      <x:c r="F69" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G69" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H69" s="11" t="str">
+        <x:v>Garden更偏机动英雄，同时保留长视野与近战掩体；侧线适合快速包夹。</x:v>
+      </x:c>
+      <x:c r="I69" s="11" t="str">
+        <x:v>https://overwatch.fandom.com/wiki/Aatlis</x:v>
+      </x:c>
+      <x:c r="J69" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="11" t="str">
+        <x:v>阿特利斯</x:v>
+      </x:c>
+      <x:c r="B70" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C70" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E70" s="11" t="str">
+        <x:v>50,50;50,40;54,31;61,23;69,16</x:v>
+      </x:c>
+      <x:c r="F70" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G70" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H70" s="11" t="str">
+        <x:v>高位用于观察入口与下一闪点方向，避免在点内失去外圈视野。</x:v>
+      </x:c>
+      <x:c r="I70" s="11" t="str">
+        <x:v>https://overwatch.fandom.com/wiki/Aatlis</x:v>
+      </x:c>
+      <x:c r="J70" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="11" t="str">
+        <x:v>霓虹交汇点</x:v>
+      </x:c>
+      <x:c r="B71" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+      <x:c r="C71" s="11" t="str">
+        <x:v>主攻路线</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="str">
+        <x:v>#f59e0b</x:v>
+      </x:c>
+      <x:c r="E71" s="11" t="str">
+        <x:v>8,81;22,73;36,66;49,58;63,52;78,45;93,35</x:v>
+      </x:c>
+      <x:c r="F71" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G71" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H71" s="11" t="str">
+        <x:v>第一点应集中资源快速建立空间；拿点后立即衔接运载，不要为了追击浪费转阶段时间。</x:v>
+      </x:c>
+      <x:c r="I71" s="11" t="str">
+        <x:v>https://owtracker.org/en/maps/neon-junction</x:v>
+      </x:c>
+      <x:c r="J71" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="11" t="str">
+        <x:v>霓虹交汇点</x:v>
+      </x:c>
+      <x:c r="B72" s="11" t="str">
+        <x:v>flank</x:v>
+      </x:c>
+      <x:c r="C72" s="11" t="str">
+        <x:v>绕后 / 侧路</x:v>
+      </x:c>
+      <x:c r="D72" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+      <x:c r="E72" s="11" t="str">
+        <x:v>10,85;24,87;39,75;53,64;67,56</x:v>
+      </x:c>
+      <x:c r="F72" s="11" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G72" s="32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H72" s="11" t="str">
+        <x:v>地图大量小房和窄巷适合从两侧推进，能减少主街长枪直线压力。</x:v>
+      </x:c>
+      <x:c r="I72" s="11" t="str">
+        <x:v>https://note.com/drop_0518/n/n4f9d9332c0f2</x:v>
+      </x:c>
+      <x:c r="J72" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="11" t="str">
+        <x:v>霓虹交汇点</x:v>
+      </x:c>
+      <x:c r="B73" s="11" t="str">
+        <x:v>highground</x:v>
+      </x:c>
+      <x:c r="C73" s="11" t="str">
+        <x:v>高台 / 优势角</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="str">
+        <x:v>#38bdf8</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="str">
+        <x:v>13,66;29,51;45,43;62,38;79,32</x:v>
+      </x:c>
+      <x:c r="F73" s="11" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G73" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H73" s="11" t="str">
+        <x:v>列车与二层区域存在关键高低差；先清高处再让队伍过隧道/街道会更稳定。</x:v>
+      </x:c>
+      <x:c r="I73" s="11" t="str">
+        <x:v>https://note.com/drop_0518/n/n4f9d9332c0f2</x:v>
+      </x:c>
+      <x:c r="J73" s="11" t="str">
+        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="11"/>
+      <x:c r="B74" s="11"/>
+      <x:c r="C74" s="11"/>
+      <x:c r="D74" s="11"/>
+      <x:c r="E74" s="11"/>
+      <x:c r="F74" s="11"/>
+      <x:c r="G74" s="11"/>
+      <x:c r="H74" s="11"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="11"/>
+      <x:c r="B75" s="11"/>
+      <x:c r="C75" s="11"/>
+      <x:c r="D75" s="11"/>
+      <x:c r="E75" s="11"/>
+      <x:c r="F75" s="11"/>
+      <x:c r="G75" s="11"/>
+      <x:c r="H75" s="11"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="11"/>
+      <x:c r="B76" s="11"/>
+      <x:c r="C76" s="11"/>
+      <x:c r="D76" s="11"/>
+      <x:c r="E76" s="11"/>
+      <x:c r="F76" s="11"/>
+      <x:c r="G76" s="11"/>
+      <x:c r="H76" s="11"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="11"/>
+      <x:c r="B77" s="11"/>
+      <x:c r="C77" s="11"/>
+      <x:c r="D77" s="11"/>
+      <x:c r="E77" s="11"/>
+      <x:c r="F77" s="11"/>
+      <x:c r="G77" s="11"/>
+      <x:c r="H77" s="11"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="11"/>
+      <x:c r="B78" s="11"/>
+      <x:c r="C78" s="11"/>
+      <x:c r="D78" s="11"/>
+      <x:c r="E78" s="11"/>
+      <x:c r="F78" s="11"/>
+      <x:c r="G78" s="11"/>
+      <x:c r="H78" s="11"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="11"/>
+      <x:c r="B79" s="11"/>
+      <x:c r="C79" s="11"/>
+      <x:c r="D79" s="11"/>
+      <x:c r="E79" s="11"/>
+      <x:c r="F79" s="11"/>
+      <x:c r="G79" s="11"/>
+      <x:c r="H79" s="11"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="11"/>
+      <x:c r="B80" s="11"/>
+      <x:c r="C80" s="11"/>
+      <x:c r="D80" s="11"/>
+      <x:c r="E80" s="11"/>
+      <x:c r="F80" s="11"/>
+      <x:c r="G80" s="11"/>
+      <x:c r="H80" s="11"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="11"/>
+      <x:c r="B81" s="11"/>
+      <x:c r="C81" s="11"/>
+      <x:c r="D81" s="11"/>
+      <x:c r="E81" s="11"/>
+      <x:c r="F81" s="11"/>
+      <x:c r="G81" s="11"/>
+      <x:c r="H81" s="11"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="11"/>
+      <x:c r="B82" s="11"/>
+      <x:c r="C82" s="11"/>
+      <x:c r="D82" s="11"/>
+      <x:c r="E82" s="11"/>
+      <x:c r="F82" s="11"/>
+      <x:c r="G82" s="11"/>
+      <x:c r="H82" s="11"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="11"/>
+      <x:c r="B83" s="11"/>
+      <x:c r="C83" s="11"/>
+      <x:c r="D83" s="11"/>
+      <x:c r="E83" s="11"/>
+      <x:c r="F83" s="11"/>
+      <x:c r="G83" s="11"/>
+      <x:c r="H83" s="11"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="11"/>
+      <x:c r="B84" s="11"/>
+      <x:c r="C84" s="11"/>
+      <x:c r="D84" s="11"/>
+      <x:c r="E84" s="11"/>
+      <x:c r="F84" s="11"/>
+      <x:c r="G84" s="11"/>
+      <x:c r="H84" s="11"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="11"/>
+      <x:c r="B85" s="11"/>
+      <x:c r="C85" s="11"/>
+      <x:c r="D85" s="11"/>
+      <x:c r="E85" s="11"/>
+      <x:c r="F85" s="11"/>
+      <x:c r="G85" s="11"/>
+      <x:c r="H85" s="11"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="11"/>
+      <x:c r="B86" s="11"/>
+      <x:c r="C86" s="11"/>
+      <x:c r="D86" s="11"/>
+      <x:c r="E86" s="11"/>
+      <x:c r="F86" s="11"/>
+      <x:c r="G86" s="11"/>
+      <x:c r="H86" s="11"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="11"/>
+      <x:c r="B87" s="11"/>
+      <x:c r="C87" s="11"/>
+      <x:c r="D87" s="11"/>
+      <x:c r="E87" s="11"/>
+      <x:c r="F87" s="11"/>
+      <x:c r="G87" s="11"/>
+      <x:c r="H87" s="11"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="11"/>
+      <x:c r="B88" s="11"/>
+      <x:c r="C88" s="11"/>
+      <x:c r="D88" s="11"/>
+      <x:c r="E88" s="11"/>
+      <x:c r="F88" s="11"/>
+      <x:c r="G88" s="11"/>
+      <x:c r="H88" s="11"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="11"/>
+      <x:c r="B89" s="11"/>
+      <x:c r="C89" s="11"/>
+      <x:c r="D89" s="11"/>
+      <x:c r="E89" s="11"/>
+      <x:c r="F89" s="11"/>
+      <x:c r="G89" s="11"/>
+      <x:c r="H89" s="11"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="11"/>
+      <x:c r="B90" s="11"/>
+      <x:c r="C90" s="11"/>
+      <x:c r="D90" s="11"/>
+      <x:c r="E90" s="11"/>
+      <x:c r="F90" s="11"/>
+      <x:c r="G90" s="11"/>
+      <x:c r="H90" s="11"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="11"/>
+      <x:c r="B91" s="11"/>
+      <x:c r="C91" s="11"/>
+      <x:c r="D91" s="11"/>
+      <x:c r="E91" s="11"/>
+      <x:c r="F91" s="11"/>
+      <x:c r="G91" s="11"/>
+      <x:c r="H91" s="11"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="11"/>
+      <x:c r="B92" s="11"/>
+      <x:c r="C92" s="11"/>
+      <x:c r="D92" s="11"/>
+      <x:c r="E92" s="11"/>
+      <x:c r="F92" s="11"/>
+      <x:c r="G92" s="11"/>
+      <x:c r="H92" s="11"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="11"/>
+      <x:c r="B93" s="11"/>
+      <x:c r="C93" s="11"/>
+      <x:c r="D93" s="11"/>
+      <x:c r="E93" s="11"/>
+      <x:c r="F93" s="11"/>
+      <x:c r="G93" s="11"/>
+      <x:c r="H93" s="11"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="11"/>
+      <x:c r="B94" s="11"/>
+      <x:c r="C94" s="11"/>
+      <x:c r="D94" s="11"/>
+      <x:c r="E94" s="11"/>
+      <x:c r="F94" s="11"/>
+      <x:c r="G94" s="11"/>
+      <x:c r="H94" s="11"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="11"/>
+      <x:c r="B95" s="11"/>
+      <x:c r="C95" s="11"/>
+      <x:c r="D95" s="11"/>
+      <x:c r="E95" s="11"/>
+      <x:c r="F95" s="11"/>
+      <x:c r="G95" s="11"/>
+      <x:c r="H95" s="11"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="11"/>
+      <x:c r="B96" s="11"/>
+      <x:c r="C96" s="11"/>
+      <x:c r="D96" s="11"/>
+      <x:c r="E96" s="11"/>
+      <x:c r="F96" s="11"/>
+      <x:c r="G96" s="11"/>
+      <x:c r="H96" s="11"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="11"/>
+      <x:c r="B97" s="11"/>
+      <x:c r="C97" s="11"/>
+      <x:c r="D97" s="11"/>
+      <x:c r="E97" s="11"/>
+      <x:c r="F97" s="11"/>
+      <x:c r="G97" s="11"/>
+      <x:c r="H97" s="11"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="11"/>
+      <x:c r="B98" s="11"/>
+      <x:c r="C98" s="11"/>
+      <x:c r="D98" s="11"/>
+      <x:c r="E98" s="11"/>
+      <x:c r="F98" s="11"/>
+      <x:c r="G98" s="11"/>
+      <x:c r="H98" s="11"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="11"/>
+      <x:c r="B99" s="11"/>
+      <x:c r="C99" s="11"/>
+      <x:c r="D99" s="11"/>
+      <x:c r="E99" s="11"/>
+      <x:c r="F99" s="11"/>
+      <x:c r="G99" s="11"/>
+      <x:c r="H99" s="11"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="11"/>
+      <x:c r="B100" s="11"/>
+      <x:c r="C100" s="11"/>
+      <x:c r="D100" s="11"/>
+      <x:c r="E100" s="11"/>
+      <x:c r="F100" s="11"/>
+      <x:c r="G100" s="11"/>
+      <x:c r="H100" s="11"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="11"/>
+      <x:c r="B101" s="11"/>
+      <x:c r="C101" s="11"/>
+      <x:c r="D101" s="11"/>
+      <x:c r="E101" s="11"/>
+      <x:c r="F101" s="11"/>
+      <x:c r="G101" s="11"/>
+      <x:c r="H101" s="11"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="11"/>
+      <x:c r="B102" s="11"/>
+      <x:c r="C102" s="11"/>
+      <x:c r="D102" s="11"/>
+      <x:c r="E102" s="11"/>
+      <x:c r="F102" s="11"/>
+      <x:c r="G102" s="11"/>
+      <x:c r="H102" s="11"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="11"/>
+      <x:c r="B103" s="11"/>
+      <x:c r="C103" s="11"/>
+      <x:c r="D103" s="11"/>
+      <x:c r="E103" s="11"/>
+      <x:c r="F103" s="11"/>
+      <x:c r="G103" s="11"/>
+      <x:c r="H103" s="11"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="11"/>
+      <x:c r="B104" s="11"/>
+      <x:c r="C104" s="11"/>
+      <x:c r="D104" s="11"/>
+      <x:c r="E104" s="11"/>
+      <x:c r="F104" s="11"/>
+      <x:c r="G104" s="11"/>
+      <x:c r="H104" s="11"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="11"/>
+      <x:c r="B105" s="11"/>
+      <x:c r="C105" s="11"/>
+      <x:c r="D105" s="11"/>
+      <x:c r="E105" s="11"/>
+      <x:c r="F105" s="11"/>
+      <x:c r="G105" s="11"/>
+      <x:c r="H105" s="11"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="11"/>
+      <x:c r="B106" s="11"/>
+      <x:c r="C106" s="11"/>
+      <x:c r="D106" s="11"/>
+      <x:c r="E106" s="11"/>
+      <x:c r="F106" s="11"/>
+      <x:c r="G106" s="11"/>
+      <x:c r="H106" s="11"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="11"/>
+      <x:c r="B107" s="11"/>
+      <x:c r="C107" s="11"/>
+      <x:c r="D107" s="11"/>
+      <x:c r="E107" s="11"/>
+      <x:c r="F107" s="11"/>
+      <x:c r="G107" s="11"/>
+      <x:c r="H107" s="11"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="11"/>
+      <x:c r="B108" s="11"/>
+      <x:c r="C108" s="11"/>
+      <x:c r="D108" s="11"/>
+      <x:c r="E108" s="11"/>
+      <x:c r="F108" s="11"/>
+      <x:c r="G108" s="11"/>
+      <x:c r="H108" s="11"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="11"/>
+      <x:c r="B109" s="11"/>
+      <x:c r="C109" s="11"/>
+      <x:c r="D109" s="11"/>
+      <x:c r="E109" s="11"/>
+      <x:c r="F109" s="11"/>
+      <x:c r="G109" s="11"/>
+      <x:c r="H109" s="11"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="11"/>
+      <x:c r="B110" s="11"/>
+      <x:c r="C110" s="11"/>
+      <x:c r="D110" s="11"/>
+      <x:c r="E110" s="11"/>
+      <x:c r="F110" s="11"/>
+      <x:c r="G110" s="11"/>
+      <x:c r="H110" s="11"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="11"/>
+      <x:c r="B111" s="11"/>
+      <x:c r="C111" s="11"/>
+      <x:c r="D111" s="11"/>
+      <x:c r="E111" s="11"/>
+      <x:c r="F111" s="11"/>
+      <x:c r="G111" s="11"/>
+      <x:c r="H111" s="11"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="11"/>
+      <x:c r="B112" s="11"/>
+      <x:c r="C112" s="11"/>
+      <x:c r="D112" s="11"/>
+      <x:c r="E112" s="11"/>
+      <x:c r="F112" s="11"/>
+      <x:c r="G112" s="11"/>
+      <x:c r="H112" s="11"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="11"/>
+      <x:c r="B113" s="11"/>
+      <x:c r="C113" s="11"/>
+      <x:c r="D113" s="11"/>
+      <x:c r="E113" s="11"/>
+      <x:c r="F113" s="11"/>
+      <x:c r="G113" s="11"/>
+      <x:c r="H113" s="11"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="11"/>
+      <x:c r="B114" s="11"/>
+      <x:c r="C114" s="11"/>
+      <x:c r="D114" s="11"/>
+      <x:c r="E114" s="11"/>
+      <x:c r="F114" s="11"/>
+      <x:c r="G114" s="11"/>
+      <x:c r="H114" s="11"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="11"/>
+      <x:c r="B115" s="11"/>
+      <x:c r="C115" s="11"/>
+      <x:c r="D115" s="11"/>
+      <x:c r="E115" s="11"/>
+      <x:c r="F115" s="11"/>
+      <x:c r="G115" s="11"/>
+      <x:c r="H115" s="11"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="11"/>
+      <x:c r="B116" s="11"/>
+      <x:c r="C116" s="11"/>
+      <x:c r="D116" s="11"/>
+      <x:c r="E116" s="11"/>
+      <x:c r="F116" s="11"/>
+      <x:c r="G116" s="11"/>
+      <x:c r="H116" s="11"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="11"/>
+      <x:c r="B117" s="11"/>
+      <x:c r="C117" s="11"/>
+      <x:c r="D117" s="11"/>
+      <x:c r="E117" s="11"/>
+      <x:c r="F117" s="11"/>
+      <x:c r="G117" s="11"/>
+      <x:c r="H117" s="11"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="11"/>
+      <x:c r="B118" s="11"/>
+      <x:c r="C118" s="11"/>
+      <x:c r="D118" s="11"/>
+      <x:c r="E118" s="11"/>
+      <x:c r="F118" s="11"/>
+      <x:c r="G118" s="11"/>
+      <x:c r="H118" s="11"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="11"/>
+      <x:c r="B119" s="11"/>
+      <x:c r="C119" s="11"/>
+      <x:c r="D119" s="11"/>
+      <x:c r="E119" s="11"/>
+      <x:c r="F119" s="11"/>
+      <x:c r="G119" s="11"/>
+      <x:c r="H119" s="11"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="11"/>
+      <x:c r="B120" s="11"/>
+      <x:c r="C120" s="11"/>
+      <x:c r="D120" s="11"/>
+      <x:c r="E120" s="11"/>
+      <x:c r="F120" s="11"/>
+      <x:c r="G120" s="11"/>
+      <x:c r="H120" s="11"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="11"/>
+      <x:c r="B121" s="11"/>
+      <x:c r="C121" s="11"/>
+      <x:c r="D121" s="11"/>
+      <x:c r="E121" s="11"/>
+      <x:c r="F121" s="11"/>
+      <x:c r="G121" s="11"/>
+      <x:c r="H121" s="11"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="11"/>
+      <x:c r="B122" s="11"/>
+      <x:c r="C122" s="11"/>
+      <x:c r="D122" s="11"/>
+      <x:c r="E122" s="11"/>
+      <x:c r="F122" s="11"/>
+      <x:c r="G122" s="11"/>
+      <x:c r="H122" s="11"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="11"/>
+      <x:c r="B123" s="11"/>
+      <x:c r="C123" s="11"/>
+      <x:c r="D123" s="11"/>
+      <x:c r="E123" s="11"/>
+      <x:c r="F123" s="11"/>
+      <x:c r="G123" s="11"/>
+      <x:c r="H123" s="11"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="11"/>
+      <x:c r="B124" s="11"/>
+      <x:c r="C124" s="11"/>
+      <x:c r="D124" s="11"/>
+      <x:c r="E124" s="11"/>
+      <x:c r="F124" s="11"/>
+      <x:c r="G124" s="11"/>
+      <x:c r="H124" s="11"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="11"/>
+      <x:c r="B125" s="11"/>
+      <x:c r="C125" s="11"/>
+      <x:c r="D125" s="11"/>
+      <x:c r="E125" s="11"/>
+      <x:c r="F125" s="11"/>
+      <x:c r="G125" s="11"/>
+      <x:c r="H125" s="11"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="11"/>
+      <x:c r="B126" s="11"/>
+      <x:c r="C126" s="11"/>
+      <x:c r="D126" s="11"/>
+      <x:c r="E126" s="11"/>
+      <x:c r="F126" s="11"/>
+      <x:c r="G126" s="11"/>
+      <x:c r="H126" s="11"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="11"/>
+      <x:c r="B127" s="11"/>
+      <x:c r="C127" s="11"/>
+      <x:c r="D127" s="11"/>
+      <x:c r="E127" s="11"/>
+      <x:c r="F127" s="11"/>
+      <x:c r="G127" s="11"/>
+      <x:c r="H127" s="11"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="11"/>
+      <x:c r="B128" s="11"/>
+      <x:c r="C128" s="11"/>
+      <x:c r="D128" s="11"/>
+      <x:c r="E128" s="11"/>
+      <x:c r="F128" s="11"/>
+      <x:c r="G128" s="11"/>
+      <x:c r="H128" s="11"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="11"/>
+      <x:c r="B129" s="11"/>
+      <x:c r="C129" s="11"/>
+      <x:c r="D129" s="11"/>
+      <x:c r="E129" s="11"/>
+      <x:c r="F129" s="11"/>
+      <x:c r="G129" s="11"/>
+      <x:c r="H129" s="11"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="11"/>
+      <x:c r="B130" s="11"/>
+      <x:c r="C130" s="11"/>
+      <x:c r="D130" s="11"/>
+      <x:c r="E130" s="11"/>
+      <x:c r="F130" s="11"/>
+      <x:c r="G130" s="11"/>
+      <x:c r="H130" s="11"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="11"/>
+      <x:c r="B131" s="11"/>
+      <x:c r="C131" s="11"/>
+      <x:c r="D131" s="11"/>
+      <x:c r="E131" s="11"/>
+      <x:c r="F131" s="11"/>
+      <x:c r="G131" s="11"/>
+      <x:c r="H131" s="11"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="11"/>
+      <x:c r="B132" s="11"/>
+      <x:c r="C132" s="11"/>
+      <x:c r="D132" s="11"/>
+      <x:c r="E132" s="11"/>
+      <x:c r="F132" s="11"/>
+      <x:c r="G132" s="11"/>
+      <x:c r="H132" s="11"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="11"/>
+      <x:c r="B133" s="11"/>
+      <x:c r="C133" s="11"/>
+      <x:c r="D133" s="11"/>
+      <x:c r="E133" s="11"/>
+      <x:c r="F133" s="11"/>
+      <x:c r="G133" s="11"/>
+      <x:c r="H133" s="11"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="11"/>
+      <x:c r="B134" s="11"/>
+      <x:c r="C134" s="11"/>
+      <x:c r="D134" s="11"/>
+      <x:c r="E134" s="11"/>
+      <x:c r="F134" s="11"/>
+      <x:c r="G134" s="11"/>
+      <x:c r="H134" s="11"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="11"/>
+      <x:c r="B135" s="11"/>
+      <x:c r="C135" s="11"/>
+      <x:c r="D135" s="11"/>
+      <x:c r="E135" s="11"/>
+      <x:c r="F135" s="11"/>
+      <x:c r="G135" s="11"/>
+      <x:c r="H135" s="11"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="11"/>
+      <x:c r="B136" s="11"/>
+      <x:c r="C136" s="11"/>
+      <x:c r="D136" s="11"/>
+      <x:c r="E136" s="11"/>
+      <x:c r="F136" s="11"/>
+      <x:c r="G136" s="11"/>
+      <x:c r="H136" s="11"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="11"/>
+      <x:c r="B137" s="11"/>
+      <x:c r="C137" s="11"/>
+      <x:c r="D137" s="11"/>
+      <x:c r="E137" s="11"/>
+      <x:c r="F137" s="11"/>
+      <x:c r="G137" s="11"/>
+      <x:c r="H137" s="11"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="11"/>
+      <x:c r="B138" s="11"/>
+      <x:c r="C138" s="11"/>
+      <x:c r="D138" s="11"/>
+      <x:c r="E138" s="11"/>
+      <x:c r="F138" s="11"/>
+      <x:c r="G138" s="11"/>
+      <x:c r="H138" s="11"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="11"/>
+      <x:c r="B139" s="11"/>
+      <x:c r="C139" s="11"/>
+      <x:c r="D139" s="11"/>
+      <x:c r="E139" s="11"/>
+      <x:c r="F139" s="11"/>
+      <x:c r="G139" s="11"/>
+      <x:c r="H139" s="11"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="11"/>
+      <x:c r="B140" s="11"/>
+      <x:c r="C140" s="11"/>
+      <x:c r="D140" s="11"/>
+      <x:c r="E140" s="11"/>
+      <x:c r="F140" s="11"/>
+      <x:c r="G140" s="11"/>
+      <x:c r="H140" s="11"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="11"/>
+      <x:c r="B141" s="11"/>
+      <x:c r="C141" s="11"/>
+      <x:c r="D141" s="11"/>
+      <x:c r="E141" s="11"/>
+      <x:c r="F141" s="11"/>
+      <x:c r="G141" s="11"/>
+      <x:c r="H141" s="11"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="11"/>
+      <x:c r="B142" s="11"/>
+      <x:c r="C142" s="11"/>
+      <x:c r="D142" s="11"/>
+      <x:c r="E142" s="11"/>
+      <x:c r="F142" s="11"/>
+      <x:c r="G142" s="11"/>
+      <x:c r="H142" s="11"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="11"/>
+      <x:c r="B143" s="11"/>
+      <x:c r="C143" s="11"/>
+      <x:c r="D143" s="11"/>
+      <x:c r="E143" s="11"/>
+      <x:c r="F143" s="11"/>
+      <x:c r="G143" s="11"/>
+      <x:c r="H143" s="11"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="11"/>
+      <x:c r="B144" s="11"/>
+      <x:c r="C144" s="11"/>
+      <x:c r="D144" s="11"/>
+      <x:c r="E144" s="11"/>
+      <x:c r="F144" s="11"/>
+      <x:c r="G144" s="11"/>
+      <x:c r="H144" s="11"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="11"/>
+      <x:c r="B145" s="11"/>
+      <x:c r="C145" s="11"/>
+      <x:c r="D145" s="11"/>
+      <x:c r="E145" s="11"/>
+      <x:c r="F145" s="11"/>
+      <x:c r="G145" s="11"/>
+      <x:c r="H145" s="11"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="11"/>
+      <x:c r="B146" s="11"/>
+      <x:c r="C146" s="11"/>
+      <x:c r="D146" s="11"/>
+      <x:c r="E146" s="11"/>
+      <x:c r="F146" s="11"/>
+      <x:c r="G146" s="11"/>
+      <x:c r="H146" s="11"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="11"/>
+      <x:c r="B147" s="11"/>
+      <x:c r="C147" s="11"/>
+      <x:c r="D147" s="11"/>
+      <x:c r="E147" s="11"/>
+      <x:c r="F147" s="11"/>
+      <x:c r="G147" s="11"/>
+      <x:c r="H147" s="11"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="11"/>
+      <x:c r="B148" s="11"/>
+      <x:c r="C148" s="11"/>
+      <x:c r="D148" s="11"/>
+      <x:c r="E148" s="11"/>
+      <x:c r="F148" s="11"/>
+      <x:c r="G148" s="11"/>
+      <x:c r="H148" s="11"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="11"/>
+      <x:c r="B149" s="11"/>
+      <x:c r="C149" s="11"/>
+      <x:c r="D149" s="11"/>
+      <x:c r="E149" s="11"/>
+      <x:c r="F149" s="11"/>
+      <x:c r="G149" s="11"/>
+      <x:c r="H149" s="11"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="11"/>
+      <x:c r="B150" s="11"/>
+      <x:c r="C150" s="11"/>
+      <x:c r="D150" s="11"/>
+      <x:c r="E150" s="11"/>
+      <x:c r="F150" s="11"/>
+      <x:c r="G150" s="11"/>
+      <x:c r="H150" s="11"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="11"/>
+      <x:c r="B151" s="11"/>
+      <x:c r="C151" s="11"/>
+      <x:c r="D151" s="11"/>
+      <x:c r="E151" s="11"/>
+      <x:c r="F151" s="11"/>
+      <x:c r="G151" s="11"/>
+      <x:c r="H151" s="11"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="11"/>
+      <x:c r="B152" s="11"/>
+      <x:c r="C152" s="11"/>
+      <x:c r="D152" s="11"/>
+      <x:c r="E152" s="11"/>
+      <x:c r="F152" s="11"/>
+      <x:c r="G152" s="11"/>
+      <x:c r="H152" s="11"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="11"/>
+      <x:c r="B153" s="11"/>
+      <x:c r="C153" s="11"/>
+      <x:c r="D153" s="11"/>
+      <x:c r="E153" s="11"/>
+      <x:c r="F153" s="11"/>
+      <x:c r="G153" s="11"/>
+      <x:c r="H153" s="11"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="11"/>
+      <x:c r="B154" s="11"/>
+      <x:c r="C154" s="11"/>
+      <x:c r="D154" s="11"/>
+      <x:c r="E154" s="11"/>
+      <x:c r="F154" s="11"/>
+      <x:c r="G154" s="11"/>
+      <x:c r="H154" s="11"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="11"/>
+      <x:c r="B155" s="11"/>
+      <x:c r="C155" s="11"/>
+      <x:c r="D155" s="11"/>
+      <x:c r="E155" s="11"/>
+      <x:c r="F155" s="11"/>
+      <x:c r="G155" s="11"/>
+      <x:c r="H155" s="11"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="11"/>
+      <x:c r="B156" s="11"/>
+      <x:c r="C156" s="11"/>
+      <x:c r="D156" s="11"/>
+      <x:c r="E156" s="11"/>
+      <x:c r="F156" s="11"/>
+      <x:c r="G156" s="11"/>
+      <x:c r="H156" s="11"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="11"/>
+      <x:c r="B157" s="11"/>
+      <x:c r="C157" s="11"/>
+      <x:c r="D157" s="11"/>
+      <x:c r="E157" s="11"/>
+      <x:c r="F157" s="11"/>
+      <x:c r="G157" s="11"/>
+      <x:c r="H157" s="11"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="11"/>
+      <x:c r="B158" s="11"/>
+      <x:c r="C158" s="11"/>
+      <x:c r="D158" s="11"/>
+      <x:c r="E158" s="11"/>
+      <x:c r="F158" s="11"/>
+      <x:c r="G158" s="11"/>
+      <x:c r="H158" s="11"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="11"/>
+      <x:c r="B159" s="11"/>
+      <x:c r="C159" s="11"/>
+      <x:c r="D159" s="11"/>
+      <x:c r="E159" s="11"/>
+      <x:c r="F159" s="11"/>
+      <x:c r="G159" s="11"/>
+      <x:c r="H159" s="11"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="11"/>
+      <x:c r="B160" s="11"/>
+      <x:c r="C160" s="11"/>
+      <x:c r="D160" s="11"/>
+      <x:c r="E160" s="11"/>
+      <x:c r="F160" s="11"/>
+      <x:c r="G160" s="11"/>
+      <x:c r="H160" s="11"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="11"/>
+      <x:c r="B161" s="11"/>
+      <x:c r="C161" s="11"/>
+      <x:c r="D161" s="11"/>
+      <x:c r="E161" s="11"/>
+      <x:c r="F161" s="11"/>
+      <x:c r="G161" s="11"/>
+      <x:c r="H161" s="11"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="11"/>
+      <x:c r="B162" s="11"/>
+      <x:c r="C162" s="11"/>
+      <x:c r="D162" s="11"/>
+      <x:c r="E162" s="11"/>
+      <x:c r="F162" s="11"/>
+      <x:c r="G162" s="11"/>
+      <x:c r="H162" s="11"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="11"/>
+      <x:c r="B163" s="11"/>
+      <x:c r="C163" s="11"/>
+      <x:c r="D163" s="11"/>
+      <x:c r="E163" s="11"/>
+      <x:c r="F163" s="11"/>
+      <x:c r="G163" s="11"/>
+      <x:c r="H163" s="11"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="11"/>
+      <x:c r="B164" s="11"/>
+      <x:c r="C164" s="11"/>
+      <x:c r="D164" s="11"/>
+      <x:c r="E164" s="11"/>
+      <x:c r="F164" s="11"/>
+      <x:c r="G164" s="11"/>
+      <x:c r="H164" s="11"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="11"/>
+      <x:c r="B165" s="11"/>
+      <x:c r="C165" s="11"/>
+      <x:c r="D165" s="11"/>
+      <x:c r="E165" s="11"/>
+      <x:c r="F165" s="11"/>
+      <x:c r="G165" s="11"/>
+      <x:c r="H165" s="11"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="11"/>
+      <x:c r="B166" s="11"/>
+      <x:c r="C166" s="11"/>
+      <x:c r="D166" s="11"/>
+      <x:c r="E166" s="11"/>
+      <x:c r="F166" s="11"/>
+      <x:c r="G166" s="11"/>
+      <x:c r="H166" s="11"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="11"/>
+      <x:c r="B167" s="11"/>
+      <x:c r="C167" s="11"/>
+      <x:c r="D167" s="11"/>
+      <x:c r="E167" s="11"/>
+      <x:c r="F167" s="11"/>
+      <x:c r="G167" s="11"/>
+      <x:c r="H167" s="11"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="11"/>
+      <x:c r="B168" s="11"/>
+      <x:c r="C168" s="11"/>
+      <x:c r="D168" s="11"/>
+      <x:c r="E168" s="11"/>
+      <x:c r="F168" s="11"/>
+      <x:c r="G168" s="11"/>
+      <x:c r="H168" s="11"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="11"/>
+      <x:c r="B169" s="11"/>
+      <x:c r="C169" s="11"/>
+      <x:c r="D169" s="11"/>
+      <x:c r="E169" s="11"/>
+      <x:c r="F169" s="11"/>
+      <x:c r="G169" s="11"/>
+      <x:c r="H169" s="11"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="11"/>
+      <x:c r="B170" s="11"/>
+      <x:c r="C170" s="11"/>
+      <x:c r="D170" s="11"/>
+      <x:c r="E170" s="11"/>
+      <x:c r="F170" s="11"/>
+      <x:c r="G170" s="11"/>
+      <x:c r="H170" s="11"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="11"/>
+      <x:c r="B171" s="11"/>
+      <x:c r="C171" s="11"/>
+      <x:c r="D171" s="11"/>
+      <x:c r="E171" s="11"/>
+      <x:c r="F171" s="11"/>
+      <x:c r="G171" s="11"/>
+      <x:c r="H171" s="11"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="11"/>
+      <x:c r="B172" s="11"/>
+      <x:c r="C172" s="11"/>
+      <x:c r="D172" s="11"/>
+      <x:c r="E172" s="11"/>
+      <x:c r="F172" s="11"/>
+      <x:c r="G172" s="11"/>
+      <x:c r="H172" s="11"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="11"/>
+      <x:c r="B173" s="11"/>
+      <x:c r="C173" s="11"/>
+      <x:c r="D173" s="11"/>
+      <x:c r="E173" s="11"/>
+      <x:c r="F173" s="11"/>
+      <x:c r="G173" s="11"/>
+      <x:c r="H173" s="11"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="11"/>
+      <x:c r="B174" s="11"/>
+      <x:c r="C174" s="11"/>
+      <x:c r="D174" s="11"/>
+      <x:c r="E174" s="11"/>
+      <x:c r="F174" s="11"/>
+      <x:c r="G174" s="11"/>
+      <x:c r="H174" s="11"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="11"/>
+      <x:c r="B175" s="11"/>
+      <x:c r="C175" s="11"/>
+      <x:c r="D175" s="11"/>
+      <x:c r="E175" s="11"/>
+      <x:c r="F175" s="11"/>
+      <x:c r="G175" s="11"/>
+      <x:c r="H175" s="11"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="11"/>
+      <x:c r="B176" s="11"/>
+      <x:c r="C176" s="11"/>
+      <x:c r="D176" s="11"/>
+      <x:c r="E176" s="11"/>
+      <x:c r="F176" s="11"/>
+      <x:c r="G176" s="11"/>
+      <x:c r="H176" s="11"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="11"/>
+      <x:c r="B177" s="11"/>
+      <x:c r="C177" s="11"/>
+      <x:c r="D177" s="11"/>
+      <x:c r="E177" s="11"/>
+      <x:c r="F177" s="11"/>
+      <x:c r="G177" s="11"/>
+      <x:c r="H177" s="11"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="11"/>
+      <x:c r="B178" s="11"/>
+      <x:c r="C178" s="11"/>
+      <x:c r="D178" s="11"/>
+      <x:c r="E178" s="11"/>
+      <x:c r="F178" s="11"/>
+      <x:c r="G178" s="11"/>
+      <x:c r="H178" s="11"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="11"/>
+      <x:c r="B179" s="11"/>
+      <x:c r="C179" s="11"/>
+      <x:c r="D179" s="11"/>
+      <x:c r="E179" s="11"/>
+      <x:c r="F179" s="11"/>
+      <x:c r="G179" s="11"/>
+      <x:c r="H179" s="11"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="11"/>
+      <x:c r="B180" s="11"/>
+      <x:c r="C180" s="11"/>
+      <x:c r="D180" s="11"/>
+      <x:c r="E180" s="11"/>
+      <x:c r="F180" s="11"/>
+      <x:c r="G180" s="11"/>
+      <x:c r="H180" s="11"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="11"/>
+      <x:c r="B181" s="11"/>
+      <x:c r="C181" s="11"/>
+      <x:c r="D181" s="11"/>
+      <x:c r="E181" s="11"/>
+      <x:c r="F181" s="11"/>
+      <x:c r="G181" s="11"/>
+      <x:c r="H181" s="11"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="11"/>
+      <x:c r="B182" s="11"/>
+      <x:c r="C182" s="11"/>
+      <x:c r="D182" s="11"/>
+      <x:c r="E182" s="11"/>
+      <x:c r="F182" s="11"/>
+      <x:c r="G182" s="11"/>
+      <x:c r="H182" s="11"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="11"/>
+      <x:c r="B183" s="11"/>
+      <x:c r="C183" s="11"/>
+      <x:c r="D183" s="11"/>
+      <x:c r="E183" s="11"/>
+      <x:c r="F183" s="11"/>
+      <x:c r="G183" s="11"/>
+      <x:c r="H183" s="11"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="11"/>
+      <x:c r="B184" s="11"/>
+      <x:c r="C184" s="11"/>
+      <x:c r="D184" s="11"/>
+      <x:c r="E184" s="11"/>
+      <x:c r="F184" s="11"/>
+      <x:c r="G184" s="11"/>
+      <x:c r="H184" s="11"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="11"/>
+      <x:c r="B185" s="11"/>
+      <x:c r="C185" s="11"/>
+      <x:c r="D185" s="11"/>
+      <x:c r="E185" s="11"/>
+      <x:c r="F185" s="11"/>
+      <x:c r="G185" s="11"/>
+      <x:c r="H185" s="11"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="11"/>
+      <x:c r="B186" s="11"/>
+      <x:c r="C186" s="11"/>
+      <x:c r="D186" s="11"/>
+      <x:c r="E186" s="11"/>
+      <x:c r="F186" s="11"/>
+      <x:c r="G186" s="11"/>
+      <x:c r="H186" s="11"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="11"/>
+      <x:c r="B187" s="11"/>
+      <x:c r="C187" s="11"/>
+      <x:c r="D187" s="11"/>
+      <x:c r="E187" s="11"/>
+      <x:c r="F187" s="11"/>
+      <x:c r="G187" s="11"/>
+      <x:c r="H187" s="11"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="11"/>
+      <x:c r="B188" s="11"/>
+      <x:c r="C188" s="11"/>
+      <x:c r="D188" s="11"/>
+      <x:c r="E188" s="11"/>
+      <x:c r="F188" s="11"/>
+      <x:c r="G188" s="11"/>
+      <x:c r="H188" s="11"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="11"/>
+      <x:c r="B189" s="11"/>
+      <x:c r="C189" s="11"/>
+      <x:c r="D189" s="11"/>
+      <x:c r="E189" s="11"/>
+      <x:c r="F189" s="11"/>
+      <x:c r="G189" s="11"/>
+      <x:c r="H189" s="11"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="11"/>
+      <x:c r="B190" s="11"/>
+      <x:c r="C190" s="11"/>
+      <x:c r="D190" s="11"/>
+      <x:c r="E190" s="11"/>
+      <x:c r="F190" s="11"/>
+      <x:c r="G190" s="11"/>
+      <x:c r="H190" s="11"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="11"/>
+      <x:c r="B191" s="11"/>
+      <x:c r="C191" s="11"/>
+      <x:c r="D191" s="11"/>
+      <x:c r="E191" s="11"/>
+      <x:c r="F191" s="11"/>
+      <x:c r="G191" s="11"/>
+      <x:c r="H191" s="11"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="11"/>
+      <x:c r="B192" s="11"/>
+      <x:c r="C192" s="11"/>
+      <x:c r="D192" s="11"/>
+      <x:c r="E192" s="11"/>
+      <x:c r="F192" s="11"/>
+      <x:c r="G192" s="11"/>
+      <x:c r="H192" s="11"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="11"/>
+      <x:c r="B193" s="11"/>
+      <x:c r="C193" s="11"/>
+      <x:c r="D193" s="11"/>
+      <x:c r="E193" s="11"/>
+      <x:c r="F193" s="11"/>
+      <x:c r="G193" s="11"/>
+      <x:c r="H193" s="11"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="11"/>
+      <x:c r="B194" s="11"/>
+      <x:c r="C194" s="11"/>
+      <x:c r="D194" s="11"/>
+      <x:c r="E194" s="11"/>
+      <x:c r="F194" s="11"/>
+      <x:c r="G194" s="11"/>
+      <x:c r="H194" s="11"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="11"/>
+      <x:c r="B195" s="11"/>
+      <x:c r="C195" s="11"/>
+      <x:c r="D195" s="11"/>
+      <x:c r="E195" s="11"/>
+      <x:c r="F195" s="11"/>
+      <x:c r="G195" s="11"/>
+      <x:c r="H195" s="11"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="11"/>
+      <x:c r="B196" s="11"/>
+      <x:c r="C196" s="11"/>
+      <x:c r="D196" s="11"/>
+      <x:c r="E196" s="11"/>
+      <x:c r="F196" s="11"/>
+      <x:c r="G196" s="11"/>
+      <x:c r="H196" s="11"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="11"/>
+      <x:c r="B197" s="11"/>
+      <x:c r="C197" s="11"/>
+      <x:c r="D197" s="11"/>
+      <x:c r="E197" s="11"/>
+      <x:c r="F197" s="11"/>
+      <x:c r="G197" s="11"/>
+      <x:c r="H197" s="11"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="11"/>
+      <x:c r="B198" s="11"/>
+      <x:c r="C198" s="11"/>
+      <x:c r="D198" s="11"/>
+      <x:c r="E198" s="11"/>
+      <x:c r="F198" s="11"/>
+      <x:c r="G198" s="11"/>
+      <x:c r="H198" s="11"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="11"/>
+      <x:c r="B199" s="11"/>
+      <x:c r="C199" s="11"/>
+      <x:c r="D199" s="11"/>
+      <x:c r="E199" s="11"/>
+      <x:c r="F199" s="11"/>
+      <x:c r="G199" s="11"/>
+      <x:c r="H199" s="11"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="11"/>
+      <x:c r="B200" s="11"/>
+      <x:c r="C200" s="11"/>
+      <x:c r="D200" s="11"/>
+      <x:c r="E200" s="11"/>
+      <x:c r="F200" s="11"/>
+      <x:c r="G200" s="11"/>
+      <x:c r="H200" s="11"/>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="B2:B200">
+      <x:formula1>"main,flank,highground"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G2:G200">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="33" t="str">
+        <x:v>字段</x:v>
+      </x:c>
+      <x:c r="B1" s="33" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+      <x:c r="C1" s="33" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>maps.image_path</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>本版本已生成战术示意底图 SVG，也可替换成你自己的 PNG/JPG/SVG。</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>assets/maps/kings-row.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>map_routes.map</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>必须和 maps.name 完全一致。</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>国王大道</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>map_routes.route_type</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>main=主攻，flank=绕后，highground=高台。</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>main</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>map_routes.label</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>路线图例名称。</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>酒店侧路</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>map_routes.color</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>SVG 路线颜色。</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>#ef4444</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>map_routes.points</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>0–100 百分比坐标；对应本项目示意底图。</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>10,80;18,64;30,52;45,50;56,54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>map_routes.line_width</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>路线宽度。</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>2.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>map_routes.dashed</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>是否虚线。</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>map_routes.note</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>路线打法说明。</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>利用侧路避开主门枪线。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>map_routes.source</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>网上参考来源 URL。</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>https://game8.co/...</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>map_routes.basis</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>路线整理原则。</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>公开攻略 + 官方地图说明</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R9e7f795c3f094279"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R82b86f40873a4c2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Rd16353446cc940d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R78d6bc48f5894bfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R03884f3e8333474b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R9633441699e24555"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R2ecde5d78be149bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="Rd10d2d8537aa4348"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R3daf12e4be1b44fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R0d4c9acb2cf841d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Re585049992e5432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="Rd1582079aa6e4b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R363a742b9a454f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Rd7cebfe3f27649ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R28e517928e694c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R45ed766c2b154dc3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,12 +32,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -67,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="39">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -148,6 +153,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -385,7 +401,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.3.1</x:v>
+        <x:v>v3.3.2</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -20527,6 +20543,8 @@
     <x:col min="14" max="14" width="50" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="64" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="34" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="48" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -20578,6 +20596,12 @@
       <x:c r="P1" s="24" t="str">
         <x:v>image_path</x:v>
       </x:c>
+      <x:c r="Q1" s="38" t="str">
+        <x:v>image_credit</x:v>
+      </x:c>
+      <x:c r="R1" s="38" t="str">
+        <x:v>image_source</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
@@ -20626,7 +20650,13 @@
         <x:v>街道狭窄、拐角密集，正面推进和速度增益价值高。大锤体系容易形成稳定的资源交换，美可以封路分割。</x:v>
       </x:c>
       <x:c r="P2" s="11" t="str">
-        <x:v>assets/maps/kings-row.svg</x:v>
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1pskvTj33hpqgtTvcqTNi_EIfjCc0dAkq</x:v>
+      </x:c>
+      <x:c r="Q2" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. Free-use terms require non-commercial use and attribution/logo retention.</x:v>
+      </x:c>
+      <x:c r="R2" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -20678,6 +20708,8 @@
       <x:c r="P3" s="11" t="str">
         <x:v>assets/maps/gibraltar.svg</x:v>
       </x:c>
+      <x:c r="Q3" s="11"/>
+      <x:c r="R3" s="11"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
@@ -20726,6 +20758,8 @@
       <x:c r="P4" s="11" t="str">
         <x:v>assets/maps/circuit-royal.svg</x:v>
       </x:c>
+      <x:c r="Q4" s="11"/>
+      <x:c r="R4" s="11"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
@@ -20774,6 +20808,8 @@
       <x:c r="P5" s="11" t="str">
         <x:v>assets/maps/havana.svg</x:v>
       </x:c>
+      <x:c r="Q5" s="11"/>
+      <x:c r="R5" s="11"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
@@ -20824,6 +20860,8 @@
       <x:c r="P6" s="11" t="str">
         <x:v>assets/maps/route-66.svg</x:v>
       </x:c>
+      <x:c r="Q6" s="11"/>
+      <x:c r="R6" s="11"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
@@ -20874,6 +20912,8 @@
       <x:c r="P7" s="11" t="str">
         <x:v>assets/maps/junkertown.svg</x:v>
       </x:c>
+      <x:c r="Q7" s="11"/>
+      <x:c r="R7" s="11"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
@@ -20922,6 +20962,8 @@
       <x:c r="P8" s="11" t="str">
         <x:v>assets/maps/dorado.svg</x:v>
       </x:c>
+      <x:c r="Q8" s="11"/>
+      <x:c r="R8" s="11"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
@@ -20970,6 +21012,8 @@
       <x:c r="P9" s="11" t="str">
         <x:v>assets/maps/rialto.svg</x:v>
       </x:c>
+      <x:c r="Q9" s="11"/>
+      <x:c r="R9" s="11"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
@@ -21020,6 +21064,8 @@
       <x:c r="P10" s="11" t="str">
         <x:v>assets/maps/midtown.svg</x:v>
       </x:c>
+      <x:c r="Q10" s="11"/>
+      <x:c r="R10" s="11"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
@@ -21070,6 +21116,8 @@
       <x:c r="P11" s="11" t="str">
         <x:v>assets/maps/eichenwalde.svg</x:v>
       </x:c>
+      <x:c r="Q11" s="11"/>
+      <x:c r="R11" s="11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
@@ -21118,6 +21166,8 @@
       <x:c r="P12" s="11" t="str">
         <x:v>assets/maps/numbani.svg</x:v>
       </x:c>
+      <x:c r="Q12" s="11"/>
+      <x:c r="R12" s="11"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
@@ -21168,6 +21218,8 @@
       <x:c r="P13" s="11" t="str">
         <x:v>assets/maps/hollywood.svg</x:v>
       </x:c>
+      <x:c r="Q13" s="11"/>
+      <x:c r="R13" s="11"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
@@ -21218,6 +21270,8 @@
       <x:c r="P14" s="11" t="str">
         <x:v>assets/maps/ilios.svg</x:v>
       </x:c>
+      <x:c r="Q14" s="11"/>
+      <x:c r="R14" s="11"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
@@ -21268,6 +21322,8 @@
       <x:c r="P15" s="11" t="str">
         <x:v>assets/maps/lijiang-tower.svg</x:v>
       </x:c>
+      <x:c r="Q15" s="11"/>
+      <x:c r="R15" s="11"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
@@ -21318,6 +21374,8 @@
       <x:c r="P16" s="11" t="str">
         <x:v>assets/maps/nepal.svg</x:v>
       </x:c>
+      <x:c r="Q16" s="11"/>
+      <x:c r="R16" s="11"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
@@ -21368,6 +21426,8 @@
       <x:c r="P17" s="11" t="str">
         <x:v>assets/maps/busan.svg</x:v>
       </x:c>
+      <x:c r="Q17" s="11"/>
+      <x:c r="R17" s="11"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
@@ -21418,6 +21478,8 @@
       <x:c r="P18" s="11" t="str">
         <x:v>assets/maps/oasis.svg</x:v>
       </x:c>
+      <x:c r="Q18" s="11"/>
+      <x:c r="R18" s="11"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
@@ -21468,6 +21530,8 @@
       <x:c r="P19" s="11" t="str">
         <x:v>assets/maps/new-queen-street.svg</x:v>
       </x:c>
+      <x:c r="Q19" s="11"/>
+      <x:c r="R19" s="11"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
@@ -21518,6 +21582,8 @@
       <x:c r="P20" s="11" t="str">
         <x:v>assets/maps/colosseo.svg</x:v>
       </x:c>
+      <x:c r="Q20" s="11"/>
+      <x:c r="R20" s="11"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
@@ -21568,6 +21634,8 @@
       <x:c r="P21" s="11" t="str">
         <x:v>assets/maps/esperanca.svg</x:v>
       </x:c>
+      <x:c r="Q21" s="11"/>
+      <x:c r="R21" s="11"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
@@ -21618,6 +21686,8 @@
       <x:c r="P22" s="11" t="str">
         <x:v>assets/maps/suravasa.svg</x:v>
       </x:c>
+      <x:c r="Q22" s="11"/>
+      <x:c r="R22" s="11"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
@@ -21668,6 +21738,8 @@
       <x:c r="P23" s="11" t="str">
         <x:v>assets/maps/new-junk-city.svg</x:v>
       </x:c>
+      <x:c r="Q23" s="11"/>
+      <x:c r="R23" s="11"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
@@ -21718,6 +21790,8 @@
       <x:c r="P24" s="11" t="str">
         <x:v>assets/maps/aatlis.svg</x:v>
       </x:c>
+      <x:c r="Q24" s="11"/>
+      <x:c r="R24" s="11"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
@@ -21768,6 +21842,8 @@
       <x:c r="P25" s="11" t="str">
         <x:v>assets/maps/neon-junction.svg</x:v>
       </x:c>
+      <x:c r="Q25" s="11"/>
+      <x:c r="R25" s="11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22203,13 +22279,13 @@
         <x:v>main</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>主攻路线</x:v>
+        <x:v>主攻：正门→A点→运载终点</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
         <x:v>#f59e0b</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>8,82;20,75;34,66;46,58;58,54;72,46;92,34</x:v>
+        <x:v>91,76;83,70;77,65;72,61;68,58;62,51;55,46;48,39;40,31;32,25;23,20;16,15</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
         <x:v>3</x:v>
@@ -22218,13 +22294,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>第一段先通过正门压到雕像附近，再进入A点；不要长时间卡死在出生点正门。</x:v>
+        <x:v>从进攻出生沿正门进入雕像/门口区域，先取得A点空间；拿点后路线继续沿货车街道向上推进。主路适合抱团推进，但第一点不要五人直线顶门，应配合侧路或高台压力。</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>https://game8.co/games/Overwatch2/archives/391314</x:v>
+        <x:v>https://www.reddit.com/r/OverwatchUniversity/comments/qqcn9d</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str">
-        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+        <x:v>路线坐标按 StatBanana King's Row 实际俯视图重新校准；路线选择结合 King's Row 社区攻略中正门、Hotel、highground 的进攻思路。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -22235,13 +22311,13 @@
         <x:v>flank</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>绕后 / 侧路</x:v>
+        <x:v>侧路：酒店→A点侧面</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
         <x:v>#ef4444</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>10,80;18,64;30,52;45,50;56,54</x:v>
+        <x:v>90,77;82,79;75,74;70,68;66,61;62,56</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
         <x:v>2.6</x:v>
@@ -22250,13 +22326,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>酒店/侧路可以避开正门直线火力，适合机动英雄先制造侧面压力。</x:v>
+        <x:v>第一点从酒店一侧绕入，可以避开正门最集中的火力并逼防守方转身。更适合机动英雄或近战阵容用来建立第二进攻角。</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>https://www.pcgamesn.com/overwatch/overwatch-map-guide</x:v>
+        <x:v>https://www.reddit.com/r/OverwatchUniversity/comments/qqcn9d</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str">
-        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+        <x:v>路线坐标按 StatBanana King's Row 实际俯视图重新校准；路线选择结合 King's Row 社区攻略中正门、Hotel、highground 的进攻思路。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -22267,13 +22343,13 @@
         <x:v>highground</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>高台 / 优势角</x:v>
+        <x:v>高台：清高→街道推进</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>#38bdf8</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>57,54;67,44;77,38;87,44;93,58</x:v>
+        <x:v>71,63;66,55;59,48;52,42;44,35;36,29</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
         <x:v>2.8</x:v>
@@ -22282,13 +22358,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>进入运载阶段后优先清理街道和高台角度，再让车安全通过狭窄街区。</x:v>
+        <x:v>国王大道第一点和运载中段都不能忽略高台。先清高处输出角，再让主力沿货车路线推进，可以避免坦克在主路同时承受多个角度的火力。</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>https://mlog.uz/en/overwatch2/map-guide</x:v>
+        <x:v>https://www.reddit.com/r/OverwatchUniversity/comments/qqcn9d</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str">
-        <x:v>依据公开攻略、官方地图说明/改动与常见主路/侧路/高地打法整理；坐标对应本项目战术示意图，不是官方像素级平面图。</x:v>
+        <x:v>路线坐标按 StatBanana King's Row 实际俯视图重新校准；路线选择结合 King's Row 社区攻略中正门、Hotel、highground 的进攻思路。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R3daf12e4be1b44fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R0d4c9acb2cf841d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Re585049992e5432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="Rd1582079aa6e4b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R363a742b9a454f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Rd7cebfe3f27649ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R28e517928e694c61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R45ed766c2b154dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="Rcc03aff27ff34786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R0ddaa830f1d242da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Racec10827467474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R612c68789ca54895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R5fd27160d45345c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Re54ecc12fc8c4261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="Rf3a86d2f8c194762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R40918c260e514d53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,12 +32,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -72,7 +77,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -164,6 +169,14 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -401,7 +414,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.3.2</x:v>
+        <x:v>v3.3.4</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -20545,6 +20558,7 @@
     <x:col min="16" max="16" width="34" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="48" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="62" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -20602,6 +20616,9 @@
       <x:c r="R1" s="38" t="str">
         <x:v>image_source</x:v>
       </x:c>
+      <x:c r="S1" s="42" t="str">
+        <x:v>image_aspect</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
@@ -20650,13 +20667,16 @@
         <x:v>街道狭窄、拐角密集，正面推进和速度增益价值高。大锤体系容易形成稳定的资源交换，美可以封路分割。</x:v>
       </x:c>
       <x:c r="P2" s="11" t="str">
-        <x:v>https://drive.google.com/uc?export=view&amp;id=1pskvTj33hpqgtTvcqTNi_EIfjCc0dAkq</x:v>
+        <x:v>assets/maps/kings-row.png</x:v>
       </x:c>
       <x:c r="Q2" s="11" t="str">
-        <x:v>Overhead map courtesy of StatBanana / Coggle. Free-use terms require non-commercial use and attribution/logo retention.</x:v>
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 请从来源页下载 King's Row 地图后保存为 assets/maps/kings-row.png；保留原图 Logo 或页面署名。</x:v>
       </x:c>
       <x:c r="R2" s="11" t="str">
         <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
+      <x:c r="S2" t="str">
+        <x:v>1/1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -20710,6 +20730,9 @@
       </x:c>
       <x:c r="Q3" s="11"/>
       <x:c r="R3" s="11"/>
+      <x:c r="S3" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
@@ -20760,6 +20783,9 @@
       </x:c>
       <x:c r="Q4" s="11"/>
       <x:c r="R4" s="11"/>
+      <x:c r="S4" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
@@ -20810,6 +20836,9 @@
       </x:c>
       <x:c r="Q5" s="11"/>
       <x:c r="R5" s="11"/>
+      <x:c r="S5" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
@@ -20862,6 +20891,9 @@
       </x:c>
       <x:c r="Q6" s="11"/>
       <x:c r="R6" s="11"/>
+      <x:c r="S6" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
@@ -20914,6 +20946,9 @@
       </x:c>
       <x:c r="Q7" s="11"/>
       <x:c r="R7" s="11"/>
+      <x:c r="S7" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
@@ -20964,6 +20999,9 @@
       </x:c>
       <x:c r="Q8" s="11"/>
       <x:c r="R8" s="11"/>
+      <x:c r="S8" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
@@ -21014,6 +21052,9 @@
       </x:c>
       <x:c r="Q9" s="11"/>
       <x:c r="R9" s="11"/>
+      <x:c r="S9" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
@@ -21066,6 +21107,9 @@
       </x:c>
       <x:c r="Q10" s="11"/>
       <x:c r="R10" s="11"/>
+      <x:c r="S10" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
@@ -21118,6 +21162,9 @@
       </x:c>
       <x:c r="Q11" s="11"/>
       <x:c r="R11" s="11"/>
+      <x:c r="S11" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
@@ -21168,6 +21215,9 @@
       </x:c>
       <x:c r="Q12" s="11"/>
       <x:c r="R12" s="11"/>
+      <x:c r="S12" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
@@ -21220,6 +21270,9 @@
       </x:c>
       <x:c r="Q13" s="11"/>
       <x:c r="R13" s="11"/>
+      <x:c r="S13" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
@@ -21272,6 +21325,9 @@
       </x:c>
       <x:c r="Q14" s="11"/>
       <x:c r="R14" s="11"/>
+      <x:c r="S14" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
@@ -21324,6 +21380,9 @@
       </x:c>
       <x:c r="Q15" s="11"/>
       <x:c r="R15" s="11"/>
+      <x:c r="S15" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
@@ -21376,6 +21435,9 @@
       </x:c>
       <x:c r="Q16" s="11"/>
       <x:c r="R16" s="11"/>
+      <x:c r="S16" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
@@ -21428,6 +21490,9 @@
       </x:c>
       <x:c r="Q17" s="11"/>
       <x:c r="R17" s="11"/>
+      <x:c r="S17" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
@@ -21480,6 +21545,9 @@
       </x:c>
       <x:c r="Q18" s="11"/>
       <x:c r="R18" s="11"/>
+      <x:c r="S18" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
@@ -21532,6 +21600,9 @@
       </x:c>
       <x:c r="Q19" s="11"/>
       <x:c r="R19" s="11"/>
+      <x:c r="S19" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
@@ -21584,6 +21655,9 @@
       </x:c>
       <x:c r="Q20" s="11"/>
       <x:c r="R20" s="11"/>
+      <x:c r="S20" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
@@ -21636,6 +21710,9 @@
       </x:c>
       <x:c r="Q21" s="11"/>
       <x:c r="R21" s="11"/>
+      <x:c r="S21" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
@@ -21688,6 +21765,9 @@
       </x:c>
       <x:c r="Q22" s="11"/>
       <x:c r="R22" s="11"/>
+      <x:c r="S22" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
@@ -21740,6 +21820,9 @@
       </x:c>
       <x:c r="Q23" s="11"/>
       <x:c r="R23" s="11"/>
+      <x:c r="S23" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
@@ -21792,6 +21875,9 @@
       </x:c>
       <x:c r="Q24" s="11"/>
       <x:c r="R24" s="11"/>
+      <x:c r="S24" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
@@ -21844,6 +21930,9 @@
       </x:c>
       <x:c r="Q25" s="11"/>
       <x:c r="R25" s="11"/>
+      <x:c r="S25" t="str">
+        <x:v>1/1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="Rcc03aff27ff34786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R0ddaa830f1d242da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Racec10827467474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R612c68789ca54895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R5fd27160d45345c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Re54ecc12fc8c4261"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="Rf3a86d2f8c194762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R40918c260e514d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R28d43f9551df4a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Rbc4cd9fb66aa4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R9ae34b426dca495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="Rce1dce9b922447ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="Rac0b624f4b2642b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R93f42b50b5284f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R5bedcf097ca04f19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R5f224f3e11684e9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,12 +32,22 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -77,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="52">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -176,6 +186,25 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -414,7 +443,7 @@
         <x:v>version</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v3.3.4</x:v>
+        <x:v>v3.4.0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -20559,6 +20588,9 @@
     <x:col min="17" max="17" width="48" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="62" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="62" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="24" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -20619,6 +20651,15 @@
       <x:c r="S1" s="42" t="str">
         <x:v>image_aspect</x:v>
       </x:c>
+      <x:c r="T1" s="47" t="str">
+        <x:v>image_fallback</x:v>
+      </x:c>
+      <x:c r="U1" s="51" t="str">
+        <x:v>asset_status</x:v>
+      </x:c>
+      <x:c r="V1" s="51" t="str">
+        <x:v>asset_provider</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
@@ -20667,16 +20708,25 @@
         <x:v>街道狭窄、拐角密集，正面推进和速度增益价值高。大锤体系容易形成稳定的资源交换，美可以封路分割。</x:v>
       </x:c>
       <x:c r="P2" s="11" t="str">
-        <x:v>assets/maps/kings-row.png</x:v>
+        <x:v>assets/maps/real/kings-row.png</x:v>
       </x:c>
       <x:c r="Q2" s="11" t="str">
-        <x:v>Overhead map courtesy of StatBanana / Coggle. 请从来源页下载 King's Row 地图后保存为 assets/maps/kings-row.png；保留原图 Logo 或页面署名。</x:v>
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
       </x:c>
       <x:c r="R2" s="11" t="str">
         <x:v>https://overwatch.statbanana.com/images</x:v>
       </x:c>
       <x:c r="S2" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T2" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/kings.png</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V2" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -20726,12 +20776,25 @@
         <x:v>大量高台和垂直空间让机动坦克价值很高。进攻要抢高台，防守长枪位也非常强势。</x:v>
       </x:c>
       <x:c r="P3" s="11" t="str">
-        <x:v>assets/maps/gibraltar.svg</x:v>
-      </x:c>
-      <x:c r="Q3" s="11"/>
-      <x:c r="R3" s="11"/>
+        <x:v>assets/maps/real/gibraltar.png</x:v>
+      </x:c>
+      <x:c r="Q3" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R3" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S3" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T3" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/watchpoint.png</x:v>
+      </x:c>
+      <x:c r="U3" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V3" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -20786,6 +20849,13 @@
       <x:c r="S4" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T4" s="11"/>
+      <x:c r="U4" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V4" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
@@ -20839,6 +20909,13 @@
       <x:c r="S5" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T5" s="11"/>
+      <x:c r="U5" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V5" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
@@ -20887,12 +20964,25 @@
         <x:v>既有长视野也有高地与侧翼路线，机动性和远程输出都重要，阵容不宜过度偏科。</x:v>
       </x:c>
       <x:c r="P6" s="11" t="str">
-        <x:v>assets/maps/route-66.svg</x:v>
-      </x:c>
-      <x:c r="Q6" s="11"/>
-      <x:c r="R6" s="11"/>
+        <x:v>assets/maps/real/route-66.png</x:v>
+      </x:c>
+      <x:c r="Q6" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R6" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S6" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T6" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/route.png</x:v>
+      </x:c>
+      <x:c r="U6" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V6" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -20942,12 +21032,25 @@
         <x:v>第一段尤其开放，长枪和伤害增幅很强；后续区域则需要更注意近距离遭遇和高台争夺。</x:v>
       </x:c>
       <x:c r="P7" s="11" t="str">
-        <x:v>assets/maps/junkertown.svg</x:v>
-      </x:c>
-      <x:c r="Q7" s="11"/>
-      <x:c r="R7" s="11"/>
+        <x:v>assets/maps/real/junkertown.png</x:v>
+      </x:c>
+      <x:c r="Q7" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R7" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S7" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T7" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/junk.png</x:v>
+      </x:c>
+      <x:c r="U7" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V7" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -20995,12 +21098,25 @@
         <x:v>高台连贯且路线复杂，能快速上下高台的英雄更容易持续保持优势角度。</x:v>
       </x:c>
       <x:c r="P8" s="11" t="str">
-        <x:v>assets/maps/dorado.svg</x:v>
-      </x:c>
-      <x:c r="Q8" s="11"/>
-      <x:c r="R8" s="11"/>
+        <x:v>assets/maps/real/dorado.png</x:v>
+      </x:c>
+      <x:c r="Q8" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R8" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S8" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T8" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/dorado.png</x:v>
+      </x:c>
+      <x:c r="U8" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V8" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -21048,12 +21164,25 @@
         <x:v>桥口与狭窄入口很多，中远程消耗很强，但也需要防止侧翼从多个角度切入。</x:v>
       </x:c>
       <x:c r="P9" s="11" t="str">
-        <x:v>assets/maps/rialto.svg</x:v>
-      </x:c>
-      <x:c r="Q9" s="11"/>
-      <x:c r="R9" s="11"/>
+        <x:v>assets/maps/real/rialto.png</x:v>
+      </x:c>
+      <x:c r="Q9" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R9" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S9" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T9" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/rialto.png</x:v>
+      </x:c>
+      <x:c r="U9" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V9" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -21110,6 +21239,13 @@
       <x:c r="S10" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T10" s="11"/>
+      <x:c r="U10" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V10" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
@@ -21158,12 +21294,25 @@
         <x:v>第一阶段桥口适合正面推进；进入城堡后空间更紧，近战和控场价值进一步提高。</x:v>
       </x:c>
       <x:c r="P11" s="11" t="str">
-        <x:v>assets/maps/eichenwalde.svg</x:v>
-      </x:c>
-      <x:c r="Q11" s="11"/>
-      <x:c r="R11" s="11"/>
+        <x:v>assets/maps/real/eichenwalde.png</x:v>
+      </x:c>
+      <x:c r="Q11" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R11" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S11" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T11" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/eich.png</x:v>
+      </x:c>
+      <x:c r="U11" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V11" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -21211,12 +21360,25 @@
         <x:v>第一点高台非常关键，机动坦克能更快争夺射击位并帮助队友清理高地。</x:v>
       </x:c>
       <x:c r="P12" s="11" t="str">
-        <x:v>assets/maps/numbani.svg</x:v>
-      </x:c>
-      <x:c r="Q12" s="11"/>
-      <x:c r="R12" s="11"/>
+        <x:v>assets/maps/real/numbani.png</x:v>
+      </x:c>
+      <x:c r="Q12" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R12" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S12" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T12" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/numbani.png</x:v>
+      </x:c>
+      <x:c r="U12" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V12" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -21266,12 +21428,25 @@
         <x:v>从窄口到开放高台都有，阵容最好同时保留高地处理能力和稳定中距离火力。</x:v>
       </x:c>
       <x:c r="P13" s="11" t="str">
-        <x:v>assets/maps/hollywood.svg</x:v>
-      </x:c>
-      <x:c r="Q13" s="11"/>
-      <x:c r="R13" s="11"/>
+        <x:v>assets/maps/real/hollywood.png</x:v>
+      </x:c>
+      <x:c r="Q13" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R13" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S13" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T13" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/holly.png</x:v>
+      </x:c>
+      <x:c r="U13" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V13" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -21321,12 +21496,25 @@
         <x:v>不同子图差异较大，但整体很重视机动、抢点速度与地形利用。深井等区域尤其要防地形杀。</x:v>
       </x:c>
       <x:c r="P14" s="11" t="str">
-        <x:v>assets/maps/ilios.svg</x:v>
-      </x:c>
-      <x:c r="Q14" s="11"/>
-      <x:c r="R14" s="11"/>
+        <x:v>assets/maps/real/ilios.png</x:v>
+      </x:c>
+      <x:c r="Q14" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R14" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S14" t="str">
-        <x:v>1/1</x:v>
+        <x:v>2/1</x:v>
+      </x:c>
+      <x:c r="T14" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/ilios.png</x:v>
+      </x:c>
+      <x:c r="U14" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V14" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -21376,12 +21564,25 @@
         <x:v>控制点周围窄口明显，速度和近距离控场往往能直接决定第一波站位。</x:v>
       </x:c>
       <x:c r="P15" s="11" t="str">
-        <x:v>assets/maps/lijiang-tower.svg</x:v>
-      </x:c>
-      <x:c r="Q15" s="11"/>
-      <x:c r="R15" s="11"/>
+        <x:v>assets/maps/real/lijiang-tower.png</x:v>
+      </x:c>
+      <x:c r="Q15" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R15" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S15" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T15" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/lijiang.png</x:v>
+      </x:c>
+      <x:c r="U15" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V15" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -21431,12 +21632,25 @@
         <x:v>三张子图差异明显，推荐保留一定机动性，方便高低差和外围路线的争夺。</x:v>
       </x:c>
       <x:c r="P16" s="11" t="str">
-        <x:v>assets/maps/nepal.svg</x:v>
-      </x:c>
-      <x:c r="Q16" s="11"/>
-      <x:c r="R16" s="11"/>
+        <x:v>assets/maps/real/nepal.png</x:v>
+      </x:c>
+      <x:c r="Q16" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R16" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S16" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T16" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/nepal.png</x:v>
+      </x:c>
+      <x:c r="U16" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V16" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -21486,12 +21700,25 @@
         <x:v>多个子图有明显高地与开阔角度，D.Va和长枪都很容易找到发挥空间。</x:v>
       </x:c>
       <x:c r="P17" s="11" t="str">
-        <x:v>assets/maps/busan.svg</x:v>
-      </x:c>
-      <x:c r="Q17" s="11"/>
-      <x:c r="R17" s="11"/>
+        <x:v>assets/maps/real/busan.png</x:v>
+      </x:c>
+      <x:c r="Q17" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R17" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S17" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T17" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/busan.png</x:v>
+      </x:c>
+      <x:c r="U17" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V17" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -21541,12 +21768,25 @@
         <x:v>转点和侧翼路线丰富，快速切入后排、再迅速撤离的机动体系比较舒服。</x:v>
       </x:c>
       <x:c r="P18" s="11" t="str">
-        <x:v>assets/maps/oasis.svg</x:v>
-      </x:c>
-      <x:c r="Q18" s="11"/>
-      <x:c r="R18" s="11"/>
+        <x:v>assets/maps/real/oasis.png</x:v>
+      </x:c>
+      <x:c r="Q18" s="11" t="str">
+        <x:v>Overhead map courtesy of StatBanana / Coggle. 本项目自动生成带署名的本地派生图，用于非商业战术分析。</x:v>
+      </x:c>
+      <x:c r="R18" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/images</x:v>
+      </x:c>
       <x:c r="S18" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T18" s="11" t="str">
+        <x:v>https://overwatch.statbanana.com/static/whitethumbnail/oasis.png</x:v>
+      </x:c>
+      <x:c r="U18" t="str">
+        <x:v>自动下载实际俯视图</x:v>
+      </x:c>
+      <x:c r="V18" t="str">
+        <x:v>StatBanana / Coggle</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -21603,6 +21843,13 @@
       <x:c r="S19" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T19" s="11"/>
+      <x:c r="U19" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V19" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
@@ -21658,6 +21905,13 @@
       <x:c r="S20" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T20" s="11"/>
+      <x:c r="U20" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V20" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
@@ -21713,6 +21967,13 @@
       <x:c r="S21" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T21" s="11"/>
+      <x:c r="U21" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V21" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
@@ -21768,6 +22029,13 @@
       <x:c r="S22" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T22" s="11"/>
+      <x:c r="U22" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V22" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
@@ -21823,6 +22091,13 @@
       <x:c r="S23" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T23" s="11"/>
+      <x:c r="U23" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V23" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
@@ -21878,6 +22153,13 @@
       <x:c r="S24" t="str">
         <x:v>1/1</x:v>
       </x:c>
+      <x:c r="T24" s="11"/>
+      <x:c r="U24" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V24" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
@@ -21932,6 +22214,13 @@
       <x:c r="R25" s="11"/>
       <x:c r="S25" t="str">
         <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="T25" s="11"/>
+      <x:c r="U25" t="str">
+        <x:v>保留战术示意图</x:v>
+      </x:c>
+      <x:c r="V25" t="str">
+        <x:v>待可复用实际俯视图资源</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="Rc953efa9eaca4f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Rbcf39b0ca9554725"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Rf1adac9196aa43d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R8826bfa6078e47c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R2e722eb5cb9647ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R72b86307b5924bc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="Rad4921faa5aa46e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R05a194bd2da14dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R093a91ba5c1f4257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R5c5ce25173114183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R537b9e57c4b443a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R714a5c40b82245b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R08cea8712375401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Reba6588898d54a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R2beb7c71115046f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R07a5961507d848dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_comps" sheetId="9" r:id="R774a594acba142b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,12 +33,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -87,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
@@ -219,6 +225,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -513,7 +530,7 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="32" t="str">
-        <x:v>v3.6.1</x:v>
+        <x:v>v3.7.0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -32580,4 +32597,3021 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="48" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="58" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="58" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="64" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="B1" s="64" t="str">
+        <x:v>rank</x:v>
+      </x:c>
+      <x:c r="C1" s="64" t="str">
+        <x:v>style_name</x:v>
+      </x:c>
+      <x:c r="D1" s="64" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E1" s="64" t="str">
+        <x:v>dps1</x:v>
+      </x:c>
+      <x:c r="F1" s="64" t="str">
+        <x:v>dps2</x:v>
+      </x:c>
+      <x:c r="G1" s="64" t="str">
+        <x:v>support1</x:v>
+      </x:c>
+      <x:c r="H1" s="64" t="str">
+        <x:v>support2</x:v>
+      </x:c>
+      <x:c r="I1" s="64" t="str">
+        <x:v>lineup</x:v>
+      </x:c>
+      <x:c r="J1" s="64" t="str">
+        <x:v>use_when</x:v>
+      </x:c>
+      <x:c r="K1" s="64" t="str">
+        <x:v>core_play</x:v>
+      </x:c>
+      <x:c r="L1" s="64" t="str">
+        <x:v>engage</x:v>
+      </x:c>
+      <x:c r="M1" s="64" t="str">
+        <x:v>caution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="58" t="str">
+        <x:v>国王大道</x:v>
+      </x:c>
+      <x:c r="B2" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E2" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F2" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G2" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H2" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="I2" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 卡西迪 + 卢西奥 + 安娜</x:v>
+      </x:c>
+      <x:c r="J2" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“近中距离 / 拐角多 / 正面推进”环境。</x:v>
+      </x:c>
+      <x:c r="K2" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L2" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M2" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="58" t="str">
+        <x:v>国王大道</x:v>
+      </x:c>
+      <x:c r="B3" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="58" t="str">
+        <x:v>快速冲阵阵容</x:v>
+      </x:c>
+      <x:c r="D3" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E3" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F3" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G3" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H3" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I3" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 卡西迪 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J3" s="58" t="str">
+        <x:v>需要快速穿过窄口、拐角，或对面远程火力很强但缺少持续近战能力时。</x:v>
+      </x:c>
+      <x:c r="K3" s="58" t="str">
+        <x:v>莱因哈特用盾和身体带队跨过危险区域，美负责墙体分割，卢西奥提供加速让整队迅速接近；卡西迪补稳定近距离伤害。</x:v>
+      </x:c>
+      <x:c r="L3" s="58" t="str">
+        <x:v>看到对方有人站位靠前或与队友脱节时，卢西奥加速整队压上，美用冰墙切断退路，集中火力先解决被分割目标。</x:v>
+      </x:c>
+      <x:c r="M3" s="58" t="str">
+        <x:v>不要在远距离慢慢消耗。Rush阵容价值来自快速接敌；如果队友跟不上加速，就宁可等齐再进。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="58" t="str">
+        <x:v>国王大道</x:v>
+      </x:c>
+      <x:c r="B4" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E4" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F4" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G4" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H4" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I4" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J4" s="58" t="str">
+        <x:v>对面抱团很难正面突破，或者需要快速抢高台、绕过正面坦克时。</x:v>
+      </x:c>
+      <x:c r="K4" s="58" t="str">
+        <x:v>温斯顿先占高地或跳后排，源氏与猎空分别从两侧切入；安娜远程支援，雾子可以跟进并用铃保护撤退。</x:v>
+      </x:c>
+      <x:c r="L4" s="58" t="str">
+        <x:v>先让侧翼找到角度，等温斯顿落点后再同时压同一名辅助或长枪。击杀后不要深追，优先回到高地和关键位置。</x:v>
+      </x:c>
+      <x:c r="M4" s="58" t="str">
+        <x:v>避免跳到对方五人正中间。先确认敌方控制技能和保命技能，再选择目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="58" t="str">
+        <x:v>直布罗陀</x:v>
+      </x:c>
+      <x:c r="B5" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D5" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E5" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F5" s="58" t="str">
+        <x:v>黑百合</x:v>
+      </x:c>
+      <x:c r="G5" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H5" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I5" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 黑百合 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J5" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“高台多 / 垂直机动 / 长枪”环境。</x:v>
+      </x:c>
+      <x:c r="K5" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L5" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M5" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="58" t="str">
+        <x:v>直布罗陀</x:v>
+      </x:c>
+      <x:c r="B6" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="58" t="str">
+        <x:v>远程消耗阵容</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E6" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F6" s="58" t="str">
+        <x:v>半藏</x:v>
+      </x:c>
+      <x:c r="G6" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="H6" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I6" s="58" t="str">
+        <x:v>西格玛 + 艾什 + 半藏 + 巴蒂斯特 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J6" s="58" t="str">
+        <x:v>对面缺乏强 Dive，或者己方长枪手感好、想通过远距离先建立人数差时。</x:v>
+      </x:c>
+      <x:c r="K6" s="58" t="str">
+        <x:v>西格玛负责占住主路与远端角度，双远程输出分开站位形成交叉枪线；辅助优先保证输出位能持续站高台或长视野位置。</x:v>
+      </x:c>
+      <x:c r="L6" s="58" t="str">
+        <x:v>不要急着冲点。先用远程伤害逼掉治疗、位移和屏障资源，打残或击杀一人后再推进目标。</x:v>
+      </x:c>
+      <x:c r="M6" s="58" t="str">
+        <x:v>最怕温斯顿/D.Va/源氏等同时扑后排。被连续切入时要及时收缩站位，必要时切换机动或反 Dive 英雄。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="58" t="str">
+        <x:v>直布罗陀</x:v>
+      </x:c>
+      <x:c r="B7" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D7" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E7" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F7" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G7" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H7" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I7" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J7" s="58" t="str">
+        <x:v>对方长枪站得很散、高台很强，正面消耗很难获得优势时。</x:v>
+      </x:c>
+      <x:c r="K7" s="58" t="str">
+        <x:v>D.Va先吃掉关键爆发并接近高台，源氏和回声从不同高度压后排；安娜提供远程治疗与禁疗，雾子负责跟进和救场。</x:v>
+      </x:c>
+      <x:c r="L7" s="58" t="str">
+        <x:v>等待对方位移或防守技能出现空档后，D.Va先接触目标，两个输出同步压同一个后排，拿到击杀后立即撤出再循环。</x:v>
+      </x:c>
+      <x:c r="M7" s="58" t="str">
+        <x:v>不要一人提前进场。Dive阵容最怕进场时间不一致；如果第一波没秒人，应迅速退出而不是在对方阵型里久留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="58" t="str">
+        <x:v>皇家赛道</x:v>
+      </x:c>
+      <x:c r="B8" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E8" s="58" t="str">
+        <x:v>黑百合</x:v>
+      </x:c>
+      <x:c r="F8" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="G8" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="H8" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I8" s="58" t="str">
+        <x:v>西格玛 + 黑百合 + 艾什 + 巴蒂斯特 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J8" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“超长视野 / 长枪 / 高地”环境。</x:v>
+      </x:c>
+      <x:c r="K8" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L8" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M8" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="58" t="str">
+        <x:v>皇家赛道</x:v>
+      </x:c>
+      <x:c r="B9" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" s="58" t="str">
+        <x:v>远程消耗阵容</x:v>
+      </x:c>
+      <x:c r="D9" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E9" s="58" t="str">
+        <x:v>黑百合</x:v>
+      </x:c>
+      <x:c r="F9" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="G9" s="58" t="str">
+        <x:v>天使</x:v>
+      </x:c>
+      <x:c r="H9" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I9" s="58" t="str">
+        <x:v>西格玛 + 黑百合 + 艾什 + 天使 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J9" s="58" t="str">
+        <x:v>对面缺乏强 Dive，或者己方长枪手感好、想通过远距离先建立人数差时。</x:v>
+      </x:c>
+      <x:c r="K9" s="58" t="str">
+        <x:v>西格玛负责占住主路与远端角度，双远程输出分开站位形成交叉枪线；辅助优先保证输出位能持续站高台或长视野位置。</x:v>
+      </x:c>
+      <x:c r="L9" s="58" t="str">
+        <x:v>不要急着冲点。先用远程伤害逼掉治疗、位移和屏障资源，打残或击杀一人后再推进目标。</x:v>
+      </x:c>
+      <x:c r="M9" s="58" t="str">
+        <x:v>最怕温斯顿/D.Va/源氏等同时扑后排。被连续切入时要及时收缩站位，必要时切换机动或反 Dive 英雄。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="58" t="str">
+        <x:v>皇家赛道</x:v>
+      </x:c>
+      <x:c r="B10" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D10" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E10" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F10" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G10" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H10" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I10" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J10" s="58" t="str">
+        <x:v>对方长枪站得很散、高台很强，正面消耗很难获得优势时。</x:v>
+      </x:c>
+      <x:c r="K10" s="58" t="str">
+        <x:v>D.Va先吃掉关键爆发并接近高台，源氏和回声从不同高度压后排；安娜提供远程治疗与禁疗，雾子负责跟进和救场。</x:v>
+      </x:c>
+      <x:c r="L10" s="58" t="str">
+        <x:v>等待对方位移或防守技能出现空档后，D.Va先接触目标，两个输出同步压同一个后排，拿到击杀后立即撤出再循环。</x:v>
+      </x:c>
+      <x:c r="M10" s="58" t="str">
+        <x:v>不要一人提前进场。Dive阵容最怕进场时间不一致；如果第一波没秒人，应迅速退出而不是在对方阵型里久留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="58" t="str">
+        <x:v>哈瓦那</x:v>
+      </x:c>
+      <x:c r="B11" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D11" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E11" s="58" t="str">
+        <x:v>黑百合</x:v>
+      </x:c>
+      <x:c r="F11" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="G11" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="H11" s="58" t="str">
+        <x:v>天使</x:v>
+      </x:c>
+      <x:c r="I11" s="58" t="str">
+        <x:v>西格玛 + 黑百合 + 艾什 + 巴蒂斯特 + 天使</x:v>
+      </x:c>
+      <x:c r="J11" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“长枪 / 远程压制”环境。</x:v>
+      </x:c>
+      <x:c r="K11" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L11" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M11" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="58" t="str">
+        <x:v>哈瓦那</x:v>
+      </x:c>
+      <x:c r="B12" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C12" s="58" t="str">
+        <x:v>远程消耗阵容</x:v>
+      </x:c>
+      <x:c r="D12" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E12" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F12" s="58" t="str">
+        <x:v>半藏</x:v>
+      </x:c>
+      <x:c r="G12" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="H12" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I12" s="58" t="str">
+        <x:v>西格玛 + 艾什 + 半藏 + 巴蒂斯特 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J12" s="58" t="str">
+        <x:v>对面缺乏强 Dive，或者己方长枪手感好、想通过远距离先建立人数差时。</x:v>
+      </x:c>
+      <x:c r="K12" s="58" t="str">
+        <x:v>西格玛负责占住主路与远端角度，双远程输出分开站位形成交叉枪线；辅助优先保证输出位能持续站高台或长视野位置。</x:v>
+      </x:c>
+      <x:c r="L12" s="58" t="str">
+        <x:v>不要急着冲点。先用远程伤害逼掉治疗、位移和屏障资源，打残或击杀一人后再推进目标。</x:v>
+      </x:c>
+      <x:c r="M12" s="58" t="str">
+        <x:v>最怕温斯顿/D.Va/源氏等同时扑后排。被连续切入时要及时收缩站位，必要时切换机动或反 Dive 英雄。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="58" t="str">
+        <x:v>哈瓦那</x:v>
+      </x:c>
+      <x:c r="B13" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C13" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D13" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E13" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F13" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G13" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H13" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I13" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J13" s="58" t="str">
+        <x:v>对方长枪站得很散、高台很强，正面消耗很难获得优势时。</x:v>
+      </x:c>
+      <x:c r="K13" s="58" t="str">
+        <x:v>D.Va先吃掉关键爆发并接近高台，源氏和回声从不同高度压后排；安娜提供远程治疗与禁疗，雾子负责跟进和救场。</x:v>
+      </x:c>
+      <x:c r="L13" s="58" t="str">
+        <x:v>等待对方位移或防守技能出现空档后，D.Va先接触目标，两个输出同步压同一个后排，拿到击杀后立即撤出再循环。</x:v>
+      </x:c>
+      <x:c r="M13" s="58" t="str">
+        <x:v>不要一人提前进场。Dive阵容最怕进场时间不一致；如果第一波没秒人，应迅速退出而不是在对方阵型里久留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="58" t="str">
+        <x:v>66号公路</x:v>
+      </x:c>
+      <x:c r="B14" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D14" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E14" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F14" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G14" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H14" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I14" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J14" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“中远距离 / 高地争夺”环境。</x:v>
+      </x:c>
+      <x:c r="K14" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L14" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M14" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="58" t="str">
+        <x:v>66号公路</x:v>
+      </x:c>
+      <x:c r="B15" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C15" s="58" t="str">
+        <x:v>高台机动阵容</x:v>
+      </x:c>
+      <x:c r="D15" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E15" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F15" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G15" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H15" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I15" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J15" s="58" t="str">
+        <x:v>地图高低差明显、对方远端输出站高台，或者需要快速转换多个角度时。</x:v>
+      </x:c>
+      <x:c r="K15" s="58" t="str">
+        <x:v>D.Va与回声利用垂直机动抢占高处，源氏从侧翼补压；安娜在安全长线支援，雾子负责跟进与解控。</x:v>
+      </x:c>
+      <x:c r="L15" s="58" t="str">
+        <x:v>先抢高台再打点。D.Va逼退高台目标后，回声和源氏立刻扩大角度，形成主路+侧面的双向压力。</x:v>
+      </x:c>
+      <x:c r="M15" s="58" t="str">
+        <x:v>不要为了追击从高台全部跳下。很多地图的优势来自高度本身，拿到击杀后优先保住高地。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="58" t="str">
+        <x:v>66号公路</x:v>
+      </x:c>
+      <x:c r="B16" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C16" s="58" t="str">
+        <x:v>正面稳定阵容</x:v>
+      </x:c>
+      <x:c r="D16" s="58" t="str">
+        <x:v>拉玛刹</x:v>
+      </x:c>
+      <x:c r="E16" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F16" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G16" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H16" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="I16" s="58" t="str">
+        <x:v>拉玛刹 + 美 + 卡西迪 + 卢西奥 + 巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="J16" s="58" t="str">
+        <x:v>对面机动英雄很多但击杀效率不高，或者己方更擅长抱团推进时。</x:v>
+      </x:c>
+      <x:c r="K16" s="58" t="str">
+        <x:v>拉玛刹负责持续压迫正面，美限制机动英雄撤退路线，卡西迪保护后排并补单点爆发；卢西奥帮助整队快速进退。</x:v>
+      </x:c>
+      <x:c r="L16" s="58" t="str">
+        <x:v>等对方Dive英雄先交位移，再利用减速、控制和近距离火力反打；建立人数优势后再整体推进目标。</x:v>
+      </x:c>
+      <x:c r="M16" s="58" t="str">
+        <x:v>不要把所有控制技能交给坦克。应优先留给真正切入后排的源氏、猎空、温斯顿等目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="58" t="str">
+        <x:v>渣客镇</x:v>
+      </x:c>
+      <x:c r="B17" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D17" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E17" s="58" t="str">
+        <x:v>黑百合</x:v>
+      </x:c>
+      <x:c r="F17" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="G17" s="58" t="str">
+        <x:v>天使</x:v>
+      </x:c>
+      <x:c r="H17" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I17" s="58" t="str">
+        <x:v>西格玛 + 黑百合 + 艾什 + 天使 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J17" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“开放 / 长枪 / 侧翼”环境。</x:v>
+      </x:c>
+      <x:c r="K17" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L17" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M17" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="58" t="str">
+        <x:v>渣客镇</x:v>
+      </x:c>
+      <x:c r="B18" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C18" s="58" t="str">
+        <x:v>远程消耗阵容</x:v>
+      </x:c>
+      <x:c r="D18" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E18" s="58" t="str">
+        <x:v>黑百合</x:v>
+      </x:c>
+      <x:c r="F18" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="G18" s="58" t="str">
+        <x:v>天使</x:v>
+      </x:c>
+      <x:c r="H18" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I18" s="58" t="str">
+        <x:v>西格玛 + 黑百合 + 艾什 + 天使 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J18" s="58" t="str">
+        <x:v>对面缺乏强 Dive，或者己方长枪手感好、想通过远距离先建立人数差时。</x:v>
+      </x:c>
+      <x:c r="K18" s="58" t="str">
+        <x:v>西格玛负责占住主路与远端角度，双远程输出分开站位形成交叉枪线；辅助优先保证输出位能持续站高台或长视野位置。</x:v>
+      </x:c>
+      <x:c r="L18" s="58" t="str">
+        <x:v>不要急着冲点。先用远程伤害逼掉治疗、位移和屏障资源，打残或击杀一人后再推进目标。</x:v>
+      </x:c>
+      <x:c r="M18" s="58" t="str">
+        <x:v>最怕温斯顿/D.Va/源氏等同时扑后排。被连续切入时要及时收缩站位，必要时切换机动或反 Dive 英雄。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="58" t="str">
+        <x:v>渣客镇</x:v>
+      </x:c>
+      <x:c r="B19" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C19" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D19" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E19" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F19" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G19" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H19" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I19" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J19" s="58" t="str">
+        <x:v>对方长枪站得很散、高台很强，正面消耗很难获得优势时。</x:v>
+      </x:c>
+      <x:c r="K19" s="58" t="str">
+        <x:v>D.Va先吃掉关键爆发并接近高台，源氏和回声从不同高度压后排；安娜提供远程治疗与禁疗，雾子负责跟进和救场。</x:v>
+      </x:c>
+      <x:c r="L19" s="58" t="str">
+        <x:v>等待对方位移或防守技能出现空档后，D.Va先接触目标，两个输出同步压同一个后排，拿到击杀后立即撤出再循环。</x:v>
+      </x:c>
+      <x:c r="M19" s="58" t="str">
+        <x:v>不要一人提前进场。Dive阵容最怕进场时间不一致；如果第一波没秒人，应迅速退出而不是在对方阵型里久留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="58" t="str">
+        <x:v>多拉多</x:v>
+      </x:c>
+      <x:c r="B20" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D20" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E20" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F20" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="G20" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H20" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I20" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 艾什 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J20" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“高台 / 机动 / 中距离”环境。</x:v>
+      </x:c>
+      <x:c r="K20" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L20" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M20" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="58" t="str">
+        <x:v>多拉多</x:v>
+      </x:c>
+      <x:c r="B21" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C21" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D21" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E21" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F21" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G21" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H21" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I21" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J21" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K21" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L21" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M21" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="58" t="str">
+        <x:v>多拉多</x:v>
+      </x:c>
+      <x:c r="B22" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D22" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E22" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F22" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G22" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H22" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I22" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J22" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K22" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L22" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M22" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="58" t="str">
+        <x:v>里阿尔托</x:v>
+      </x:c>
+      <x:c r="B23" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C23" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D23" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E23" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F23" s="58" t="str">
+        <x:v>半藏</x:v>
+      </x:c>
+      <x:c r="G23" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="H23" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I23" s="58" t="str">
+        <x:v>西格玛 + 艾什 + 半藏 + 巴蒂斯特 + 雾子</x:v>
+      </x:c>
+      <x:c r="J23" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“中远距离 / 桥口 / 侧翼”环境。</x:v>
+      </x:c>
+      <x:c r="K23" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L23" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M23" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="58" t="str">
+        <x:v>里阿尔托</x:v>
+      </x:c>
+      <x:c r="B24" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="58" t="str">
+        <x:v>快速冲阵阵容</x:v>
+      </x:c>
+      <x:c r="D24" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E24" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F24" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G24" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H24" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I24" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 卡西迪 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J24" s="58" t="str">
+        <x:v>需要快速穿过窄口、拐角，或对面远程火力很强但缺少持续近战能力时。</x:v>
+      </x:c>
+      <x:c r="K24" s="58" t="str">
+        <x:v>莱因哈特用盾和身体带队跨过危险区域，美负责墙体分割，卢西奥提供加速让整队迅速接近；卡西迪补稳定近距离伤害。</x:v>
+      </x:c>
+      <x:c r="L24" s="58" t="str">
+        <x:v>看到对方有人站位靠前或与队友脱节时，卢西奥加速整队压上，美用冰墙切断退路，集中火力先解决被分割目标。</x:v>
+      </x:c>
+      <x:c r="M24" s="58" t="str">
+        <x:v>不要在远距离慢慢消耗。Rush阵容价值来自快速接敌；如果队友跟不上加速，就宁可等齐再进。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="58" t="str">
+        <x:v>里阿尔托</x:v>
+      </x:c>
+      <x:c r="B25" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C25" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D25" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E25" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F25" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G25" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H25" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I25" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J25" s="58" t="str">
+        <x:v>对面抱团很难正面突破，或者需要快速抢高台、绕过正面坦克时。</x:v>
+      </x:c>
+      <x:c r="K25" s="58" t="str">
+        <x:v>温斯顿先占高地或跳后排，源氏与猎空分别从两侧切入；安娜远程支援，雾子可以跟进并用铃保护撤退。</x:v>
+      </x:c>
+      <x:c r="L25" s="58" t="str">
+        <x:v>先让侧翼找到角度，等温斯顿落点后再同时压同一名辅助或长枪。击杀后不要深追，优先回到高地和关键位置。</x:v>
+      </x:c>
+      <x:c r="M25" s="58" t="str">
+        <x:v>避免跳到对方五人正中间。先确认敌方控制技能和保命技能，再选择目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="58" t="str">
+        <x:v>中城</x:v>
+      </x:c>
+      <x:c r="B26" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D26" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E26" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F26" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G26" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H26" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I26" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J26" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“中距离 / 高地 / 拐角”环境。</x:v>
+      </x:c>
+      <x:c r="K26" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L26" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M26" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="58" t="str">
+        <x:v>中城</x:v>
+      </x:c>
+      <x:c r="B27" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C27" s="58" t="str">
+        <x:v>快速冲阵阵容</x:v>
+      </x:c>
+      <x:c r="D27" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E27" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F27" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G27" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H27" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I27" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 卡西迪 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J27" s="58" t="str">
+        <x:v>需要快速穿过窄口、拐角，或对面远程火力很强但缺少持续近战能力时。</x:v>
+      </x:c>
+      <x:c r="K27" s="58" t="str">
+        <x:v>莱因哈特用盾和身体带队跨过危险区域，美负责墙体分割，卢西奥提供加速让整队迅速接近；卡西迪补稳定近距离伤害。</x:v>
+      </x:c>
+      <x:c r="L27" s="58" t="str">
+        <x:v>看到对方有人站位靠前或与队友脱节时，卢西奥加速整队压上，美用冰墙切断退路，集中火力先解决被分割目标。</x:v>
+      </x:c>
+      <x:c r="M27" s="58" t="str">
+        <x:v>不要在远距离慢慢消耗。Rush阵容价值来自快速接敌；如果队友跟不上加速，就宁可等齐再进。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="58" t="str">
+        <x:v>中城</x:v>
+      </x:c>
+      <x:c r="B28" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C28" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D28" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E28" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F28" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G28" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H28" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I28" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J28" s="58" t="str">
+        <x:v>对面抱团很难正面突破，或者需要快速抢高台、绕过正面坦克时。</x:v>
+      </x:c>
+      <x:c r="K28" s="58" t="str">
+        <x:v>温斯顿先占高地或跳后排，源氏与猎空分别从两侧切入；安娜远程支援，雾子可以跟进并用铃保护撤退。</x:v>
+      </x:c>
+      <x:c r="L28" s="58" t="str">
+        <x:v>先让侧翼找到角度，等温斯顿落点后再同时压同一名辅助或长枪。击杀后不要深追，优先回到高地和关键位置。</x:v>
+      </x:c>
+      <x:c r="M28" s="58" t="str">
+        <x:v>避免跳到对方五人正中间。先确认敌方控制技能和保命技能，再选择目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="58" t="str">
+        <x:v>艾兴瓦尔德</x:v>
+      </x:c>
+      <x:c r="B29" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D29" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E29" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F29" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G29" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H29" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="I29" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 源氏 + 卢西奥 + 安娜</x:v>
+      </x:c>
+      <x:c r="J29" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“桥口 / 近战 / 高地”环境。</x:v>
+      </x:c>
+      <x:c r="K29" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L29" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M29" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="58" t="str">
+        <x:v>艾兴瓦尔德</x:v>
+      </x:c>
+      <x:c r="B30" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C30" s="58" t="str">
+        <x:v>快速冲阵阵容</x:v>
+      </x:c>
+      <x:c r="D30" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E30" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F30" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G30" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H30" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I30" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 卡西迪 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J30" s="58" t="str">
+        <x:v>需要快速穿过窄口、拐角，或对面远程火力很强但缺少持续近战能力时。</x:v>
+      </x:c>
+      <x:c r="K30" s="58" t="str">
+        <x:v>莱因哈特用盾和身体带队跨过危险区域，美负责墙体分割，卢西奥提供加速让整队迅速接近；卡西迪补稳定近距离伤害。</x:v>
+      </x:c>
+      <x:c r="L30" s="58" t="str">
+        <x:v>看到对方有人站位靠前或与队友脱节时，卢西奥加速整队压上，美用冰墙切断退路，集中火力先解决被分割目标。</x:v>
+      </x:c>
+      <x:c r="M30" s="58" t="str">
+        <x:v>不要在远距离慢慢消耗。Rush阵容价值来自快速接敌；如果队友跟不上加速，就宁可等齐再进。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="58" t="str">
+        <x:v>艾兴瓦尔德</x:v>
+      </x:c>
+      <x:c r="B31" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C31" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D31" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E31" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F31" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G31" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H31" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I31" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J31" s="58" t="str">
+        <x:v>对面抱团很难正面突破，或者需要快速抢高台、绕过正面坦克时。</x:v>
+      </x:c>
+      <x:c r="K31" s="58" t="str">
+        <x:v>温斯顿先占高地或跳后排，源氏与猎空分别从两侧切入；安娜远程支援，雾子可以跟进并用铃保护撤退。</x:v>
+      </x:c>
+      <x:c r="L31" s="58" t="str">
+        <x:v>先让侧翼找到角度，等温斯顿落点后再同时压同一名辅助或长枪。击杀后不要深追，优先回到高地和关键位置。</x:v>
+      </x:c>
+      <x:c r="M31" s="58" t="str">
+        <x:v>避免跳到对方五人正中间。先确认敌方控制技能和保命技能，再选择目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="58" t="str">
+        <x:v>努巴尼</x:v>
+      </x:c>
+      <x:c r="B32" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C32" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D32" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E32" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F32" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="G32" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H32" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I32" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 艾什 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J32" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“高台 / 垂直机动”环境。</x:v>
+      </x:c>
+      <x:c r="K32" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L32" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M32" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="58" t="str">
+        <x:v>努巴尼</x:v>
+      </x:c>
+      <x:c r="B33" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C33" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D33" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E33" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F33" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G33" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H33" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I33" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J33" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K33" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L33" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M33" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="58" t="str">
+        <x:v>努巴尼</x:v>
+      </x:c>
+      <x:c r="B34" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C34" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D34" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E34" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F34" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G34" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H34" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I34" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J34" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K34" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L34" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M34" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="58" t="str">
+        <x:v>好莱坞</x:v>
+      </x:c>
+      <x:c r="B35" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C35" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D35" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E35" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F35" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G35" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H35" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I35" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J35" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“混合 / 高台 / 中远距离”环境。</x:v>
+      </x:c>
+      <x:c r="K35" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L35" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M35" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="58" t="str">
+        <x:v>好莱坞</x:v>
+      </x:c>
+      <x:c r="B36" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C36" s="58" t="str">
+        <x:v>远程消耗阵容</x:v>
+      </x:c>
+      <x:c r="D36" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E36" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F36" s="58" t="str">
+        <x:v>半藏</x:v>
+      </x:c>
+      <x:c r="G36" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="H36" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I36" s="58" t="str">
+        <x:v>西格玛 + 艾什 + 半藏 + 巴蒂斯特 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J36" s="58" t="str">
+        <x:v>对面缺乏强 Dive，或者己方长枪手感好、想通过远距离先建立人数差时。</x:v>
+      </x:c>
+      <x:c r="K36" s="58" t="str">
+        <x:v>西格玛负责占住主路与远端角度，双远程输出分开站位形成交叉枪线；辅助优先保证输出位能持续站高台或长视野位置。</x:v>
+      </x:c>
+      <x:c r="L36" s="58" t="str">
+        <x:v>不要急着冲点。先用远程伤害逼掉治疗、位移和屏障资源，打残或击杀一人后再推进目标。</x:v>
+      </x:c>
+      <x:c r="M36" s="58" t="str">
+        <x:v>最怕温斯顿/D.Va/源氏等同时扑后排。被连续切入时要及时收缩站位，必要时切换机动或反 Dive 英雄。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="58" t="str">
+        <x:v>好莱坞</x:v>
+      </x:c>
+      <x:c r="B37" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C37" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D37" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E37" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F37" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G37" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H37" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I37" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J37" s="58" t="str">
+        <x:v>对方长枪站得很散、高台很强，正面消耗很难获得优势时。</x:v>
+      </x:c>
+      <x:c r="K37" s="58" t="str">
+        <x:v>D.Va先吃掉关键爆发并接近高台，源氏和回声从不同高度压后排；安娜提供远程治疗与禁疗，雾子负责跟进和救场。</x:v>
+      </x:c>
+      <x:c r="L37" s="58" t="str">
+        <x:v>等待对方位移或防守技能出现空档后，D.Va先接触目标，两个输出同步压同一个后排，拿到击杀后立即撤出再循环。</x:v>
+      </x:c>
+      <x:c r="M37" s="58" t="str">
+        <x:v>不要一人提前进场。Dive阵容最怕进场时间不一致；如果第一波没秒人，应迅速退出而不是在对方阵型里久留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="58" t="str">
+        <x:v>伊利奥斯</x:v>
+      </x:c>
+      <x:c r="B38" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C38" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D38" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E38" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F38" s="58" t="str">
+        <x:v>法老之鹰</x:v>
+      </x:c>
+      <x:c r="G38" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H38" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I38" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 法老之鹰 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J38" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“近战 / 地形杀 / 多子图”环境。</x:v>
+      </x:c>
+      <x:c r="K38" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L38" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M38" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="58" t="str">
+        <x:v>伊利奥斯</x:v>
+      </x:c>
+      <x:c r="B39" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C39" s="58" t="str">
+        <x:v>快速冲阵阵容</x:v>
+      </x:c>
+      <x:c r="D39" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E39" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F39" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G39" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H39" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I39" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 卡西迪 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J39" s="58" t="str">
+        <x:v>需要快速穿过窄口、拐角，或对面远程火力很强但缺少持续近战能力时。</x:v>
+      </x:c>
+      <x:c r="K39" s="58" t="str">
+        <x:v>莱因哈特用盾和身体带队跨过危险区域，美负责墙体分割，卢西奥提供加速让整队迅速接近；卡西迪补稳定近距离伤害。</x:v>
+      </x:c>
+      <x:c r="L39" s="58" t="str">
+        <x:v>看到对方有人站位靠前或与队友脱节时，卢西奥加速整队压上，美用冰墙切断退路，集中火力先解决被分割目标。</x:v>
+      </x:c>
+      <x:c r="M39" s="58" t="str">
+        <x:v>不要在远距离慢慢消耗。Rush阵容价值来自快速接敌；如果队友跟不上加速，就宁可等齐再进。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="58" t="str">
+        <x:v>伊利奥斯</x:v>
+      </x:c>
+      <x:c r="B40" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C40" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D40" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E40" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F40" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G40" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H40" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I40" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J40" s="58" t="str">
+        <x:v>对面抱团很难正面突破，或者需要快速抢高台、绕过正面坦克时。</x:v>
+      </x:c>
+      <x:c r="K40" s="58" t="str">
+        <x:v>温斯顿先占高地或跳后排，源氏与猎空分别从两侧切入；安娜远程支援，雾子可以跟进并用铃保护撤退。</x:v>
+      </x:c>
+      <x:c r="L40" s="58" t="str">
+        <x:v>先让侧翼找到角度，等温斯顿落点后再同时压同一名辅助或长枪。击杀后不要深追，优先回到高地和关键位置。</x:v>
+      </x:c>
+      <x:c r="M40" s="58" t="str">
+        <x:v>避免跳到对方五人正中间。先确认敌方控制技能和保命技能，再选择目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="58" t="str">
+        <x:v>漓江塔</x:v>
+      </x:c>
+      <x:c r="B41" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C41" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D41" s="58" t="str">
+        <x:v>莱因哈特</x:v>
+      </x:c>
+      <x:c r="E41" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F41" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G41" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H41" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I41" s="58" t="str">
+        <x:v>莱因哈特 + 美 + 卡西迪 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J41" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“近战 / 快速转点”环境。</x:v>
+      </x:c>
+      <x:c r="K41" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L41" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M41" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="58" t="str">
+        <x:v>漓江塔</x:v>
+      </x:c>
+      <x:c r="B42" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C42" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D42" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E42" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F42" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G42" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H42" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I42" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J42" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K42" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L42" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M42" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="58" t="str">
+        <x:v>漓江塔</x:v>
+      </x:c>
+      <x:c r="B43" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C43" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D43" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E43" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F43" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G43" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H43" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I43" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J43" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K43" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L43" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M43" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="58" t="str">
+        <x:v>尼泊尔</x:v>
+      </x:c>
+      <x:c r="B44" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C44" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D44" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E44" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F44" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G44" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H44" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I44" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 卡西迪 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J44" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“近中距离 / 多地形”环境。</x:v>
+      </x:c>
+      <x:c r="K44" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L44" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M44" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="58" t="str">
+        <x:v>尼泊尔</x:v>
+      </x:c>
+      <x:c r="B45" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C45" s="58" t="str">
+        <x:v>高台机动阵容</x:v>
+      </x:c>
+      <x:c r="D45" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E45" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F45" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G45" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H45" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I45" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J45" s="58" t="str">
+        <x:v>地图高低差明显、对方远端输出站高台，或者需要快速转换多个角度时。</x:v>
+      </x:c>
+      <x:c r="K45" s="58" t="str">
+        <x:v>D.Va与回声利用垂直机动抢占高处，源氏从侧翼补压；安娜在安全长线支援，雾子负责跟进与解控。</x:v>
+      </x:c>
+      <x:c r="L45" s="58" t="str">
+        <x:v>先抢高台再打点。D.Va逼退高台目标后，回声和源氏立刻扩大角度，形成主路+侧面的双向压力。</x:v>
+      </x:c>
+      <x:c r="M45" s="58" t="str">
+        <x:v>不要为了追击从高台全部跳下。很多地图的优势来自高度本身，拿到击杀后优先保住高地。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="58" t="str">
+        <x:v>尼泊尔</x:v>
+      </x:c>
+      <x:c r="B46" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C46" s="58" t="str">
+        <x:v>正面稳定阵容</x:v>
+      </x:c>
+      <x:c r="D46" s="58" t="str">
+        <x:v>拉玛刹</x:v>
+      </x:c>
+      <x:c r="E46" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F46" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G46" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H46" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="I46" s="58" t="str">
+        <x:v>拉玛刹 + 美 + 卡西迪 + 卢西奥 + 巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="J46" s="58" t="str">
+        <x:v>对面机动英雄很多但击杀效率不高，或者己方更擅长抱团推进时。</x:v>
+      </x:c>
+      <x:c r="K46" s="58" t="str">
+        <x:v>拉玛刹负责持续压迫正面，美限制机动英雄撤退路线，卡西迪保护后排并补单点爆发；卢西奥帮助整队快速进退。</x:v>
+      </x:c>
+      <x:c r="L46" s="58" t="str">
+        <x:v>等对方Dive英雄先交位移，再利用减速、控制和近距离火力反打；建立人数优势后再整体推进目标。</x:v>
+      </x:c>
+      <x:c r="M46" s="58" t="str">
+        <x:v>不要把所有控制技能交给坦克。应优先留给真正切入后排的源氏、猎空、温斯顿等目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="58" t="str">
+        <x:v>釜山</x:v>
+      </x:c>
+      <x:c r="B47" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C47" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D47" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E47" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F47" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G47" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H47" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I47" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J47" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“中远距离 / 高地 / 机动”环境。</x:v>
+      </x:c>
+      <x:c r="K47" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L47" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M47" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="58" t="str">
+        <x:v>釜山</x:v>
+      </x:c>
+      <x:c r="B48" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C48" s="58" t="str">
+        <x:v>远程消耗阵容</x:v>
+      </x:c>
+      <x:c r="D48" s="58" t="str">
+        <x:v>西格玛</x:v>
+      </x:c>
+      <x:c r="E48" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F48" s="58" t="str">
+        <x:v>半藏</x:v>
+      </x:c>
+      <x:c r="G48" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="H48" s="58" t="str">
+        <x:v>禅雅塔</x:v>
+      </x:c>
+      <x:c r="I48" s="58" t="str">
+        <x:v>西格玛 + 艾什 + 半藏 + 巴蒂斯特 + 禅雅塔</x:v>
+      </x:c>
+      <x:c r="J48" s="58" t="str">
+        <x:v>对面缺乏强 Dive，或者己方长枪手感好、想通过远距离先建立人数差时。</x:v>
+      </x:c>
+      <x:c r="K48" s="58" t="str">
+        <x:v>西格玛负责占住主路与远端角度，双远程输出分开站位形成交叉枪线；辅助优先保证输出位能持续站高台或长视野位置。</x:v>
+      </x:c>
+      <x:c r="L48" s="58" t="str">
+        <x:v>不要急着冲点。先用远程伤害逼掉治疗、位移和屏障资源，打残或击杀一人后再推进目标。</x:v>
+      </x:c>
+      <x:c r="M48" s="58" t="str">
+        <x:v>最怕温斯顿/D.Va/源氏等同时扑后排。被连续切入时要及时收缩站位，必要时切换机动或反 Dive 英雄。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="58" t="str">
+        <x:v>釜山</x:v>
+      </x:c>
+      <x:c r="B49" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C49" s="58" t="str">
+        <x:v>机动切后阵容</x:v>
+      </x:c>
+      <x:c r="D49" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E49" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F49" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G49" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H49" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I49" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J49" s="58" t="str">
+        <x:v>对方长枪站得很散、高台很强，正面消耗很难获得优势时。</x:v>
+      </x:c>
+      <x:c r="K49" s="58" t="str">
+        <x:v>D.Va先吃掉关键爆发并接近高台，源氏和回声从不同高度压后排；安娜提供远程治疗与禁疗，雾子负责跟进和救场。</x:v>
+      </x:c>
+      <x:c r="L49" s="58" t="str">
+        <x:v>等待对方位移或防守技能出现空档后，D.Va先接触目标，两个输出同步压同一个后排，拿到击杀后立即撤出再循环。</x:v>
+      </x:c>
+      <x:c r="M49" s="58" t="str">
+        <x:v>不要一人提前进场。Dive阵容最怕进场时间不一致；如果第一波没秒人，应迅速退出而不是在对方阵型里久留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="58" t="str">
+        <x:v>绿洲</x:v>
+      </x:c>
+      <x:c r="B50" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C50" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D50" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E50" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F50" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G50" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H50" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I50" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J50" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“机动 / 近中距离”环境。</x:v>
+      </x:c>
+      <x:c r="K50" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L50" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M50" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="58" t="str">
+        <x:v>绿洲</x:v>
+      </x:c>
+      <x:c r="B51" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C51" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D51" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E51" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F51" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G51" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H51" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I51" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J51" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K51" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L51" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M51" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="58" t="str">
+        <x:v>绿洲</x:v>
+      </x:c>
+      <x:c r="B52" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C52" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D52" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E52" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F52" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G52" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H52" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I52" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J52" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K52" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L52" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M52" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="58" t="str">
+        <x:v>新皇后街</x:v>
+      </x:c>
+      <x:c r="B53" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C53" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D53" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E53" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="F53" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G53" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H53" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I53" s="58" t="str">
+        <x:v>温斯顿 + 猎空 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J53" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“机动 / 长路线 / 侧翼”环境。</x:v>
+      </x:c>
+      <x:c r="K53" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L53" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M53" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="58" t="str">
+        <x:v>新皇后街</x:v>
+      </x:c>
+      <x:c r="B54" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C54" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D54" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E54" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F54" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G54" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H54" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I54" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J54" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K54" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L54" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M54" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="58" t="str">
+        <x:v>新皇后街</x:v>
+      </x:c>
+      <x:c r="B55" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C55" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D55" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E55" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F55" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G55" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H55" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I55" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J55" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K55" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L55" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M55" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="58" t="str">
+        <x:v>斗兽场</x:v>
+      </x:c>
+      <x:c r="B56" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C56" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D56" s="58" t="str">
+        <x:v>拉玛刹</x:v>
+      </x:c>
+      <x:c r="E56" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="F56" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G56" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H56" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I56" s="58" t="str">
+        <x:v>拉玛刹 + 卡西迪 + 源氏 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J56" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“中近距离 / 拐角 / 机动”环境。</x:v>
+      </x:c>
+      <x:c r="K56" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L56" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M56" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="58" t="str">
+        <x:v>斗兽场</x:v>
+      </x:c>
+      <x:c r="B57" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C57" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D57" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E57" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F57" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G57" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H57" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I57" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J57" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K57" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L57" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M57" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="58" t="str">
+        <x:v>斗兽场</x:v>
+      </x:c>
+      <x:c r="B58" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C58" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D58" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E58" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F58" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G58" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H58" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I58" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J58" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K58" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L58" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M58" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="58" t="str">
+        <x:v>埃斯佩兰萨</x:v>
+      </x:c>
+      <x:c r="B59" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C59" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D59" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E59" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F59" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G59" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H59" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I59" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J59" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“长视野 / 高地 / 机动”环境。</x:v>
+      </x:c>
+      <x:c r="K59" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L59" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M59" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="58" t="str">
+        <x:v>埃斯佩兰萨</x:v>
+      </x:c>
+      <x:c r="B60" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C60" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D60" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E60" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F60" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G60" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H60" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I60" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J60" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K60" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L60" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M60" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="58" t="str">
+        <x:v>埃斯佩兰萨</x:v>
+      </x:c>
+      <x:c r="B61" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C61" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D61" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E61" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F61" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G61" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H61" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I61" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J61" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K61" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L61" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M61" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="58" t="str">
+        <x:v>苏拉瓦萨</x:v>
+      </x:c>
+      <x:c r="B62" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C62" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D62" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E62" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="F62" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G62" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H62" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I62" s="58" t="str">
+        <x:v>温斯顿 + 猎空 + 源氏 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J62" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“高速转点 / 近战 / 机动”环境。</x:v>
+      </x:c>
+      <x:c r="K62" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L62" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M62" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="58" t="str">
+        <x:v>苏拉瓦萨</x:v>
+      </x:c>
+      <x:c r="B63" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C63" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D63" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E63" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F63" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G63" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H63" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I63" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J63" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K63" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L63" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M63" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="58" t="str">
+        <x:v>苏拉瓦萨</x:v>
+      </x:c>
+      <x:c r="B64" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C64" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D64" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E64" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F64" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G64" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H64" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I64" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J64" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K64" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L64" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M64" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="58" t="str">
+        <x:v>新渣客城</x:v>
+      </x:c>
+      <x:c r="B65" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C65" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D65" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E65" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="F65" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G65" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H65" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I65" s="58" t="str">
+        <x:v>温斯顿 + 猎空 + 源氏 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J65" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“快速转点 / 多入口”环境。</x:v>
+      </x:c>
+      <x:c r="K65" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L65" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M65" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="58" t="str">
+        <x:v>新渣客城</x:v>
+      </x:c>
+      <x:c r="B66" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C66" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D66" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E66" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F66" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G66" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H66" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I66" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J66" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K66" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L66" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M66" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="58" t="str">
+        <x:v>新渣客城</x:v>
+      </x:c>
+      <x:c r="B67" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C67" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D67" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E67" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F67" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G67" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H67" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I67" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J67" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K67" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L67" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M67" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="58" t="str">
+        <x:v>阿特利斯</x:v>
+      </x:c>
+      <x:c r="B68" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C68" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D68" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E68" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F68" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G68" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H68" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I68" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 卢西奥 + 雾子</x:v>
+      </x:c>
+      <x:c r="J68" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“紧凑团战 / 快速轮转”环境。</x:v>
+      </x:c>
+      <x:c r="K68" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L68" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M68" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="58" t="str">
+        <x:v>阿特利斯</x:v>
+      </x:c>
+      <x:c r="B69" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C69" s="58" t="str">
+        <x:v>高速机动阵容</x:v>
+      </x:c>
+      <x:c r="D69" s="58" t="str">
+        <x:v>温斯顿</x:v>
+      </x:c>
+      <x:c r="E69" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F69" s="58" t="str">
+        <x:v>猎空</x:v>
+      </x:c>
+      <x:c r="G69" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H69" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I69" s="58" t="str">
+        <x:v>温斯顿 + 源氏 + 猎空 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J69" s="58" t="str">
+        <x:v>需要频繁转点、追击残血或不断抢高台的地图阶段。</x:v>
+      </x:c>
+      <x:c r="K69" s="58" t="str">
+        <x:v>温斯顿负责第一个制造空间，猎空和源氏利用速度提前占侧翼；双辅助保持能快速转移的位置，不要落在队伍最后。</x:v>
+      </x:c>
+      <x:c r="L69" s="58" t="str">
+        <x:v>转点时提前离开旧战场，先让猎空/源氏占入口；团战开始后温斯顿落点，两个输出同时切同一后排。</x:v>
+      </x:c>
+      <x:c r="M69" s="58" t="str">
+        <x:v>最忌讳有人恋战导致全队转点脱节。该阵容宁愿少追一个残血，也要保证下一波先到关键位置。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="58" t="str">
+        <x:v>阿特利斯</x:v>
+      </x:c>
+      <x:c r="B70" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C70" s="58" t="str">
+        <x:v>稳定中距离阵容</x:v>
+      </x:c>
+      <x:c r="D70" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E70" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F70" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G70" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H70" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I70" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J70" s="58" t="str">
+        <x:v>对面反 Dive 很强，或者需要兼顾高台与正面持续输出时。</x:v>
+      </x:c>
+      <x:c r="K70" s="58" t="str">
+        <x:v>D.Va既能保护后排也能抢高地，艾什稳定中距离输出，源氏负责收割和侧压；安娜与雾子提供强功能和容错。</x:v>
+      </x:c>
+      <x:c r="L70" s="58" t="str">
+        <x:v>先用艾什和安娜制造血线压力，逼对面交资源；D.Va随后吃关键伤害并压高台，源氏在对面残血后再进入收割。</x:v>
+      </x:c>
+      <x:c r="M70" s="58" t="str">
+        <x:v>不要让D.Va长期单独站正面吃伤害。她的价值在于反复占角、保护和短时间爆发，而不是当固定护盾坦克。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="58" t="str">
+        <x:v>霓虹交汇点</x:v>
+      </x:c>
+      <x:c r="B71" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C71" s="58" t="str">
+        <x:v>默认稳定阵容</x:v>
+      </x:c>
+      <x:c r="D71" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E71" s="58" t="str">
+        <x:v>艾什</x:v>
+      </x:c>
+      <x:c r="F71" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="G71" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H71" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I71" s="58" t="str">
+        <x:v>D.Va + 艾什 + 源氏 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J71" s="58" t="str">
+        <x:v>默认开局或不确定对面阵容时。适合这张图的“城市巷战 / 高低差 / 混合”环境。</x:v>
+      </x:c>
+      <x:c r="K71" s="58" t="str">
+        <x:v>围绕地图特性打稳定资源交换：先处理关键高台/拐角，再让坦克推进空间。输出位不要只跟着坦克站正面，至少保留一个侧角制造交叉火力。</x:v>
+      </x:c>
+      <x:c r="L71" s="58" t="str">
+        <x:v>坦克先逼出对方位移、护盾或关键保命技能；看到对方资源交掉后，输出位再同步压角，辅助把功能技能留给真正的击杀窗口。</x:v>
+      </x:c>
+      <x:c r="M71" s="58" t="str">
+        <x:v>不要因为阵容完整就强行五人抱死。若对面长枪压制明显，就先抢角度；若对面 Dive 很强，则缩短后排之间的距离并保留反切技能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="58" t="str">
+        <x:v>霓虹交汇点</x:v>
+      </x:c>
+      <x:c r="B72" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C72" s="58" t="str">
+        <x:v>高台机动阵容</x:v>
+      </x:c>
+      <x:c r="D72" s="58" t="str">
+        <x:v>D.Va</x:v>
+      </x:c>
+      <x:c r="E72" s="58" t="str">
+        <x:v>源氏</x:v>
+      </x:c>
+      <x:c r="F72" s="58" t="str">
+        <x:v>回声</x:v>
+      </x:c>
+      <x:c r="G72" s="58" t="str">
+        <x:v>安娜</x:v>
+      </x:c>
+      <x:c r="H72" s="58" t="str">
+        <x:v>雾子</x:v>
+      </x:c>
+      <x:c r="I72" s="58" t="str">
+        <x:v>D.Va + 源氏 + 回声 + 安娜 + 雾子</x:v>
+      </x:c>
+      <x:c r="J72" s="58" t="str">
+        <x:v>地图高低差明显、对方远端输出站高台，或者需要快速转换多个角度时。</x:v>
+      </x:c>
+      <x:c r="K72" s="58" t="str">
+        <x:v>D.Va与回声利用垂直机动抢占高处，源氏从侧翼补压；安娜在安全长线支援，雾子负责跟进与解控。</x:v>
+      </x:c>
+      <x:c r="L72" s="58" t="str">
+        <x:v>先抢高台再打点。D.Va逼退高台目标后，回声和源氏立刻扩大角度，形成主路+侧面的双向压力。</x:v>
+      </x:c>
+      <x:c r="M72" s="58" t="str">
+        <x:v>不要为了追击从高台全部跳下。很多地图的优势来自高度本身，拿到击杀后优先保住高地。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="58" t="str">
+        <x:v>霓虹交汇点</x:v>
+      </x:c>
+      <x:c r="B73" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C73" s="58" t="str">
+        <x:v>正面稳定阵容</x:v>
+      </x:c>
+      <x:c r="D73" s="58" t="str">
+        <x:v>拉玛刹</x:v>
+      </x:c>
+      <x:c r="E73" s="58" t="str">
+        <x:v>美</x:v>
+      </x:c>
+      <x:c r="F73" s="58" t="str">
+        <x:v>卡西迪</x:v>
+      </x:c>
+      <x:c r="G73" s="58" t="str">
+        <x:v>卢西奥</x:v>
+      </x:c>
+      <x:c r="H73" s="58" t="str">
+        <x:v>巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="I73" s="58" t="str">
+        <x:v>拉玛刹 + 美 + 卡西迪 + 卢西奥 + 巴蒂斯特</x:v>
+      </x:c>
+      <x:c r="J73" s="58" t="str">
+        <x:v>对面机动英雄很多但击杀效率不高，或者己方更擅长抱团推进时。</x:v>
+      </x:c>
+      <x:c r="K73" s="58" t="str">
+        <x:v>拉玛刹负责持续压迫正面，美限制机动英雄撤退路线，卡西迪保护后排并补单点爆发；卢西奥帮助整队快速进退。</x:v>
+      </x:c>
+      <x:c r="L73" s="58" t="str">
+        <x:v>等对方Dive英雄先交位移，再利用减速、控制和近距离火力反打；建立人数优势后再整体推进目标。</x:v>
+      </x:c>
+      <x:c r="M73" s="58" t="str">
+        <x:v>不要把所有控制技能交给坦克。应优先留给真正切入后排的源氏、猎空、温斯顿等目标。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R093a91ba5c1f4257"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R5c5ce25173114183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="R537b9e57c4b443a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R714a5c40b82245b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R08cea8712375401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Reba6588898d54a24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R2beb7c71115046f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R07a5961507d848dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_comps" sheetId="9" r:id="R774a594acba142b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R1fee1f896cf548df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R7d59c61fab144227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Ra59ac97a9aab4b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R3fc5359190fe4c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R2f3354bdf47a4094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R877f31d340244e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R15de08537a9f4c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R8e8c39cf3bcd435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_comps" sheetId="9" r:id="R3c0d3004ed494e4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,12 +33,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2B3445"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -93,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
@@ -235,6 +240,17 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -530,7 +546,7 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="32" t="str">
-        <x:v>v3.7.0</x:v>
+        <x:v>v3.8.0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -629,6 +645,7 @@
     <x:col min="3" max="3" width="10" style="14" customWidth="1"/>
     <x:col min="4" max="4" width="34" style="14" customWidth="1"/>
     <x:col min="5" max="5" width="56" style="14" customWidth="1"/>
+    <x:col min="6" max="6" width="65" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -657,6 +674,9 @@
           <x:t xml:space="preserve">note</x:t>
         </x:is>
       </x:c>
+      <x:c r="F1" s="69" t="str">
+        <x:v>avatar_url</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="32" t="n">
@@ -682,6 +702,9 @@
           <x:t xml:space="preserve">擅长吃飞行弹道与切后排。面对查莉娅时，防御矩阵无法阻挡光束，注意不要给她白送能量。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F2" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/df5a5532862d9292634fb3dc0e51a4705aa601de65e5e815513ccc663d84de56.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="32" t="n">
@@ -707,6 +730,9 @@
           <x:t xml:space="preserve">核心是机动性与进出场节奏。硬控越多越难发挥，先逼控制技能再进场。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F3" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/ff5c54f43ad253c7faeda9c4ed31d42582ea6b19205d197866f3dd0c0aa14c16.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="32" t="n">
@@ -732,6 +758,9 @@
           <x:t xml:space="preserve">近距离持续压迫强，怕被拉扯与减疗。利用掩体缩短接敌距离。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F4" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/06eeecb359f311f43a8f5121d4f9f3a93c565d70b30e94ef543c05596c9a39dc.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="32" t="n">
@@ -757,6 +786,9 @@
           <x:t xml:space="preserve">强在正面抗压和打断。遇到高能查莉娅时尽量拉开并集火她的队友。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F5" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/a73958a28551f5254f3ab3f97c5f5f8d698a95c0b6a515d1a2b1caac169205a6.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="32" t="n">
@@ -782,6 +814,9 @@
           <x:t xml:space="preserve">变身阶段近战压制力高。注意形态切换窗口，不要在资源不足时强行冲脸。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F6" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/ddef7c9fb8ce4256e8508196b486f81950efe7aaa6cf27fec4668beb4cd15774.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="32" t="n">
@@ -807,6 +842,9 @@
           <x:t xml:space="preserve">强依赖近距离与地图拐角。空旷图和高地多时通常更难发挥。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F7" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/551fbe070c16fdfcc17f7f1de63af22c53e7d2f1340fc2f3172441504527bc4e.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="32" t="n">
@@ -832,6 +870,9 @@
           <x:t xml:space="preserve">钩中关键目标能快速形成击杀。最怕减疗与被集火，注意呼吸器使用时机。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F8" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/89ddf07e4b619ed96169042e296a1b8856d102746f35add88284b44a9a5a6a03.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="32" t="n">
@@ -857,6 +898,9 @@
           <x:t xml:space="preserve">中远距离资源交换很强，怕被贴脸和多方向切入。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F9" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/a4c032fa466c9a6d9c6974747635d7ef910027f91cd58892af0c899db565f92d.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="32" t="n">
@@ -882,6 +926,9 @@
           <x:t xml:space="preserve">主要针对脆皮后排和高台。跳入前先确认队友能否跟伤害，否则容易白给。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F10" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/46a10db3aa908c590ddc4e7606376a88143d1f1306ecfbea043263040f9529a5.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="32" t="n">
@@ -907,6 +954,9 @@
           <x:t xml:space="preserve">靠骚扰和位移制造空间。遇到大量控制时减少长时间停留。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F11" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/9ef1d58867136e0b26f928d896000b9dab216118f6e2f59e53f2e975e1e27afa.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="32" t="n">
@@ -932,6 +982,9 @@
           <x:t xml:space="preserve">对依赖吸收弹道的坦克很强。护盾使用质量决定能量与生存，避免双盾一起交空。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F12" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/9b6f63cc66ddf9d5e0862173c733cc0d2e574c5c89357798d91b93b2f95a7080.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="32" t="n">
@@ -957,6 +1010,9 @@
           <x:t xml:space="preserve">机甲坦克，兼具正面屏障、机动和近战压迫。2026-09-17 热修后 5v5 护甲由 325 降至 275，Focused Fusion 伤害、推进器续航与 Fusion Repeater 也被削弱；当前更需要控制进场时机，避免长时间正面硬换血。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F13" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/a46c60b8562fdbd0b8308396d0808f7606fba208bc67cccf3f82fe56d2c73b9d.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="32" t="n">
@@ -982,6 +1038,9 @@
           <x:t xml:space="preserve">硬光坦克，依靠屏障、推击和中距离压制控制正面空间。面对多方向突进或持续光束时更依赖站位。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F14" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/1161c112292c56c052c0ae711792fcde06e3251b98bc9709e582dd7585b5dcd6.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="32" t="n">
@@ -1007,6 +1066,9 @@
           <x:t xml:space="preserve">强突进坦克，依靠跳跃、尖刺和墙体压缩空间。遇到稳定抗冲和持续光束阵容时避免无脑进场。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F15" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/ca48b96dbae6ea7f58ce8a5e73513c8c62b1685bdbf258020fb78bb21a008b5f.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="32" t="n">
@@ -1032,6 +1094,9 @@
           <x:t xml:space="preserve">持续火力和近中距离压迫很强，适合正面对拼大体型目标。面对减疗、矩阵和远程消耗时减少长时间站桩。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F16" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/33d39bb439c08975197fc52eff4874716839711b5356c4fdc174f9c24bac1d0e.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="32" t="n">
@@ -1057,6 +1122,9 @@
           <x:t xml:space="preserve">中远距离压制优秀，怕强突脸。站位要给自己留撤退路线。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F17" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/4076bbaa2eb52a0bfe612434071e56e7702d5454473dbbea2f9e392a9d997a94.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="32" t="n">
@@ -1082,6 +1150,9 @@
           <x:t xml:space="preserve">爆发火力高，但体型大、技能窗口明显。尽量跟坦克资源同步。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F18" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/4ede795c2a681aaccfa72d0c901cba0cb8a2c292fd6a97b2ba9faed161c2d184.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="32" t="n">
@@ -1107,6 +1178,9 @@
           <x:t xml:space="preserve">中近距离稳定，磁性手雷/控制类技能能限制高机动英雄。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F19" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/9240cd64cc8ef58df9acbf55204ab1b5d8578f743fda5931f0dbccbd75ab841b.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="32" t="n">
@@ -1132,6 +1206,9 @@
           <x:t xml:space="preserve">适合切脆皮和收割残血。面对光束英雄时，弹反价值会明显下降。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F20" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/156b12c20b1aea872c1eeb5bb37a7de1047b2ab30ecefd0663a8925badde1ea8.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="32" t="n">
@@ -1157,6 +1234,9 @@
           <x:t xml:space="preserve">有高爆发和探测能力，但被贴脸后容错下降。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F21" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/78b61c3e806fb26b02b8980fba62189155074fc15bd865b0883268e546030be5.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="32" t="n">
@@ -1182,6 +1262,9 @@
           <x:t xml:space="preserve">狭窄地形强，空中与远距离目标难处理。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F22" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/7660b9fc6f25f30858fdd8797fe0d52b2306f1e78fef99843f58a274e69af046.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="32" t="n">
@@ -1207,6 +1290,9 @@
           <x:t xml:space="preserve">擅长分割阵型和减速近战目标。远距离压力相对有限。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F23" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/4a55ced3bd597fb08e0fde9dc007f8543ac616ba98ca3db9b0e4d871a8ae17f8.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="32" t="n">
@@ -1232,6 +1318,9 @@
           <x:t xml:space="preserve">利用高空角度绕盾输出。对面双长枪时更依赖掩体和天使资源。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F24" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/60ac2d5de4a6d34644d8872233da402f1436c87f804bb11a21661bb30bf4a51f.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="32" t="n">
@@ -1257,6 +1346,9 @@
           <x:t xml:space="preserve">近距离对大体型目标伤害很高，核心是利用传送/幽灵形态接近并安全撤出。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F25" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/dc6ff07ac790c00dc95a40882449617bb6e0e38906b353a630cffe0c815270a9.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="32" t="n">
@@ -1282,6 +1374,9 @@
           <x:t xml:space="preserve">适合破坏高机动英雄节奏。不要只追求单杀，黑入关键目标帮助团队集火更稳定。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F26" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/47727b02a16e3bd7b2447d86ae1edf11587bc320b2aecb4f2f16a7ca4ad4e8a0.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="32" t="n">
@@ -1307,6 +1402,9 @@
           <x:t xml:space="preserve">泛用性高，对空稳定。高地与持续输出环境最舒服。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F27" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/c93b5f0a528c40473188f77cc2a267aee7d5b6cf5c9e104105d634b4388674e2.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="32" t="n">
@@ -1332,6 +1430,9 @@
           <x:t xml:space="preserve">轨道枪爆发和滑铲机动兼备，适合中距离持续充能后寻找关键爆发。面对高机动切入时保留滑铲更安全。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F28" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/82b8c1b8765dcb9a0ba16e343c3516bf324c771ac81e9878473280216e70a889.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="32" t="n">
@@ -1357,6 +1458,9 @@
           <x:t xml:space="preserve">光束对矩阵和弹反类防御很有效，适合近距离和狭窄目标点。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F29" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/ebec57e8bd68b3d4383edfeb34f8f52dd0b94a6467d594c2fee722e8a97c32aa.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="32" t="n">
@@ -1382,6 +1486,9 @@
           <x:t xml:space="preserve">炮台能限制侧翼英雄活动，但面对远程与空中压制时容易被安全拆掉。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F30" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/ce17118cedc29b0d2ac1e059666bed36b9531c85079b0b894bb402d12c917ba9.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="32" t="n">
@@ -1407,6 +1514,9 @@
           <x:t xml:space="preserve">靠持续骚扰和资源差取胜。尽量逼技能，不必每次都强求击杀。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F31" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/4504f6f15cb3feaa92ecd38e01dcf751cb5abdac2e0bb52d0555727e53277502.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="32" t="n">
@@ -1432,6 +1542,9 @@
           <x:t xml:space="preserve">远距离威慑强，最怕高机动强突。站位要能快速换点。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F32" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/6e4702b45f196aaf51555cf57327322721f45458b17f5f0643ed008a88378259.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="32" t="n">
@@ -1457,6 +1570,9 @@
           <x:t xml:space="preserve">机动性与爆发强，但空中轨迹容易被长枪锁定。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F33" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/d4f2d5b0c2b7e82d61353186c5f23152ccba9d3569b50839aa580dca3e9114ba.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="32" t="n">
@@ -1482,6 +1598,9 @@
           <x:t xml:space="preserve">高机动火焰侧翼，擅长追击脆皮和制造燃烧压力。面对稳定控制和强保护阵容时不要连续硬切。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F34" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/2c38b41d79a1ce9a08b9ad8eb7edf3ff819bd448af16a5815be8c7fdb7203aa0.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="32" t="n">
@@ -1507,6 +1626,9 @@
           <x:t xml:space="preserve">中距离爆发型输出，步枪和手雷适合持续压血线。被高机动英雄贴脸时输出环境会明显变差。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F35" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/c51e2f698138861c0e3b6cfab3c3ca9d67fd709be175e7c397aa6f2649712a30.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="32" t="n">
@@ -1532,6 +1654,9 @@
           <x:t xml:space="preserve">高机动远程输出，擅长借助位移寻找射击角度。被快速贴脸时需要提前保留位移。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F36" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/811963897c352d9f178bec882d94bd0281074feee7c429c5145b6b8ea8ebe862.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="32" t="n">
@@ -1557,6 +1682,9 @@
           <x:t xml:space="preserve">高机动侧翼输出，通过位移和持续枪火切入后排。遇到强控制、炮台或贴身保护阵容时先逼技能。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F37" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/070481cf871590a2b45a51d1335f9fe3d65eb4e4d361ecdd998b34fae2ed65d5.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="32" t="n">
@@ -1582,6 +1710,9 @@
           <x:t xml:space="preserve">偏精准追踪和中距离持续输出，能够稳定惩罚暴露目标。面对强突和超远距离狙击时需要不断换位。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F38" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/4bfd3d8b95844231115cb5bf4db03344c71bc3e865189c52403b2dc51438e63a.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="32" t="n">
@@ -1607,6 +1738,9 @@
           <x:t xml:space="preserve">近战侧翼输出，依靠冲刺和格挡接近目标。面对空中英雄、长枪和强近身保护时更难持续贴身。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F39" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/cf8ffb52b6f315546d5e94e9d6defad5a2c570798776956de23f47536f9529da.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="32" t="n">
@@ -1632,6 +1766,9 @@
           <x:t xml:space="preserve">钻地和冲刺带来很强的突进与撤离能力，适合近距离爆发和切后排。面对空中目标和长枪时射程劣势明显。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F40" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/dcab9123f5f55df22e54d4e797de43c71b917e0149dd059a7fd6136f48464cd0.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="32" t="n">
@@ -1657,6 +1794,9 @@
           <x:t xml:space="preserve">禁疗是对高回复阵容的核心克制。自保依赖睡针，站位尽量让自己只暴露一个角度。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F41" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/985b06beae46b7ba3ca87d1512d0fc62ca7f206ceca58ef16fc44d43a1cc84ed.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="32" t="n">
@@ -1682,6 +1822,9 @@
           <x:t xml:space="preserve">不朽领域能反制爆发，但怕被强突后排。利用跳跃维持高地优势。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F42" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/d4e6f1ca45d9f88fa89260787397f141a6f007b14e5b26698883b6a17bab9680.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="32" t="n">
@@ -1707,6 +1850,9 @@
           <x:t xml:space="preserve">专长是保护后排、反突进。不要把自己当主坦长期站最前面。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F43" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/795fba91376d87d441a7f359ae12a3175dfa95825ccc4414cc6b95b129fc4cb0.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="32" t="n">
@@ -1732,6 +1878,9 @@
           <x:t xml:space="preserve">价值主要来自加速与节奏控制，而不是单纯治疗量。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F44" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/040bb13f5123ab93faad2f95627ba184608aef4b2469a4d3003859c7087df044.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="32" t="n">
@@ -1757,6 +1906,9 @@
           <x:t xml:space="preserve">伤害增幅能显著提高长枪/飞行英雄威胁。注意飞行路径与复活位置。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F45" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/3bfb8bd8ec827e53d870f1238ab73d8aa1f5dbfbcfaaf7f96ffcd35b5c6102ab.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="32" t="n">
@@ -1782,6 +1934,9 @@
           <x:t xml:space="preserve">自保和追残血强，但功能性偏少。适合对付很难瞄准的近身侧翼。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F46" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/f48f8485056d5d00dad195859188d23e50f7126b8b08b5646f46ef1b42f5e1de.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="32" t="n">
@@ -1807,6 +1962,9 @@
           <x:t xml:space="preserve">乱能显著提高集火效率，但自身缺乏位移，需要队友保护。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F47" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/7d1546b1541a8afc39353f9337a408d6275a141b0432b7e560ef61579996b0fc.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="32" t="n">
@@ -1832,6 +1990,9 @@
           <x:t xml:space="preserve">铃可以解除多种负面效果，位移让她很难被单切。关键是不要过早浪费铃。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F48" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/408603fe037e8576078eaac5eab2fb251489ced4003b11f5f522776d43d0b83d.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="32" t="n">
@@ -1857,6 +2018,9 @@
           <x:t xml:space="preserve">拉人和平台能救队友失误，但需要提前观察战场，避免把队友拉离优势位置。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F49" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/3376515cebed0904012e67e956f6d1b9c12e03da642845eeaf787b7e4c7b339d.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="32" t="n">
@@ -1882,6 +2046,9 @@
           <x:t xml:space="preserve">输出能力较高，治疗塔位置决定续航。塔被频繁拆掉时需要不断换点。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F50" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/ce42d1455e03e79f321345fea84b27a8918b5db8bd7ab9b2ca9e569606ede9e4.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="32" t="n">
@@ -1907,6 +2074,9 @@
           <x:t xml:space="preserve">依赖移动和团队节奏，保持与队伍的安全距离并利用加速窗口。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F51" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/c0167d251e57b0aa2b1e16c37d87f0e7c77263db9dd0503d77b5f2589bf3e4a0.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="32" t="n">
@@ -1932,6 +2102,9 @@
           <x:t xml:space="preserve">空中机动辅助，可以快速转移并帮助队友调整位置。面对强对空或高机动追击时利用高度和掩体保持安全。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F52" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/03a184cd0de27091e0099ac22635ad9615a8f6997881a5c25cc5f2444764f729.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="32" t="n">
@@ -1957,6 +2130,9 @@
           <x:t xml:space="preserve">兼顾范围治疗、弹射输出和限制能力，适合中近距离团队作战。面对强突后排时提前用位移和回返能力拉开。</x:t>
         </x:is>
       </x:c>
+      <x:c r="F53" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/a9733c2367e0cbd70b9316fd2e1e17028653ec56d0051ea6ff098531dc4f99fc.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="32" t="n">
@@ -1981,6 +2157,9 @@
         <x:is>
           <x:t xml:space="preserve">高机动治疗辅助，可以持续照顾队友并快速重新站位。被多名高机动英雄压后排时优先保证自身生存。</x:t>
         </x:is>
+      </x:c>
+      <x:c r="F54" s="58" t="str">
+        <x:v>https://d15f34w2p8l1cc.cloudfront.net/overwatch/4959500b495b35c0908be2abda56b53f2601b2c5cc39a1cfde8df1bffd38d66d.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R1fee1f896cf548df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="R7d59c61fab144227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Ra59ac97a9aab4b90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="R3fc5359190fe4c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R2f3354bdf47a4094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="R877f31d340244e33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R15de08537a9f4c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="R8e8c39cf3bcd435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_comps" sheetId="9" r:id="R3c0d3004ed494e4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R0f1689567ac64660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heroes" sheetId="2" r:id="Rf7e65777eed542d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="counters" sheetId="3" r:id="Rb401066d314846d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maps" sheetId="4" r:id="Re81a23eee88046b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="5" r:id="R6863c5dbad354933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="6" r:id="Red8acd64060f400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_routes" sheetId="7" r:id="R1a42005226074196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="route_help" sheetId="8" r:id="Radac6c8a8d374bf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="map_comps" sheetId="9" r:id="Rc2845f44c8304695"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -546,7 +546,7 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="32" t="str">
-        <x:v>v3.8.0</x:v>
+        <x:v>v3.8.1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
